--- a/data/gates/base_completa_ILIA2026.xlsx
+++ b/data/gates/base_completa_ILIA2026.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modelos de Procesamiento de Lenguaje Natural y algoritmos de clustering. </t>
+          <t>Remesh (plataforma de diálogo masivo con IA de Remesh Inc., Nueva York), adoptada por la ONU (DPPA Innovation Cell) para los diálogos digitales.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -817,7 +817,11 @@
           <t>Herramientas de Inteligencia Artificial (transcripción de audios/videos, análisis, sistematización y síntesis de las discusiones) operadas por la empresa TDS Company; la plataforma Strateegia (de TDS Company) fue usada para la recolección de recomendaciones en la etapa nacional. No se identifica con certeza el modelo/familia técnica de IA empleado en la sistematización.</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Voz a Texto; NLP</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
@@ -1338,7 +1342,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -1933,7 +1937,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>otra institución pública</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1988,12 +1992,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Biblioteca del Congreso Nacional</t>
+          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -2362,7 +2366,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
@@ -2869,7 +2873,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -3190,12 +3194,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Atención automatizada mediante procesamiento de lenguaje natural, análisis de datos y algoritmos de inteligencia artificial para responder consultas ciudadanas sobre más de 400 temas de interés.</t>
+          <t>Agente virtual de Bogotá (Secretaría General) con módulos de participación además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa ; atiende por WhatsApp/Telegram/webchat.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares; Presupuestos Participativos</t>
+          <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -3761,7 +3765,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -4092,7 +4096,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4120,7 +4124,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras.</t>
+          <t>Facilitar diálogos anónimos en tiempo real, agrupar opiniones y permitir votaciones sobre las opiniones de otros participantes.</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4130,7 +4134,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural (NLP)</t>
+          <t>Remesh (plataforma de diálogo masivo con IA, Remesh Inc.), con apoyo de la DPPA Innovation Cell.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -4145,7 +4149,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4514,7 +4518,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chatbot a través de WhatsA´´ </t>
+          <t>Chatbot a través de WhatsApp</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4854,7 +4858,11 @@
           <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
@@ -4875,7 +4883,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -4885,7 +4893,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
@@ -4895,7 +4903,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>NLP; Resumen automatico; Clasificacion/agrupacion de texto (capacidad de la plataforma sujeta a plan Premium; activacion NO confirmada en TT)</t>
+          <t>Chatbot - Inespecífico</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -5033,7 +5041,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil; Academia</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">

--- a/data/gates/base_completa_ILIA2026.xlsx
+++ b/data/gates/base_completa_ILIA2026.xlsx
@@ -12,9 +12,9 @@
     <sheet name="3 · Evidencia y fuentes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos que entran'!$A$1:$Z$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · Excluidos'!$A$1:$E$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Evidencia y fuentes'!$A$1:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos que entran'!$A$1:$Z$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · Excluidos'!$A$1:$E$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Evidencia y fuentes'!$A$1:$K$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
+          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Investigación académica (Co:Lab USP / Cátedra Brasil-Alemania, getip) sobre el uso de IA generativa para apoyar a la ciudadanía a redactar y estructurar propuestas en procesos de participación, tomando como referencia el orçamento participativo de São Paulo. Descrito como 'pesquisas em andamento' / proyecto de investigación-prototipo, no como una herramienta oficial desplegada en el proceso real (que opera vía la plataforma Participe+/Participe Mais de la Prefeitura, sin IA generativa confirmada).</t>
+          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1164,16 +1164,16 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Asistir a la ciudadanía a formular, redactar y estructurar propuestas de forma comprensible y jurídicamente/financieramente viable; reducir asimetrías para que las propuestas no fracasen por obstáculos legales o financieros; servir de puente entre gobierno y sociedad. (Descrito como capacidad investigada/prototipada, no como servicio en producción.).</t>
+          <t>Según el material de Colab, en la edición 2025-2026 / 2026-2027 la IA agilizó la fase de análisis y 'reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón en costos directos y 99,98% de disponibilidad del sistema incluso en picos de votación. Una fuente describe además que 'a inteligência artificial foi utilizada para filtrar conexões inseguras' mediante AWS CloudFront (seguridad/infraestructura). El uso adicional de IA en torno al opa es un chatbot creado en el curso CapacitIA y el 'Observatório do opa' (transparencia/monitoreo). no hay evidencia textual de que la IA clasifique por temas, agrupe (clustering), priorice o sintetice el contenido de las propuestas del opa; la 'análise técnica' (documentación, viabilidad de ejecución, claridad, adecuación al área temática, no duplicación) se describe de forma reiterada y convergente como tarea de 'equipes técnicas' conducida a través de la plataforma. La única atribución hallada de IA que 'agrupa ideias semelhantes / estrutura propostas por eixo temático' corresponde a otro proceso (Diálogos pelo Piauí / revisión del PPA 2024-2027, talleres presenciales en 12 Territórios de Desenvolvimento), no al opa, y ni siquiera pudo confirmarse verbatim para Diálogos.</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1198,70 +1198,66 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Sistema de IA generativa basado en grandes modelos de lenguaje (LLM) descrito en la investigación: asistente que dialoga con la ciudadanía, hace preguntas y ayuda a redactar/estructurar la propuesta (ej. 'rede de ciclovias na zona leste de São Paulo') y a convertirla en un texto viable. Se citan sistemas como ChatGPT y DeepSeek como referentes tecnológicos. No es un producto desplegado verificado.</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>LLM / IA generativa (NLP)</t>
-        </is>
-      </c>
+          <t>No identificado por nombre. Capacidad de IA integrada en la plataforma Colab Gov (govtech Colab) sobre infraestructura AWS. En el OPA, la IA se asocia a la 'análise'/'processamento' de propuestas (agilización, -40% de tiempo), al filtrado de conexiones inseguras vía AWS CloudFront (seguridad/infraestructura), a un chatbot construido en un curso CapacitIA y a un 'Observatório do OPA' (panel de transparencia). La infraestructura AWS descrita es de cómputo/almacenamiento/seguridad (Amazon EC2, Amazon RDS, AWS CloudFront), no servicios de ML de contenido. No se especifica modelo, técnica (NLP, clustering, LLM) ni que la IA actúe sobre el contenido semántico de las propuestas del OPA. La plataforma Colab Gov.AI (lanzada en oct/2025 con AWS, basada en IA generativa/LangChain) ofrece funciones genéricas (generar flujos de servicio, etiquetar demandas en dashboards, asistir al ciudadano a redactar propuestas), pero ninguna de estas se atribuye específicamente al análisis de contenido de las propuestas del OPA Piauí.</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>Governo do Estado do Piauí - Secretaria do Planejamento (SEPLAN), con apoyo de la Secretaria de Relações Sociais (Seres). Socio tecnológico: GovTech Colab (plataforma Colab Gov); infraestructura: AWS (Amazon Web Services).</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Academia</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>activo (investigación en curso)</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>Co:Lab / Colaboratório de Desenvolvimento e Participação (EACH-USP) y GETIP - Grupo de Estudos em Tecnologia e Inovação na Gestão Pública; investigador José Carlos Vaz (titular da Cátedra CAPES Brasil-Alemanha na Universidade de Münster); coautora Fernanda Campagnucci.</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
           <t>MEDIA</t>
         </is>
       </c>
       <c r="W6" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>Confirmar uso de IA en el proceso → https://participemais.prefeitura.sp.gov.br/budgets · Confirmar estado de actividad → https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/ · Confirmar sistema_IA → https://scope.uni-muenster.de/wp-content/uploads/2025/01/PT-BR-Policy-Brief-AI_Jan2025.pdf · Confirmar tipo de proceso → https://colab.each.usp.br/blog/tag/ia-generativa/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar rol de la IA / uso de IA en el proceso (incertidumbre residual NO decisiva) → https://sia.pi.gov.br/projetos/opa/ · Confirmar sistema_IA / tipos de IA / uso de LLM generativa → https://tiinside.com.br/21/10/2025/em-parceria-com-a-aws-colab-lanca-ia-que-constroi-fluxos-de-governo-em-segundos/ · Confirmar cita textual (página renderizada) → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar etapas de uso de IA → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar estado de actividad → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar nivel de consolidación → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar convocante → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
+          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>BR-catedra-brasil-co-lab-usp-ia-generativa</t>
+          <t>BR-opa-piaui-presupuesto-participativo-digi</t>
         </is>
       </c>
     </row>
@@ -1273,26 +1269,26 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
+          <t>Plan Plurianual de la ciudad de Natal</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
+          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Participación Digital</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1311,43 +1307,47 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>apoyo</t>
+          <t>contenido</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Según el material de Colab, en la edición 2025-2026 / 2026-2027 la IA agilizó la fase de análisis y 'reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón en costos directos y 99,98% de disponibilidad del sistema incluso en picos de votación. Una fuente describe además que 'a inteligência artificial foi utilizada para filtrar conexões inseguras' mediante AWS CloudFront (seguridad/infraestructura). El uso adicional de IA en torno al opa es un chatbot creado en el curso CapacitIA y el 'Observatório do opa' (transparencia/monitoreo). no hay evidencia textual de que la IA clasifique por temas, agrupe (clustering), priorice o sintetice el contenido de las propuestas del opa; la 'análise técnica' (documentación, viabilidad de ejecución, claridad, adecuación al área temática, no duplicación) se describe de forma reiterada y convergente como tarea de 'equipes técnicas' conducida a través de la plataforma. La única atribución hallada de IA que 'agrupa ideias semelhantes / estrutura propostas por eixo temático' corresponde a otro proceso (Diálogos pelo Piauí / revisión del PPA 2024-2027, talleres presenciales en 12 Territórios de Desenvolvimento), no al opa, y ni siquiera pudo confirmarse verbatim para Diálogos.</t>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas.</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>No identificado por nombre. Capacidad de IA integrada en la plataforma Colab Gov (govtech Colab) sobre infraestructura AWS. En el OPA, la IA se asocia a la 'análise'/'processamento' de propuestas (agilización, -40% de tiempo), al filtrado de conexiones inseguras vía AWS CloudFront (seguridad/infraestructura), a un chatbot construido en un curso CapacitIA y a un 'Observatório do OPA' (panel de transparencia). La infraestructura AWS descrita es de cómputo/almacenamiento/seguridad (Amazon EC2, Amazon RDS, AWS CloudFront), no servicios de ML de contenido. No se especifica modelo, técnica (NLP, clustering, LLM) ni que la IA actúe sobre el contenido semántico de las propuestas del OPA. La plataforma Colab Gov.AI (lanzada en oct/2025 con AWS, basada en IA generativa/LangChain) ofrece funciones genéricas (generar flujos de servicio, etiquetar demandas en dashboards, asistir al ciudadano a redactar propuestas), pero ninguna de estas se atribuye específicamente al análisis de contenido de las propuestas del OPA Piauí.</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>Chatbot de IA</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>LLM; NLP</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Gobierno; Privado</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Nacional, Internacional</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>Governo do Estado do Piauí - Secretaria do Planejamento (SEPLAN), con apoyo de la Secretaria de Relações Sociais (Seres). Socio tecnológico: GovTech Colab (plataforma Colab Gov); infraestructura: AWS (Amazon Web Services).</t>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1367,25 +1367,25 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="n">
-        <v>7</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>Confirmar rol de la IA / uso de IA en el proceso (incertidumbre residual NO decisiva) → https://sia.pi.gov.br/projetos/opa/ · Confirmar sistema_IA / tipos de IA / uso de LLM generativa → https://tiinside.com.br/21/10/2025/em-parceria-com-a-aws-colab-lanca-ia-que-constroi-fluxos-de-governo-em-segundos/ · Confirmar cita textual (página renderizada) → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar etapas de uso de IA → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar estado de actividad → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar nivel de consolidación → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar convocante → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>BR-opa-piaui-presupuesto-participativo-digi</t>
+          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
+          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Traducción Política</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas.</t>
+          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Chatbot de IA</t>
+          <t>Modelo de IA desarrollado internamente para análisis de transcripciones y videos.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>LLM; NLP</t>
+          <t>Voz a Texto; LLM; NLP</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Gobierno; Privado</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Nacional, Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+          <t>Senado Federal de Brasil</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1498,22 +1498,22 @@
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="W8" s="3" t="n">
-        <v>0</v>
+      <c r="W8" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar nivel de consolidación → https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
+          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
         </is>
       </c>
     </row>
@@ -1525,22 +1525,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
+          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1568,80 +1568,80 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
+          <t>Clasificar y organizar el contenido de las propuestas ciudadanas enviadas a la consulta pública: la IA (Google Gemini) categoriza por tema las 6.368 propostas, las rankea por asunto y cantidad de apoyos y alimenta painéis de participación por distrito/subprefeitura, con el objetivo declarado de 'facilitar a divulgação das propostas à população'. Es procesamiento del contenido de los aportes (clasificar/agrupar/sintetizar), no apoyo meramente logístico.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Herramienta de análisis de datos construida en Python con la librería Pandas y la IA generativa Google Gemini. A partir de la base de propostas exportada del portal Participe Mais, clasifica las propuestas ciudadanas en categorías temáticas, las ordena por asunto y por cantidad de apoyos, y produce relatórios y painéis visuales: ranking de los temas más recurrentes y participación por distrito y subprefeitura. Se describe el uso de prompts/comandos a la IA (con 'ajustes necessários nos comandos para a Inteligência Artificial' como desafío reportado). No se publica el detalle técnico (modelo Gemini exacto, prompts), por lo que la implementación se conoce solo por descripción.</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>LLM generativa; NLP; Clasificación de texto</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Modelo de IA desarrollado internamente para análisis de transcripciones y videos.</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Voz a Texto; LLM; NLP</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Sociedad Civil; Gobierno</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>concluido</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>Proceso participativo (Programa de Metas / PPA / PAS): Prefeitura de São Paulo (Secretaria Municipal de Planejamento / Casa Civil / Coordenadoria de Governo Aberto, portal Participe Mais). Herramienta de IA: desarrollada por Carolina Borges, Agente de Governo Aberto de São Paulo (formación en Ciência da Computação y posgrado en Gestão e Controle Social de Políticas Públicas por la Escola de Contas do TCM-SP; experiencia profesional, académica y voluntaria), presentada en la oficina de la Escola do Parlamento da Câmara Municipal de São Paulo en parceria con el Programa Agentes de Governo Aberto. No se confirmó que la Prefeitura adoptara esta herramienta como su pipeline oficial de análisis del proceso.</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>Senado Federal de Brasil</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA-ALTA</t>
         </is>
       </c>
       <c r="W9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>Confirmar nivel de consolidación → https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>Confirmar cita textual (verificación carácter a carácter en los PDFs oficiales) → https://gestaourbana.prefeitura.sp.gov.br/wp-content/uploads/2025/10/Relatorio_Oficinas_Participativas.pdf · Confirmar confirmación de no-adopción (hipótesis remota de uso interno no publicado) → https://gestaourbana.prefeitura.sp.gov.br/planos-de-acao-das-subprefeituras/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
+          <t>BR-sao-paulo-programa-de-metas-participe-ma</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
+          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
+          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1696,32 +1696,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Clasificar y organizar el contenido de las propuestas ciudadanas enviadas a la consulta pública: la IA (Google Gemini) categoriza por tema las 6.368 propostas, las rankea por asunto y cantidad de apoyos y alimenta painéis de participación por distrito/subprefeitura, con el objetivo declarado de 'facilitar a divulgação das propostas à população'. Es procesamiento del contenido de los aportes (clasificar/agrupar/sintetizar), no apoyo meramente logístico.</t>
+          <t>Recolectar/recuperar y emparejar (matching) el contenido de las ideas legislativas ciudadanas con proyectos de ley: con IA se hace una búsqueda en el banco de ideias legislativas y se seleccionan las compatibles con la propuesta del senador, que luego pueden incorporarse al proyecto y citarse en su justificación. Transforma un archivo antes subutilizado en fuente para fundamentar justificaciones, inspirar redacciones y orientar ajustes de los proyectos parlamentarios.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Herramienta de análisis de datos construida en Python con la librería Pandas y la IA generativa Google Gemini. A partir de la base de propostas exportada del portal Participe Mais, clasifica las propuestas ciudadanas en categorías temáticas, las ordena por asunto y por cantidad de apoyos, y produce relatórios y painéis visuales: ranking de los temas más recurrentes y participación por distrito y subprefeitura. Se describe el uso de prompts/comandos a la IA (con 'ajustes necessários nos comandos para a Inteligência Artificial' como desafío reportado). No se publica el detalle técnico (modelo Gemini exacto, prompts), por lo que la implementación se conoce solo por descripción.</t>
+          <t>Herramienta de inteligencia artificial de búsqueda semántica desarrollada internamente por el servidor Alisson Bruno (Desafio de Inovação do Senado). Realiza una búsqueda sobre el banco de ideias legislativas del e-Cidadania para seleccionar las sugerencias ciudadanas temáticamente compatibles con un proyecto de ley en preparación por la Consultoria Legislativa. No se publica el detalle técnico del modelo (embeddings/semantic search), por lo que la familia exacta no está confirmada documentalmente.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>LLM generativa; NLP; Clasificación de texto</t>
+          <t>NLP; Búsqueda semántica</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil; Gobierno</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1736,67 +1736,67 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>concluido</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Proceso participativo (Programa de Metas / PPA / PAS): Prefeitura de São Paulo (Secretaria Municipal de Planejamento / Casa Civil / Coordenadoria de Governo Aberto, portal Participe Mais). Herramienta de IA: desarrollada por Carolina Borges, Agente de Governo Aberto de São Paulo (formación en Ciência da Computação y posgrado en Gestão e Controle Social de Políticas Públicas por la Escola de Contas do TCM-SP; experiencia profesional, académica y voluntaria), presentada en la oficina de la Escola do Parlamento da Câmara Municipal de São Paulo en parceria con el Programa Agentes de Governo Aberto. No se confirmó que la Prefeitura adoptara esta herramienta como su pipeline oficial de análisis del proceso.</t>
+          <t>Senado Federal do Brasil - Consultoria Legislativa en conjunto con el Programa e-Cidadania (Secretaria de Transparência / Coordenação do e-Cidadania). Herramienta desarrollada por el servidor Alisson Bruno (coordenador do e-Cidadania) en el marco del Desafio de Inovação do Senado.</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>NO (duplicado)</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>MEDIA-ALTA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="W10" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>Confirmar cita textual (verificación carácter a carácter en los PDFs oficiales) → https://gestaourbana.prefeitura.sp.gov.br/wp-content/uploads/2025/10/Relatorio_Oficinas_Participativas.pdf · Confirmar confirmación de no-adopción (hipótesis remota de uso interno no publicado) → https://gestaourbana.prefeitura.sp.gov.br/planos-de-acao-das-subprefeituras/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar tipos de IA / uso de LLM generativa → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial · Confirmar año de inicio (mes exacto / fecha de despliegue) → https://www12.senado.leg.br/radio/1/noticia/2026/01/15/ia-vai-aproximar-ideias-legislativas-do-e-cidadania-e-projetos-de-senadores · Confirmar nivel de consolidación (&gt;=2 ediciones) → https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/ · Confirmar cita textual (cita textual exacta verificada en HTML) → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>BR-sao-paulo-programa-de-metas-participe-ma</t>
+          <t>BR-e-cidadania-senado-ia-matching-de-ideas</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
+          <t>Cabildos 2016</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
+          <t>Análisis de los cabildos del proceso constitucional en 2016.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Recolectar/recuperar y emparejar (matching) el contenido de las ideas legislativas ciudadanas con proyectos de ley: con IA se hace una búsqueda en el banco de ideias legislativas y se seleccionan las compatibles con la propuesta del senador, que luego pueden incorporarse al proyecto y citarse en su justificación. Transforma un archivo antes subutilizado en fuente para fundamentar justificaciones, inspirar redacciones y orientar ajustes de los proyectos parlamentarios.</t>
+          <t>Clasificación y análisis de texto para identificar conceptos clave.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Herramienta de inteligencia artificial de búsqueda semántica desarrollada internamente por el servidor Alisson Bruno (Desafio de Inovação do Senado). Realiza una búsqueda sobre el banco de ideias legislativas del e-Cidadania para seleccionar las sugerencias ciudadanas temáticamente compatibles con un proyecto de ley en preparación por la Consultoria Legislativa. No se publica el detalle técnico del modelo (embeddings/semantic search), por lo que la familia exacta no está confirmada documentalmente.</t>
+          <t>Procesamiento de Lenguaje Natural</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>NLP; Búsqueda semántica</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1859,45 +1859,45 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Senado Federal do Brasil - Consultoria Legislativa en conjunto con el Programa e-Cidadania (Secretaria de Transparência / Coordenação do e-Cidadania). Herramienta desarrollada por el servidor Alisson Bruno (coordenador do e-Cidadania) en el marco del Desafio de Inovação do Senado.</t>
+          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>NO (duplicado)</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>4</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>Confirmar tipos de IA / uso de LLM generativa → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial · Confirmar año de inicio (mes exacto / fecha de despliegue) → https://www12.senado.leg.br/radio/1/noticia/2026/01/15/ia-vai-aproximar-ideias-legislativas-do-e-cidadania-e-projetos-de-senadores · Confirmar nivel de consolidación (&gt;=2 ediciones) → https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/ · Confirmar cita textual (cita textual exacta verificada en HTML) → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
+          <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>BR-e-cidadania-senado-ia-matching-de-ideas</t>
+          <t>CL-cabildos-2016</t>
         </is>
       </c>
     </row>
@@ -1909,17 +1909,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cabildos 2016</t>
+          <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Análisis de los cabildos del proceso constitucional en 2016.</t>
+          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la segegob y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de sistematizar los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (rnn) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/lda) sobre el contenido de diálogos y consultas individuales.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Clasificación y análisis de texto para identificar conceptos clave.</t>
+          <t>La IA procesa el contenido de los aportes ciudadanos (texto libre de diálogos y consultas individuales): clasifica las contribuciones mediante redes neuronales recurrentes (carpeta contributions_rnn) y mediante árboles de decisión/Random Forest (carpeta randomforest), sistematiza las emociones expresadas (Grouping Emotions.ipynb) y analiza los tópicos de necesidades personales y país (Analisis de Topicos - Necesidades.ipynb). El objetivo es sistematizar ~130.000 aportes ciudadanos para informar políticas públicas.</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de Lenguaje Natural</t>
+          <t>Conjunto de modelos de aprendizaje automático y NLP desarrollados por MinCiencia (código público en GitHub: MinCiencia/ECQQ) para sistematizar las contribuciones ciudadanas: clasificación de contribuciones con redes neuronales recurrentes (RNN) y con árboles de decisión (Random Forest), agrupamiento/sistematización de emociones y análisis de tópicos de necesidades (NLP/LDA). Visualización mediante dashboards (Apache Superset).</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP; Clasificación de texto; Modelado de tópicos (LDA); Redes neuronales recurrentes (RNN); Random Forest; Clasificación de emociones; Machine Learning</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
+          <t>Gobierno de Chile - proceso conjunto liderado por el Ministerio de Desarrollo Social y Familia; sistematización de los aportes con ciencia de datos/IA a cargo del Ministerio de Ciencia, Tecnología, Conocimiento e Innovación (MinCiencia). Participaron también Ministerio de Agricultura, SEGEGOB y División de Gobierno Digital.</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -2007,25 +2007,25 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>0</v>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar evidencia de actividad 2026 → https://github.com/MinCiencia/ECQQ/activity · Confirmar ano_cierre / informe final → https://www.chilequequeremos.cl · Confirmar rol de la IA (integración formal del output) → https://minciencia.gob.cl/noticias/</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/</t>
+          <t>https://github.com/MinCiencia/ECQQ</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>CL-cabildos-2016</t>
+          <t>CL-el-chile-que-queremos-ecqq-minciencia</t>
         </is>
       </c>
     </row>
@@ -2037,17 +2037,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la segegob y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de sistematizar los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (rnn) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/lda) sobre el contenido de diálogos y consultas individuales.</t>
+          <t>Uso de IA para analizar datos cualitativos en consulta ciudadana.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>La IA procesa el contenido de los aportes ciudadanos (texto libre de diálogos y consultas individuales): clasifica las contribuciones mediante redes neuronales recurrentes (carpeta contributions_rnn) y mediante árboles de decisión/Random Forest (carpeta randomforest), sistematiza las emociones expresadas (Grouping Emotions.ipynb) y analiza los tópicos de necesidades personales y país (Analisis de Topicos - Necesidades.ipynb). El objetivo es sistematizar ~130.000 aportes ciudadanos para informar políticas públicas.</t>
+          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Conjunto de modelos de aprendizaje automático y NLP desarrollados por MinCiencia (código público en GitHub: MinCiencia/ECQQ) para sistematizar las contribuciones ciudadanas: clasificación de contribuciones con redes neuronales recurrentes (RNN) y con árboles de decisión (Random Forest), agrupamiento/sistematización de emociones y análisis de tópicos de necesidades (NLP/LDA). Visualización mediante dashboards (Apache Superset).</t>
+          <t>No especificado, probablemente NLP.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>NLP; Clasificación de texto; Modelado de tópicos (LDA); Redes neuronales recurrentes (RNN); Random Forest; Clasificación de emociones; Machine Learning</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Gobierno de Chile - proceso conjunto liderado por el Ministerio de Desarrollo Social y Familia; sistematización de los aportes con ciencia de datos/IA a cargo del Ministerio de Ciencia, Tecnología, Conocimiento e Innovación (MinCiencia). Participaron también Ministerio de Agricultura, SEGEGOB y División de Gobierno Digital.</t>
+          <t>Secretaría de Gobierno Digital</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -2135,25 +2135,25 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>3</v>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>Confirmar evidencia de actividad 2026 → https://github.com/MinCiencia/ECQQ/activity · Confirmar ano_cierre / informe final → https://www.chilequequeremos.cl · Confirmar rol de la IA (integración formal del output) → https://minciencia.gob.cl/noticias/</t>
+          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/MinCiencia/ECQQ</t>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>CL-el-chile-que-queremos-ecqq-minciencia</t>
+          <t>CL-estrategia-de-gobierno-digital-informe-p</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+          <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Uso de IA para analizar datos cualitativos en consulta ciudadana.</t>
+          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>sociedad civil; empresa</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana.</t>
+          <t>Realización de entrevistas y codificación de respuestas.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>No especificado, probablemente NLP.</t>
+          <t>Apoyo a la interacción (chatbots, asistentes virtuales y otros), Razonamiento con estructuras de conocimiento, Reconocimiento.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Gobierno Digital</t>
+          <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
+          <t>https://estudiodialogos.cl/</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>CL-estrategia-de-gobierno-digital-informe-p</t>
+          <t>CL-estudio-dialogos-percepciones-de-futuro</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Estudio dIAlogos - Percepciones de Futuro</t>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena.</t>
+          <t>Jornadas de diálogo de la comunidad académica y otos stakeholders.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil; empresa</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Realización de entrevistas y codificación de respuestas.</t>
+          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Apoyo a la interacción (chatbots, asistentes virtuales y otros), Razonamiento con estructuras de conocimiento, Reconocimiento.</t>
+          <t>Procesamiento de Lenguaje Natural (NLP)</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Fundación Encuentros del Futuro y Merlín Research</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2399,17 +2399,17 @@
       </c>
       <c r="X15" s="4" t="inlineStr">
         <is>
-          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Adjuntar el enlace directo del informe/dashboard de la jornada; el de Tableau no es verificable públicamente. El equipo ejecutó el proceso, confirmar la técnica de análisis usada. · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://estudiodialogos.cl/</t>
+          <t>https://ipp.unab.cl/</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>CL-estudio-dialogos-percepciones-de-futuro</t>
+          <t>CL-jornada-de-escucha-lanzamiento-instituto</t>
         </is>
       </c>
     </row>
@@ -2421,22 +2421,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+          <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Jornadas de diálogo de la comunidad académica y otos stakeholders.</t>
+          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Mini públicos</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Planificación</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno nacional; universidad; sociedad civil</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones.</t>
+          <t>El moderador automatizado de la Stanford Online Deliberation Platform gestiona la logística de la deliberación: mantiene los tiempos y distribuye equitativamente los derechos/turnos de palabra, permite a los participantes formar colas de habla (speaking queues), aplica agendas con tiempos (timed agendas), controla mediante un sistema de señal automatizado a quién se le pide la siguiente intervención y un temporizador para cuánto tiempo tiene cada participante; además solicita argumentos a favor y en contra de las propuestas, incentiva a quienes no están hablando y consulta si todas las posturas fueron exploradas. Es decir, estructura la conversación (turnos, tiempos, equidad de participación), no analiza ni sintetiza automáticamente el contenido de los aportes en reportes. En paralelo, la IA del Centro de Microdatos de la U. de Chile se usó para seleccionar la muestra representativa (~400 de un universo de ~35.000 / 18 millones de habitantes). El análisis sustantivo de resultados se hizo mediante encuesta cuantitativa (clcert/Centro de Microdatos) y un informe cualitativo, no mediante síntesis automática por IA del contenido deliberado.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de Lenguaje Natural (NLP)</t>
+          <t>Stanford Online Deliberation Platform (plataforma de deliberación online del Center for Deliberative Democracy / Deliberative Democracy Lab de la Universidad de Stanford) con moderador automatizado (automated moderator) para facilitar la Encuesta Deliberativa online. Adicionalmente, el Centro de Microdatos de la U. de Chile empleó tecnología basada en IA para la selección de la muestra representativa.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización; Muestreo estadístico asistido por IA</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2489,27 +2489,27 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Senado de Chile (Comisión Desafíos del Futuro, Ciencia, Tecnología e Innovación) y Fundación Tribu, con la Universidad de Stanford (Center for Deliberative Democracy / Deliberative Democracy Lab), la Universidad de Chile (Centro de Microdatos), la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil e Identificación.</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2519,25 +2519,25 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>0</v>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
-          <t>Adjuntar el enlace directo del informe/dashboard de la jornada; el de Tableau no es verificable públicamente. El equipo ejecutó el proceso, confirmar la técnica de análisis usada. · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar rol de la IA (reporte de IA) → https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera · Confirmar estado de actividad / evidencia de actividad 2026 → https://www.lxs400.cl/noticias/ · Confirmar nivel de consolidación → https://www.senado.cl/comunicaciones/noticias/chile-delibera-lxs-400-un-fin-de-semana-de-democracia-deliberativa-online · Confirmar fuentes (verbatim directo) → https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/</t>
+          <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>CL-jornada-de-escucha-lanzamiento-instituto</t>
+          <t>CL-lxs-400-chile-delibera</t>
         </is>
       </c>
     </row>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LXS 400 - Chile Delibera</t>
+          <t>La voz de los nuevos votantes</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
+          <t>Análisis de Lenguaje Natural para los audios transcritos de encuesta realizada en persona.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Mini públicos</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Planificación</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -2577,22 +2577,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; universidad; sociedad civil</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>apoyo</t>
+          <t>contenido</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>El moderador automatizado de la Stanford Online Deliberation Platform gestiona la logística de la deliberación: mantiene los tiempos y distribuye equitativamente los derechos/turnos de palabra, permite a los participantes formar colas de habla (speaking queues), aplica agendas con tiempos (timed agendas), controla mediante un sistema de señal automatizado a quién se le pide la siguiente intervención y un temporizador para cuánto tiempo tiene cada participante; además solicita argumentos a favor y en contra de las propuestas, incentiva a quienes no están hablando y consulta si todas las posturas fueron exploradas. Es decir, estructura la conversación (turnos, tiempos, equidad de participación), no analiza ni sintetiza automáticamente el contenido de los aportes en reportes. En paralelo, la IA del Centro de Microdatos de la U. de Chile se usó para seleccionar la muestra representativa (~400 de un universo de ~35.000 / 18 millones de habitantes). El análisis sustantivo de resultados se hizo mediante encuesta cuantitativa (clcert/Centro de Microdatos) y un informe cualitativo, no mediante síntesis automática por IA del contenido deliberado.</t>
+          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Stanford Online Deliberation Platform (plataforma de deliberación online del Center for Deliberative Democracy / Deliberative Democracy Lab de la Universidad de Stanford) con moderador automatizado (automated moderator) para facilitar la Encuesta Deliberativa online. Adicionalmente, el Centro de Microdatos de la U. de Chile empleó tecnología basada en IA para la selección de la muestra representativa.</t>
+          <t>Procesamiento de Lenguaje Natural (NLP)</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización; Muestreo estadístico asistido por IA</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2617,27 +2617,27 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>Senado de Chile (Comisión Desafíos del Futuro, Ciencia, Tecnología e Innovación) y Fundación Tribu, con la Universidad de Stanford (Center for Deliberative Democracy / Deliberative Democracy Lab), la Universidad de Chile (Centro de Microdatos), la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil e Identificación.</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2647,25 +2647,25 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="W17" s="5" t="n">
-        <v>4</v>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>Confirmar rol de la IA (reporte de IA) → https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera · Confirmar estado de actividad / evidencia de actividad 2026 → https://www.lxs400.cl/noticias/ · Confirmar nivel de consolidación → https://www.senado.cl/comunicaciones/noticias/chile-delibera-lxs-400-un-fin-de-semana-de-democracia-deliberativa-online · Confirmar fuentes (verbatim directo) → https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
+          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>CL-lxs-400-chile-delibera</t>
+          <t>CL-la-voz-de-los-nuevos-votantes</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>La voz de los nuevos votantes</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de Lenguaje Natural para los audios transcritos de encuesta realizada en persona.</t>
+          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Secretaría de Participación Ciudadana</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>CL-la-voz-de-los-nuevos-votantes</t>
+          <t>CL-participacion-ciudadana-proceso-constitu</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional.</t>
+          <t>Iniciativa de diálogo y participación llevada a cabo por la uch y puc en el contexto de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases.</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Participación Ciudadana</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://www.tenemosquehablardechile.cl/</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>CL-participacion-ciudadana-proceso-constitu</t>
+          <t>CL-tenemos-que-hablar-de-chile</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogo y participación llevada a cabo por la uch y puc en el contexto de manifestaciones sociales.</t>
+          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas.</t>
+          <t>Análisis temático de las transcripciones de las mesas.</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3044,39 +3044,39 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tenemosquehablardechile.cl/</t>
+          <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>CL-tenemos-que-hablar-de-chile</t>
+          <t>CL-un-encuentro-para-la-equidad-de-genero-e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
+          <t>Chatico</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
+          <t>Agente virtual de Bogotá (Secretaría General) con módulos de participación además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa ; atiende por WhatsApp/Telegram/webchat.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -3084,17 +3084,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Análisis temático de las transcripciones de las mesas.</t>
+          <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo.</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3114,22 +3114,22 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de Lenguaje Natural (NLP)</t>
+          <t>Procesamiento de lenguaje natural (NLP)</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP; LLM</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Privado; Gobierno</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3139,17 +3139,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="W21" s="3" t="n">
@@ -3167,17 +3167,17 @@
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/</t>
+          <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>CL-un-encuentro-para-la-equidad-de-genero-e</t>
+          <t>CO-chatico</t>
         </is>
       </c>
     </row>
@@ -3189,22 +3189,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Chatico</t>
+          <t>ECHO – HáblameD Medellín</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Agente virtual de Bogotá (Secretaría General) con módulos de participación además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa ; atiende por WhatsApp/Telegram/webchat.</t>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Participación Digital</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>organización internacional; gobierno local</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo.</t>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural (NLP)</t>
+          <t>Procesamiento de Lenguaje Natural (NLP), Speech to Text</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>NLP; LLM</t>
+          <t>Voz a Texto; NLP; LLM</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3257,27 +3257,27 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Privado; Gobierno</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones</t>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>CO-chatico</t>
+          <t>CO-echo-hablamed-medellin</t>
         </is>
       </c>
     </row>
@@ -3317,22 +3317,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa del Laboratorio de Aceleración del PNUD Colombia que, en el contexto del paro nacional de 2021, usó la plataforma de IA Citibeats para monitorear y agrupar en tiempo real las opiniones y propuestas de la juventud colombiana sobre la coyuntura del país, con el fin de 'mejorar la deliberación pública'. La IA filtra y clasifica contenido de fuentes abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video). En paralelo, el PNUD y aliados como El Avispero generaron espacios presenciales para contrastar lo dicho en las conversaciones en línea; no hay evidencia de que Citibeats procesara los aportes de un proceso participativo formal convocado (consulta, cabildo o deliberación con inputs estructurados), sino principalmente social listening de medios digitales.</t>
+          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital</t>
+          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -3340,19 +3340,15 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>organización internacional</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
+          <t>sociedad civil</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3360,52 +3356,52 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats monitorea y da seguimiento en tiempo real a opiniones y propuestas, filtrando contenido relevante de fuentes de datos abiertas (Twitter, Facebook Public Pages, Instagram, foros, blogs, noticias y comentarios de video), clasificando las opiniones de los usuarios en categorías y extrayendo conocimiento y patrones de forma automática. En el proyecto del PNUD se analizaron alrededor de 2,1 millones de documentos para identificar los principales tópicos de interés de la juventud (las categorías predominantes giraron en torno a Paz y Justicia, Gobernanza e Inclusión Social) y comprender mejor las preocupaciones de los jóvenes para informar decisiones.</t>
+          <t>Resume las propuestas, organiza opiniones, procesa tendencias y construye consensos sobre el contenido de los aportes de la comunidad; convierte las opiniones en datos procesables y produce un resultado verificable (blockchain).</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats - plataforma comercial de analítica de datos / IA ética para comprensión social en tiempo real (NLP + Machine Learning).</t>
+          <t>Gaitana IA — plataforma/chatbot basada en el LLM DeepSeek adaptado a la cosmovisión Zenú; registro de decisiones en blockchain (Ethereum)</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>NLP; Machine Learning; Clasificación de texto; Análisis de sentimiento; Clustering temático</t>
+          <t>LLM; NLP</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>desconocido</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>PNUD Colombia - Laboratorio de Aceleración (Accelerator Lab), con la plataforma de IA Citibeats (empresa, España)</t>
+          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3415,25 +3411,25 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
         </is>
       </c>
       <c r="W23" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>Confirmar uso de IA en el proceso / rol de la IA → https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia · Confirmar estado de actividad / evidencia de actividad 2026 → https://www.undp.org/es/colombia/laboratorio-aceleracion · Confirmar nivel de consolidación → https://www.undp.org/es/colombia/blog/data-analytics-improve-public-deliberation-colombia · Confirmar ano_cierre → https://www.co.undp.org/content/colombia/es/home/Blog/2021/diciembre/data-analytics-to-improve-public-deliberation-in-colombia.html · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar el alcance del uso del LLM (DeepSeek) sobre los aportes y el estado de consolidación (¿puntual o recurrente?). · Confirmar rol de la IA → https://cerosetenta.uniandes.edu.co/ · Confirmar nivel de consolidación → https://gaitanaia.org/ · Confirmar tipo_organizacion → https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia</t>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>CO-citibeats-pnud-colombia-deliberacion-pub</t>
+          <t>CO-gaitana-ia-resguardo-zenu</t>
         </is>
       </c>
     </row>
@@ -3445,12 +3441,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial.</t>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3460,7 +3456,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -3473,7 +3469,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; gobierno local</t>
+          <t>universidad; empresa; sociedad civil</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3488,7 +3484,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t>Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos.</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3498,52 +3494,52 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de Lenguaje Natural (NLP), Speech to Text</t>
+          <t>Procesamiento de lenguaje natural (NLP)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; NLP; LLM</t>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Academia</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>cerrado</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>cerrado</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="W24" s="3" t="n">
@@ -3551,44 +3547,44 @@
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://tenemosquehablarcolombia.co/</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>CO-echo-hablamed-medellin</t>
+          <t>CO-tenemos-que-hablar-de-colombia</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
+          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (cen). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema xiscop y luego procesadas en el sistema GEMA-cen, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). xiscop (uci) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -3596,15 +3592,19 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Resume las propuestas, organiza opiniones, procesa tendencias y construye consensos sobre el contenido de los aportes de la comunidad; convierte las opiniones en datos procesables y produce un resultado verificable (blockchain).</t>
+          <t>Analizar el contenido de las propuestas ciudadanas recogidas en la consulta popular: GEMA-cen procesaba los expedientes con propuestas, recuperaba y comparaba su contenido, agrupaba las propuestas similares (idénticas o con redacción distinta que se referían al mismo criterio u opinión) y permitía determinar las 'propuestas típicas' por párrafo en cada categoría/Título establecida, sintetizando así el universo de aportes (de las propuestas procesadas se determinaron 5.237 propuestas típicas por Título). xiscop realizaba la entrada, clasificación por juristas y estadísticas oficiales. La función técnica de GEMA combina recuperación de información, agrupamiento/clasificación de documentos por temática, OCR y resumen automático extractivo.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3622,97 +3622,97 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA — plataforma/chatbot basada en el LLM DeepSeek adaptado a la cosmovisión Zenú; registro de decisiones en blockchain (Ethereum)</t>
+          <t>GEMA-CEN: adaptación para el Consejo Electoral Nacional del producto GEMA de Datys (empresa estatal cubana). Según la ficha oficial de Datys, GEMA es 'una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información'; es un 'sistema de procesamiento paralelo, distribuido y resistente a fallos' que clasifica archivos 'atendiendo a temáticas predefinidas por los usuarios', extrae texto de imágenes mediante OCR, recupera información por contenido y 'mediante técnicas modernas de recuperación de información' obtiene archivos similares, elimina resultados no relevantes y agrupa documentos comunes; además genera sumarios 'conformados por las oraciones con mayor importancia dentro del texto'. En la consulta, los especialistas usaban GEMA-CEN para el 'análisis inteligente de los expedientes', agrupar propuestas similares y determinar 'propuestas típicas'. El sistema XISCOP (UCI) realizaba la captura, revisión/clasificación por juristas y las estadísticas oficiales. No se publica el detalle técnico exacto (si el agrupamiento usa ML/embeddings semánticos o similitud clásica de recuperación de información).</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>LLM; NLP</t>
+          <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Privado; Academia; Gobierno</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>cerrado</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="W25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>Confirmar el alcance del uso del LLM (DeepSeek) sobre los aportes y el estado de consolidación (¿puntual o recurrente?). · Confirmar rol de la IA → https://cerosetenta.uniandes.edu.co/ · Confirmar nivel de consolidación → https://gaitanaia.org/ · Confirmar tipo_organizacion → https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar la técnica exacta de agrupamiento de GEMA-CEN (similitud/clustering) para precisar tipos de IA. · Confirmar tipos de IA / técnica exacta de agrupamiento → http://www.datys.cu/spa/site/product/15 · Confirmar cita textual (verificación carácter a carácter en HTML) → https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18 · Confirmar rol específico de XISCOP vs GEMA-CEN en el uso de IA → https://www.uci.cu/ · Confirmar uso de LLM generativa → http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
+          <t>http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>CO-gaitana-ia-resguardo-zenu</t>
+          <t>CU-consulta-popular-codigo-de-las-familias</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>universidad; empresa; sociedad civil</t>
+          <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos.</t>
+          <t>Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3750,22 +3750,22 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural (NLP)</t>
+          <t>Modelos de lenguaje de gran escala (LLMs)</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="W26" s="3" t="n">
@@ -3803,44 +3803,44 @@
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
-          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/</t>
+          <t>https://ia.gobiernoabierto.ec/</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>CO-tenemos-que-hablar-de-colombia</t>
+          <t>EC-paga-ia</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (cen). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema xiscop y luego procesadas en el sistema GEMA-cen, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). xiscop (uci) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>organización internacional; sociedad civil</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Analizar el contenido de las propuestas ciudadanas recogidas en la consulta popular: GEMA-cen procesaba los expedientes con propuestas, recuperaba y comparaba su contenido, agrupaba las propuestas similares (idénticas o con redacción distinta que se referían al mismo criterio u opinión) y permitía determinar las 'propuestas típicas' por párrafo en cada categoría/Título establecida, sintetizando así el universo de aportes (de las propuestas procesadas se determinaron 5.237 propuestas típicas por Título). xiscop realizaba la entrada, clasificación por juristas y estadísticas oficiales. La función técnica de GEMA combina recuperación de información, agrupamiento/clasificación de documentos por temática, OCR y resumen automático extractivo.</t>
+          <t>Facilitar diálogos anónimos en tiempo real, agrupar opiniones y permitir votaciones sobre las opiniones de otros participantes.</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>GEMA-CEN: adaptación para el Consejo Electoral Nacional del producto GEMA de Datys (empresa estatal cubana). Según la ficha oficial de Datys, GEMA es 'una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información'; es un 'sistema de procesamiento paralelo, distribuido y resistente a fallos' que clasifica archivos 'atendiendo a temáticas predefinidas por los usuarios', extrae texto de imágenes mediante OCR, recupera información por contenido y 'mediante técnicas modernas de recuperación de información' obtiene archivos similares, elimina resultados no relevantes y agrupa documentos comunes; además genera sumarios 'conformados por las oraciones con mayor importancia dentro del texto'. En la consulta, los especialistas usaban GEMA-CEN para el 'análisis inteligente de los expedientes', agrupar propuestas similares y determinar 'propuestas típicas'. El sistema XISCOP (UCI) realizaba la captura, revisión/clasificación por juristas y las estadísticas oficiales. No se publica el detalle técnico exacto (si el agrupamiento usa ML/embeddings semánticos o similitud clásica de recuperación de información).</t>
+          <t>Remesh (plataforma de diálogo masivo con IA, Remesh Inc.), con apoyo de la DPPA Innovation Cell.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -3893,27 +3893,27 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Privado; Academia; Gobierno</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3923,42 +3923,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="W27" s="5" t="n">
-        <v>4</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X27" s="4" t="inlineStr">
         <is>
-          <t>Confirmar la técnica exacta de agrupamiento de GEMA-CEN (similitud/clustering) para precisar tipos de IA. · Confirmar tipos de IA / técnica exacta de agrupamiento → http://www.datys.cu/spa/site/product/15 · Confirmar cita textual (verificación carácter a carácter en HTML) → https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18 · Confirmar rol específico de XISCOP vs GEMA-CEN en el uso de IA → https://www.uci.cu/ · Confirmar uso de LLM generativa → http://www.datys.cu/spa/site/product/15</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15</t>
+          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>CU-consulta-popular-codigo-de-las-familias</t>
+          <t>GT-guatemala-joven-conversa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAGA IA </t>
+          <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios.</t>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -3976,17 +3976,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; sociedad civil</t>
+          <t>organización internacional; universidad</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto.</t>
+          <t>Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4006,27 +4006,27 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Modelos de lenguaje de gran escala (LLMs)</t>
+          <t>Procesamiento de lenguaje natural para clasificar propuestas.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Gobierno; Academia</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional, Nacional</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -4064,39 +4064,39 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://ia.gobiernoabierto.ec/</t>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>EC-paga-ia</t>
+          <t>HN-redpublica-iverify</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (copladeg), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e iplaneg. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -4109,12 +4109,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; sociedad civil</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Facilitar diálogos anónimos en tiempo real, agrupar opiniones y permitir votaciones sobre las opiniones de otros participantes.</t>
+          <t>Procesar y organizar las miles de ideas y propuestas ciudadanas recibidas en talleres/consultas; identificar las prioridades más mencionadas por la ciudadanía; entender las necesidades de cada región; transformar el diálogo social en datos claros para la toma de decisiones que estructuran los ejes del programa. (La asistente 'Esperanza' cumple una función adicional de consulta/atención sobre el programa ya elaborado.).</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4134,27 +4134,27 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Remesh (plataforma de diálogo masivo con IA, Remesh Inc.), con apoyo de la DPPA Innovation Cell.</t>
+          <t>Herramientas de inteligencia artificial (no especificadas públicamente por nombre/proveedor) empleadas para procesar y organizar los aportes ciudadanos e identificar prioridades. Por separado, asistente virtual conversacional 'Esperanza' para consultar el Programa de Gobierno ya publicado. Ninguna fuente nombra el modelo/empresa concreto usado para el análisis de los 26k aportes.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
+          <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -4179,52 +4179,52 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>0</v>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="W29" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="X29" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar sistema_IA → https://guanajuatointeligente.com/como-hicimos-el-programa/ · Confirmar uso de LLM generativa → https://iplaneg.guanajuato.gob.mx/programagobierno24-30/ · Confirmar tipos de IA → https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf · Confirmar ano_cierre → https://boletines.guanajuato.gob.mx/2025/02/13/guanajuato-hara-historia-con-el-primer-programa-de-gobierno-realizado-con-ia/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47</t>
+          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>GT-guatemala-joven-conversa</t>
+          <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
+          <t>Presupuesto CRECES</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Presupuestos Participativos</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; universidad</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional.</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural para clasificar propuestas.</t>
+          <t>Chatbot a través de WhatsApp</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>Chatbot - Inespecífico</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -4277,17 +4277,17 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Gobierno; Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>Internacional, Nacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+          <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4307,52 +4307,52 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v>0</v>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="X30" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar evidencia de actividad 2026 → https://presupuestocreces.hermosillo.gob.mx/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>HN-redpublica-iverify</t>
+          <t>MX-presupuesto-creces</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (copladeg), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e iplaneg. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
+          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el contenido de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento punteral (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. importante: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4360,17 +4360,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Procesar y organizar las miles de ideas y propuestas ciudadanas recibidas en talleres/consultas; identificar las prioridades más mencionadas por la ciudadanía; entender las necesidades de cada región; transformar el diálogo social en datos claros para la toma de decisiones que estructuran los ejes del programa. (La asistente 'Esperanza' cumple una función adicional de consulta/atención sobre el programa ya elaborado.).</t>
+          <t>Según las fuentes, la IA permite acceder de forma fácil y expedita a más de 175.000 propuestas ciudadanas y 'recoge en un solo clic los consensos nacionales y regionales/provinciales', constituyendo una base de datos navegable de proyectos. Es decir, la IA agrega, organiza y sintetiza el contenido de los aportes ciudadanos del Pacto del Bicentenario para hacerlos consultables por tema y por territorio. No se especifica el método técnico (clasificación/clustering/búsqueda semántica/generación).</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4390,14 +4390,10 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Herramientas de inteligencia artificial (no especificadas públicamente por nombre/proveedor) empleadas para procesar y organizar los aportes ciudadanos e identificar prioridades. Por separado, asistente virtual conversacional 'Esperanza' para consultar el Programa de Gobierno ya publicado. Ninguna fuente nombra el modelo/empresa concreto usado para el análisis de los 26k aportes.</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Otros(no especificado)</t>
-        </is>
-      </c>
+          <t>Mansa Idea (www.mansaidea.com): plataforma digital descrita por sus impulsores como 'basada en inteligencia artificial' que organiza, agrega y hace navegables las propuestas del Pacto del Bicentenario, presentando consensos nacionales y provinciales por tema. La tecnología de IA concreta (familia de modelos, si usa clustering/NLP/embeddings o LLM) NO está identificada explícitamente en las fuentes públicas halladas.</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
@@ -4405,7 +4401,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4420,12 +4416,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>desconocido</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
+          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -4435,52 +4431,52 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA</t>
         </is>
       </c>
       <c r="W31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X31" s="4" t="inlineStr">
         <is>
-          <t>Confirmar sistema_IA → https://guanajuatointeligente.com/como-hicimos-el-programa/ · Confirmar uso de LLM generativa → https://iplaneg.guanajuato.gob.mx/programagobierno24-30/ · Confirmar tipos de IA → https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf · Confirmar ano_cierre → https://boletines.guanajuato.gob.mx/2025/02/13/guanajuato-hara-historia-con-el-primer-programa-de-gobierno-realizado-con-ia/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar sistema_IA / tipos de IA / uso de LLM generativa / funcion_IA (método técnico) → https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa. · Confirmar estado de actividad / evidencia de actividad 2026 → https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'. · Confirmar nivel de consolidación → https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias. · Confirmar convocante (atribución) → https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/ · Confirmar naturaleza jurídica Fundación Panamá Participa (empresa vs ONG) (abrir la fuente)</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/</t>
+          <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>MX-guanajuato-inteligente-2024-2030</t>
+          <t>PA-mansa-idea-pacto-del-bicentenario</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto CRECES</t>
+          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos.</t>
+          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4493,7 +4489,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>otra institución pública</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -4508,7 +4504,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional.</t>
+          <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4518,12 +4514,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Chatbot a través de WhatsApp</t>
+          <t>Procesamiento del Lenguaje Natural (PLN) / Comprensión del Lenguaje Natural (NLU)</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Chatbot - Inespecífico</t>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4538,22 +4534,22 @@
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Ayundamiento de Hermosilla</t>
+          <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4563,42 +4559,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="W32" s="5" t="n">
-        <v>1</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X32" s="4" t="inlineStr">
         <is>
-          <t>Confirmar evidencia de actividad 2026 → https://presupuestocreces.hermosillo.gob.mx/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>MX-presupuesto-creces</t>
+          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el contenido de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento punteral (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. importante: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (idb). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo no viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking depende del plan contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras de investigacion (&gt;=14 busquedas/fetches) no se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el contenido de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, excluido del criterio).</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4608,11 +4604,11 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -4621,73 +4617,77 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil; gobierno nacional</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>apoyo</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Capacidad de la plataforma Go Vocal: el modulo 'Sensemaking'/'AI Analysis' analiza y resume automaticamente grandes conjuntos de aportes, etiqueta automaticamente, detecta sentimiento e idioma, detecta patrones entre grupos y descubre vinculos estadisticamente significativos entre demografia, experiencia y prioridades, reduciendo el tiempo de analisis (&gt;=50% segun Go Vocal). Esa capacidad esta sujeta al plan contratado (Premium para auto-insights). no confirmado que la instancia de Trinidad la active ni use sobre el contenido de los aportes del NDTS. La unica IA confirmada en el ecosistema tt es AskNDTS, un chatbot conversacional que responde preguntas sobre el NDTS (FAQ informativo, no procesa aportes).</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma Go Vocal (antes CitizenLab), software de participacion ciudadana que ofrece de forma NATIVA pero NO por defecto un modulo de IA/NLP llamado 'Sensemaking'/'AI Analysis' (analisis y resumen automatico de aportes ciudadanos, deteccion de patrones, etiquetado automatico, deteccion de sentimiento, vinculos estadisticos). Segun el Go Vocal Support Base, el acceso a esa funcion DEPENDE DEL PLAN (Advanced Sensemaking con auto-insights = plan Premium), por lo que su disponibilidad en una instancia concreta no es automatica. En la instancia de Trinidad (engage.gov.tt) NO se confirma activacion ni uso de dicho modulo de IA sobre el contenido de los aportes del NDTS. Aparte, AskNDTS es un chatbot de IA conversacional (FAQ sobre el NDTS), pero no procesa aportes de un proceso participativo (excluido).</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot - Inespecífico</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Según las fuentes, la IA permite acceder de forma fácil y expedita a más de 175.000 propuestas ciudadanas y 'recoge en un solo clic los consensos nacionales y regionales/provinciales', constituyendo una base de datos navegable de proyectos. Es decir, la IA agrega, organiza y sintetiza el contenido de los aportes ciudadanos del Pacto del Bicentenario para hacerlos consultables por tema y por territorio. No se especifica el método técnico (clasificación/clustering/búsqueda semántica/generación).</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea (www.mansaidea.com): plataforma digital descrita por sus impulsores como 'basada en inteligencia artificial' que organiza, agrega y hace navegables las propuestas del Pacto del Bicentenario, presentando consensos nacionales y provinciales por tema. La tecnología de IA concreta (familia de modelos, si usa clustering/NLP/embeddings o LLM) NO está identificada explícitamente en las fuentes públicas halladas.</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>desconocido</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="W33" s="5" t="n">
@@ -4695,39 +4695,39 @@
       </c>
       <c r="X33" s="4" t="inlineStr">
         <is>
-          <t>Confirmar sistema_IA / tipos de IA / uso de LLM generativa / funcion_IA (método técnico) → https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa. · Confirmar estado de actividad / evidencia de actividad 2026 → https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'. · Confirmar nivel de consolidación → https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias. · Confirmar convocante (atribución) → https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/ · Confirmar naturaleza jurídica Fundación Panamá Participa (empresa vs ONG) (abrir la fuente)</t>
+          <t>Confirmar si el módulo de IA de Go Vocal (Sensemaking) se activó sobre los aportes, o si el uso de IA es solo el chatbot informativo AskNDTS. Revisar el panel de engage.gov.tt o consultar al Ministerio (MPAAI). · Confirmar uso de IA en el proceso / rol de la IA (metodologia del Actionable Feedback) → https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan · Confirmar uso de IA en el proceso (plan contratado por TT) → https://www.govocal.com/plans · Confirmar uso de LLM generativa → https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool · Confirmar nivel de consolidación → https://engage.gov.tt/projects · Confirmar ano_cierre / estado de actividad → https://engage.gov.tt/pages/information · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/</t>
+          <t>https://support.govocal.com/en/articles/8316692-ai-analysis</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>PA-mansa-idea-pacto-del-bicentenario</t>
+          <t>TT-engagett-plataforma-go-vocal</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>UY</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
+          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
+          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>otra institución pública</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
+          <t>Mapea las respuestas de los participantes, agrupa opiniones en clusters e identifica automáticamente statements de consenso y de división ('bridges') sobre una consulta multi-tema.</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento del Lenguaje Natural (PLN) / Comprensión del Lenguaje Natural (NLU)</t>
+          <t>Pol.is — clustering de opiniones (reducción de dimensionalidad / agrupamiento no supervisado sobre votos de acuerdo/desacuerdo a statements ciudadanos)</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>Clustering; ML - Inespecífico</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>Consejo Nacional de Educación del Perú</t>
+          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4815,286 +4815,30 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="n">
-        <v>0</v>
+          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="X34" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar criterio_temporal → https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/ · Confirmar nivel de consolidación → https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional</t>
+          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TT</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (idb). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo no viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking depende del plan contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras de investigacion (&gt;=14 busquedas/fetches) no se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el contenido de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, excluido del criterio).</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>gobierno nacional</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>apoyo</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Capacidad de la plataforma Go Vocal: el modulo 'Sensemaking'/'AI Analysis' analiza y resume automaticamente grandes conjuntos de aportes, etiqueta automaticamente, detecta sentimiento e idioma, detecta patrones entre grupos y descubre vinculos estadisticamente significativos entre demografia, experiencia y prioridades, reduciendo el tiempo de analisis (&gt;=50% segun Go Vocal). Esa capacidad esta sujeta al plan contratado (Premium para auto-insights). no confirmado que la instancia de Trinidad la active ni use sobre el contenido de los aportes del NDTS. La unica IA confirmada en el ecosistema tt es AskNDTS, un chatbot conversacional que responde preguntas sobre el NDTS (FAQ informativo, no procesa aportes).</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>Plataforma Go Vocal (antes CitizenLab), software de participacion ciudadana que ofrece de forma NATIVA pero NO por defecto un modulo de IA/NLP llamado 'Sensemaking'/'AI Analysis' (analisis y resumen automatico de aportes ciudadanos, deteccion de patrones, etiquetado automatico, deteccion de sentimiento, vinculos estadisticos). Segun el Go Vocal Support Base, el acceso a esa funcion DEPENDE DEL PLAN (Advanced Sensemaking con auto-insights = plan Premium), por lo que su disponibilidad en una instancia concreta no es automatica. En la instancia de Trinidad (engage.gov.tt) NO se confirma activacion ni uso de dicho modulo de IA sobre el contenido de los aportes del NDTS. Aparte, AskNDTS es un chatbot de IA conversacional (FAQ sobre el NDTS), pero no procesa aportes de un proceso participativo (excluido).</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>Chatbot - Inespecífico</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="W35" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="X35" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar si el módulo de IA de Go Vocal (Sensemaking) se activó sobre los aportes, o si el uso de IA es solo el chatbot informativo AskNDTS. Revisar el panel de engage.gov.tt o consultar al Ministerio (MPAAI). · Confirmar uso de IA en el proceso / rol de la IA (metodologia del Actionable Feedback) → https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan · Confirmar uso de IA en el proceso (plan contratado por TT) → https://www.govocal.com/plans · Confirmar uso de LLM generativa → https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool · Confirmar nivel de consolidación → https://engage.gov.tt/projects · Confirmar ano_cierre / estado de actividad → https://engage.gov.tt/pages/information · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t>https://support.govocal.com/en/articles/8316692-ai-analysis</t>
-        </is>
-      </c>
-      <c r="Z35" s="2" t="inlineStr">
-        <is>
-          <t>TT-engagett-plataforma-go-vocal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>UY</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Uso único</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>universidad</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Mapea las respuestas de los participantes, agrupa opiniones en clusters e identifica automáticamente statements de consenso y de división ('bridges') sobre una consulta multi-tema.</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>Pol.is — clustering de opiniones (reducción de dimensionalidad / agrupamiento no supervisado sobre votos de acuerdo/desacuerdo a statements ciudadanos)</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Clustering; ML - Inespecífico</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>cerrado</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
-        </is>
-      </c>
-      <c r="W36" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X36" s="4" t="inlineStr">
-        <is>
-          <t>Confirmar criterio_temporal → https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/ · Confirmar nivel de consolidación → https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
-        <is>
-          <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr">
-        <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z36"/>
+  <autoFilter ref="A1:Z34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5105,7 +4849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5339,22 +5083,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>De ciudadano a senador: la inteligencia artificial y la reinvención de la elaboración legislativa en Brasil”</t>
+          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar.</t>
+          <t>Investigación académica en curso ('pesquisas em andamento') sobre IA generativa para participación: sin despliegue con ciudadanos ni proceso propio . Estudio sin despliegue.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://rebootdemocracy.ai/blog/ai-lawmaking-brazil-senate</t>
+          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-de-ciudadano-a-senador-la-inteligencia-a</t>
+          <t>BR-catedra-brasil-co-lab-usp-ia-generativa</t>
         </is>
       </c>
     </row>
@@ -5366,22 +5110,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fala.BR</t>
+          <t>De ciudadano a senador: la inteligencia artificial y la reinvención de la elaboración legislativa en Brasil”</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>Propuesta, pero no hay datos sobre que se vaya a ejecutar.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://falabr.cgu.gov.br/</t>
+          <t>https://rebootdemocracy.ai/blog/ai-lawmaking-brazil-senate</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-fala-br</t>
+          <t>BR-EXC-de-ciudadano-a-senador-la-inteligencia-a</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5137,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Jaque</t>
+          <t>Fala.BR</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -5403,12 +5147,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://falabr.cgu.gov.br/</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-jaque</t>
+          <t>BR-EXC-fala-br</t>
         </is>
       </c>
     </row>
@@ -5420,22 +5164,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mudamos</t>
+          <t>Jaque</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://www.mudamos.org/</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-mudamos</t>
+          <t>BR-EXC-jaque</t>
         </is>
       </c>
     </row>
@@ -5447,22 +5191,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ParticipACT Brasil</t>
+          <t>Mudamos</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de reporte urbano (app para reportar problemas): no es un proceso participativo.</t>
+          <t>No se identifica uso de IA.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://site.participact.com.br/</t>
+          <t>https://www.mudamos.org/</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>BR-participact-brasil</t>
+          <t>BR-EXC-mudamos</t>
         </is>
       </c>
     </row>
@@ -5474,22 +5218,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Participa+ Brasil</t>
+          <t>ParticipACT Brasil</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>No se identifica uso de IA.</t>
+          <t>Civic tech de reporte urbano (app para reportar problemas): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://www.gov.br/participamaisbrasil/pagina-inicial</t>
+          <t>https://site.participact.com.br/</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-participa-brasil</t>
+          <t>BR-participact-brasil</t>
         </is>
       </c>
     </row>
@@ -5501,22 +5245,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Participe+ (ParticipeMais) - app estudiantil UnB-MDS de IA sobre contenidos de Brasil Participativo</t>
+          <t>Participa+ Brasil</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Aunque tecnicamente la IA si procesa el contenido de los aportes (agrupa por temas via hdbscan y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple una condicion necesaria del criterio de inclusion ('si solo si caso distinto, desplegado oficialmente'): no hay despliegue oficial ni adopcion por la Secretaria Nacional de Participacao Social; es un ejercicio de la disciplina mds (Ingenieria de Software, UnB, org unb-mds, semestre 2025.1) con release v1.0.0 del 09/07/2025 y unico 'deploy' un sitio de documentacion en GitHub Pages, patron tipico de proyecto academico de un semestre, sin usuarios reales ni operacion gubernamental. substancial solapamiento con el caso ya contado br-brasil-participativo-clustering-semantic: opera sobre la misma plataforma Brasil Participativo (raspa sus propuestas), pertenece al mismo ecosistema UnB y replica la misma idea de clustering/clasificacion tematica de propuestas, pero como artefacto estudiantil paralelo, no como el pipeline oficial de lappis/brisa. Se distingue del municipal 'Participe+' de la Prefeitura de Sao Paulo (participemais.prefeitura.sp.gov.br), que es otro caso no relacionado. Por incumplir 'desplegado oficialmente' (ejercicio estudiantil sin adopcion) y por solapar con el caso federal ya contado, la decision es no. La duda central (¿va mas alla de resumir?) se resuelve a favor de 'si procesa contenido', pero eso no basta para entrar sin despliegue oficial.</t>
+          <t>No se identifica uso de IA.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/unb-mds/ParticipeMais</t>
+          <t>https://www.gov.br/participamaisbrasil/pagina-inicial</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>BR-participe-mais-unb-mds</t>
+          <t>BR-EXC-participa-brasil</t>
         </is>
       </c>
     </row>
@@ -5528,22 +5272,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Projeto Lumina - análise de sentimentos das propostas de Brasil Participativo (projeto estudantil UnB-MDS)</t>
+          <t>Participe+ (ParticipeMais) - app estudiantil UnB-MDS de IA sobre contenidos de Brasil Participativo</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Aunque la IA sí actúa sobre el contenido de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo,, falla el requisito de despliegue oficial: Projeto Lumina es un ejercicio académico de la disciplina 'Métodos de Desenvolvimento de Software' del curso de Engenharia de Software de la UnB (semestre 2024-2), no un sistema adoptado ni operado por el gobierno. La señal del candidato conflaciona 'mds' (el nombre de la disciplina y de la org GitHub 'unb-mds') con 'Ministério do Desenvolvimento Social': no se halló evidencia de asociación oficial con ese Ministerio ni con la Secretaria Nacional de Participação Social, ni de integración en producción. El repositorio sigue el patrón idéntico de decenas de proyectos estudiantiles de 'unb-mds' (DFemObras, SuaGradeUnB, LicitaBSB, forUnB, GovInsights, etc.), tiene 3 stars/4 forks y su 'Versão Final' (feb-2025) marca el fin del curso. Sobre el doble conteo: no es un componente ni duplicado técnico de la ficha ya contada 'Brasil Participativo - clustering semántico' (esa es el pipeline oficial BERTopic+LLM de lappis/brisa con mentoría de la Secretaria de Participação Social); Lumina es un artefacto distinto (webapp estudiantil que consume datos de bp), pero igualmente inelegible por ser académico sin adopción. Conclusión: no por ejercicio académico sin despliegue oficial.</t>
+          <t>Aunque tecnicamente la IA si procesa el contenido de los aportes (agrupa por temas via hdbscan y clasifica en eixos por similitud semantica, ademas de resumir con LLM), el candidato incumple una condicion necesaria del criterio de inclusion ('si solo si caso distinto, desplegado oficialmente'): no hay despliegue oficial ni adopcion por la Secretaria Nacional de Participacao Social; es un ejercicio de la disciplina mds (Ingenieria de Software, UnB, org unb-mds, semestre 2025.1) con release v1.0.0 del 09/07/2025 y unico 'deploy' un sitio de documentacion en GitHub Pages, patron tipico de proyecto academico de un semestre, sin usuarios reales ni operacion gubernamental. substancial solapamiento con el caso ya contado br-brasil-participativo-clustering-semantic: opera sobre la misma plataforma Brasil Participativo (raspa sus propuestas), pertenece al mismo ecosistema UnB y replica la misma idea de clustering/clasificacion tematica de propuestas, pero como artefacto estudiantil paralelo, no como el pipeline oficial de lappis/brisa. Se distingue del municipal 'Participe+' de la Prefeitura de Sao Paulo (participemais.prefeitura.sp.gov.br), que es otro caso no relacionado. Por incumplir 'desplegado oficialmente' (ejercicio estudiantil sin adopcion) y por solapar con el caso federal ya contado, la decision es no. La duda central (¿va mas alla de resumir?) se resuelve a favor de 'si procesa contenido', pero eso no basta para entrar sin despliegue oficial.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/unb-mds/2024-2-Lumina</t>
+          <t>https://github.com/unb-mds/ParticipeMais</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>BR-projeto-lumina-unb-mds</t>
+          <t>BR-participe-mais-unb-mds</t>
         </is>
       </c>
     </row>
@@ -5555,22 +5299,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Querido Diário</t>
+          <t>Projeto Lumina - análise de sentimentos das propostas de Brasil Participativo (projeto estudantil UnB-MDS)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Aunque la IA sí actúa sobre el contenido de aportes ciudadanos (análisis de sentimiento positivo/negativo/neutro de las propuestas y comentarios de Brasil Participativo,, falla el requisito de despliegue oficial: Projeto Lumina es un ejercicio académico de la disciplina 'Métodos de Desenvolvimento de Software' del curso de Engenharia de Software de la UnB (semestre 2024-2), no un sistema adoptado ni operado por el gobierno. La señal del candidato conflaciona 'mds' (el nombre de la disciplina y de la org GitHub 'unb-mds') con 'Ministério do Desenvolvimento Social': no se halló evidencia de asociación oficial con ese Ministerio ni con la Secretaria Nacional de Participação Social, ni de integración en producción. El repositorio sigue el patrón idéntico de decenas de proyectos estudiantiles de 'unb-mds' (DFemObras, SuaGradeUnB, LicitaBSB, forUnB, GovInsights, etc.), tiene 3 stars/4 forks y su 'Versão Final' (feb-2025) marca el fin del curso. Sobre el doble conteo: no es un componente ni duplicado técnico de la ficha ya contada 'Brasil Participativo - clustering semántico' (esa es el pipeline oficial BERTopic+LLM de lappis/brisa con mentoría de la Secretaria de Participação Social); Lumina es un artefacto distinto (webapp estudiantil que consume datos de bp), pero igualmente inelegible por ser académico sin adopción. Conclusión: no por ejercicio académico sin despliegue oficial.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://ok.org.br/projetos/querido-diario/</t>
+          <t>https://github.com/unb-mds/2024-2-Lumina</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-querido-diario</t>
+          <t>BR-projeto-lumina-unb-mds</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5326,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Robô ALICE (CGU)</t>
+          <t>Querido Diário</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5592,12 +5336,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://oecd-opsi.org/innovations/robot-alice-bid-contract-and-notice-analyser/</t>
+          <t>https://ok.org.br/projetos/querido-diario/</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-robo-alice-cgu</t>
+          <t>BR-EXC-querido-diario</t>
         </is>
       </c>
     </row>
@@ -5609,22 +5353,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Serenata.ai</t>
+          <t>Robô ALICE (CGU)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>No es participación Ciudadana.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://serenata.ai/</t>
+          <t>https://oecd-opsi.org/innovations/robot-alice-bid-contract-and-notice-analyser/</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-serenata-ai</t>
+          <t>BR-EXC-robo-alice-cgu</t>
         </is>
       </c>
     </row>
@@ -5636,49 +5380,49 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tira-Dúvidas TSE</t>
+          <t>Serenata.ai</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>No es participación Ciudadana.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://www.tse.jus.br/comunicacao/noticias/2022/Setembro/tira-duvidas-do-tse-no-whatsapp-ganha-ferramenta-inedita-de-checagem-de-fatos-para-as-eleicoes-2022-402542</t>
+          <t>https://serenata.ai/</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>BR-EXC-tira-duvidas-tse</t>
+          <t>BR-EXC-serenata-ai</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Caminar</t>
+          <t>Tira-Dúvidas TSE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>De acuerdo a la descripción, solo permitiría a los ciudadanos consultar.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://parlamericas.org/uploads/documents/Presentation-OPNStaffMeeting-ProyectoCAMINARChile_MiguelLanderos-sp.pdf</t>
+          <t>https://www.tse.jus.br/comunicacao/noticias/2022/Setembro/tira-duvidas-do-tse-no-whatsapp-ganha-ferramenta-inedita-de-checagem-de-fatos-para-as-eleicoes-2022-402542</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>CL-EXC-caminar</t>
+          <t>BR-EXC-tira-duvidas-tse</t>
         </is>
       </c>
     </row>
@@ -5690,22 +5434,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Modelo de inferencia de posturas en Twitter (referéndum)</t>
+          <t>Caminar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Es un estudio.</t>
+          <t>De acuerdo a la descripción, solo permitiría a los ciudadanos consultar.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2303.15532</t>
+          <t>https://parlamericas.org/uploads/documents/Presentation-OPNStaffMeeting-ProyectoCAMINARChile_MiguelLanderos-sp.pdf</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CL-EXC-modelo-de-inferencia-de-posturas-en-twit</t>
+          <t>CL-EXC-caminar</t>
         </is>
       </c>
     </row>
@@ -5717,22 +5461,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
+          <t>Modelo de inferencia de posturas en Twitter (referéndum)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo real, pero solo se confirma que la plataforma (Go Vocal) tiene el módulo de IA/NLP de fábrica; no hay traza de que Pudahuel lo activara sobre los aportes, sin evidencia). Sin uso de IA verificado.</t>
+          <t>Es un estudio.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://participa.mpudahuel.cl/</t>
+          <t>https://arxiv.org/abs/2303.15532</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CL-participa-pudahuel-presupuesto</t>
+          <t>CL-EXC-modelo-de-inferencia-de-posturas-en-twit</t>
         </is>
       </c>
     </row>
@@ -5744,22 +5488,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Participa Pudahuel — Presupuesto Participativo deliberativo (plataforma Go Vocal/CitizenLab)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias).</t>
+          <t>Presupuesto participativo real, pero solo se confirma que la plataforma (Go Vocal) tiene el módulo de IA/NLP de fábrica; no hay traza de que Pudahuel lo activara sobre los aportes, sin evidencia). Sin uso de IA verificado.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://participa.mpudahuel.cl/</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CL-participacion-ciudadana-proceso-constitu-2</t>
+          <t>CL-participa-pudahuel-presupuesto</t>
         </is>
       </c>
     </row>
@@ -5771,22 +5515,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Plataforma UCampus - participación 2023 (proceso constitucional)</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Existe un proceso participativo elegible (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Universidad de Chile) fue el operador técnico de dos de los cuatro mecanismos (Audiencias Públicas e Iniciativa Popular de Norma). Sin embargo, no se halló evidencia de que la plataforma UCampus aplicara IA sobre el contenido de los aportes ciudadanos (clasificar/analizar/agrupar/sintetizar). Las fuentes describen a UCampus en funciones de recepción y gestión (recibir solicitudes de audiencia, revisar artículos, proponer enmiendas, recolectar firmas con ClaveÚnica), y la sistematización analítica de los aportes la realizó la Secretaría de Participación mediante una sistematización cualitativa encabezada por académicos de derecho constitucional y ciencias sociales -no mediante NLP/IA-. Las herramientas de IA visibles en el proceso 2023 (Constitucion.AI, Discolab, ChatBot Constitucional) operaron sobre el texto de la propuesta para comprensión ciudadana, no sobre los aportes, y son proyectos independientes sin vínculo con UCampus. Por tanto, a diferencia de los cabildos 2016 (donde sí hubo análisis NLP de aportes), no se confirma IA sobre el contenido de los aportes en la plataforma UCampus 2023. Se mantiene excluido (entra=no); las URLs oficiales clave (uchile.cl, ingenieria.uchile.cl, informe oficial de la Secretaría en pdf) devolvieron http 403 y quedan en gaps para verificación manual.</t>
+          <t>Aplica a los dos casos homónimos (autoconvocados y audiencias).</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://ucampus.cl/ucampus-es-la-plataforma-digital-del-proceso-constitucional-2023/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CL-EXC-ucampus</t>
+          <t>CL-participacion-ciudadana-proceso-constitu-2</t>
         </is>
       </c>
     </row>
@@ -5798,22 +5542,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Senador Virtual / CrowdLaw (GobLab UAI + IMFD)</t>
+          <t>Plataforma UCampus - participación 2023 (proceso constitucional)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>(resuelve duda -&gt; no). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 anios, &gt;130.000 participantes), pero la plataforma en si no usa IA sobre el contenido de los aportes y por tanto no basta. El componente con IA/NLP es el proyecto CrowdLaw del GobLab UAI (+ Harvard), que la evidencia describe consistentemente como investigacion academica de metodologia mixta (analisis estadistico, entrevistas, etnografia digital) aplicada retrospectivamente a 15-16 anios de datos, cuyo producto son recomendaciones de diseno; el propio articulo '16 years of CrowdLaw' indica que, para aprovechar la plataforma, hay que 'anadir una metodologia confiable para procesar el aporte ciudadano' (una capacidad aun no implementada), no que exista una herramienta de NLP en produccion. La 'senial imfd + NLP' del caso se refiere a un producto distinto (plataforma 'Vincula' del imfd: NLP para vincular temas de interes con academicos/expertos y conectarlos con el Congreso), que no procesa los aportes ciudadanos de Senador Virtual. La actualizacion BID (2018-2020) solo anadio 'analisis de datos' y 'reporte con visualizaciones para la comision' (analitica descriptiva). La literatura academica chilena (Guridi et al., Cornell, arXiv 2410.22937, 2024) concluye que los gobiernos 'no estan adoptando ampliamente' NLP para analizar las contribuciones ciudadanas, reforzando la no existencia de despliegue. Como el NLP/IA sobre el contenido de los aportes solo aparece como investigacion/recomendacion (no integrada al proceso) y no como despliegue en produccion, no es elegible. Convocante del proceso = gobierno nacional (Senado/Congreso); desarrollador del eventual componente IA = universidad (GobLab UAI) + academia (Harvard / imfd).</t>
+          <t>Existe un proceso participativo elegible (Proceso Constitucional 2023, mecanismos de participación ciudadana con ~280 mil personas, convocado por el Estado de Chile), y UCampus (Universidad de Chile) fue el operador técnico de dos de los cuatro mecanismos (Audiencias Públicas e Iniciativa Popular de Norma). Sin embargo, no se halló evidencia de que la plataforma UCampus aplicara IA sobre el contenido de los aportes ciudadanos (clasificar/analizar/agrupar/sintetizar). Las fuentes describen a UCampus en funciones de recepción y gestión (recibir solicitudes de audiencia, revisar artículos, proponer enmiendas, recolectar firmas con ClaveÚnica), y la sistematización analítica de los aportes la realizó la Secretaría de Participación mediante una sistematización cualitativa encabezada por académicos de derecho constitucional y ciencias sociales -no mediante NLP/IA-. Las herramientas de IA visibles en el proceso 2023 (Constitucion.AI, Discolab, ChatBot Constitucional) operaron sobre el texto de la propuesta para comprensión ciudadana, no sobre los aportes, y son proyectos independientes sin vínculo con UCampus. Por tanto, a diferencia de los cabildos 2016 (donde sí hubo análisis NLP de aportes), no se confirma IA sobre el contenido de los aportes en la plataforma UCampus 2023. Se mantiene excluido (entra=no); las URLs oficiales clave (uchile.cl, ingenieria.uchile.cl, informe oficial de la Secretaría en pdf) devolvieron http 403 y quedan en gaps para verificación manual.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://goblab.uai.cl/en/16-years-of-crowdlaw-in-the-chilean-parliament/</t>
+          <t>https://ucampus.cl/ucampus-es-la-plataforma-digital-del-proceso-constitucional-2023/</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CL-senador-virtual-crowdlaw-goblab-uai-imfd</t>
+          <t>CL-EXC-ucampus</t>
         </is>
       </c>
     </row>
@@ -5825,49 +5569,49 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
+          <t>Senador Virtual / CrowdLaw (GobLab UAI + IMFD)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo real sobre plataforma Go Vocal, pero no se encontró en el informe ejecutivo ninguna traza de uso de IA sobre los aportes, sin evidencia). Sin uso de IA verificado.</t>
+          <t>(resuelve duda -&gt; no). La plataforma Senador Virtual / Congreso Virtual es un proceso participativo digital del Congreso de Chile (gobierno nacional) plenamente activo y consolidado (&gt;16 anios, &gt;130.000 participantes), pero la plataforma en si no usa IA sobre el contenido de los aportes y por tanto no basta. El componente con IA/NLP es el proyecto CrowdLaw del GobLab UAI (+ Harvard), que la evidencia describe consistentemente como investigacion academica de metodologia mixta (analisis estadistico, entrevistas, etnografia digital) aplicada retrospectivamente a 15-16 anios de datos, cuyo producto son recomendaciones de diseno; el propio articulo '16 years of CrowdLaw' indica que, para aprovechar la plataforma, hay que 'anadir una metodologia confiable para procesar el aporte ciudadano' (una capacidad aun no implementada), no que exista una herramienta de NLP en produccion. La 'senial imfd + NLP' del caso se refiere a un producto distinto (plataforma 'Vincula' del imfd: NLP para vincular temas de interes con academicos/expertos y conectarlos con el Congreso), que no procesa los aportes ciudadanos de Senador Virtual. La actualizacion BID (2018-2020) solo anadio 'analisis de datos' y 'reporte con visualizaciones para la comision' (analitica descriptiva). La literatura academica chilena (Guridi et al., Cornell, arXiv 2410.22937, 2024) concluye que los gobiernos 'no estan adoptando ampliamente' NLP para analizar las contribuciones ciudadanas, reforzando la no existencia de despliegue. Como el NLP/IA sobre el contenido de los aportes solo aparece como investigacion/recomendacion (no integrada al proceso) y no como despliegue en produccion, no es elegible. Convocante del proceso = gobierno nacional (Senado/Congreso); desarrollador del eventual componente IA = universidad (GobLab UAI) + academia (Harvard / imfd).</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://vinadecide.cl/pages/presupuestoparticipativo</t>
+          <t>https://goblab.uai.cl/en/16-years-of-crowdlaw-in-the-chilean-parliament/</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CL-vina-decide-presupuesto-participativo</t>
+          <t>CL-senador-virtual-crowdlaw-goblab-uai-imfd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
+          <t>Viña Decide — Primer Presupuesto Participativo de Viña del Mar (plataforma Go Vocal/CitizenLab)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes ciudadanos dentro del proceso participativo. La metodologia describe 'instrumentos que facilitan la sistematizacion' como innovacion metodologica/manual, sin mencion de IA, PLN ni analisis automatizado de propuestas. Las referencias a IA halladas pertenecen a iniciativas separadas: un estudio academico de 'Factibilidad de inteligencia artificial para la participacion ciudadana en la planificacion urbana de Bogota: caso del POT', que es investigacion de aceptacion/factibilidad de una herramienta propuesta, no desplegada en la Asamblea; politicas distritales de uso de IA en entidades publicas. Se mantiene la exclusion de 2025 ('No se encontro informacion sobre el uso de la IA en la implementacion de los Mini Publics'). Decision: (entra=no).</t>
+          <t>Presupuesto participativo real sobre plataforma Go Vocal, pero no se encontró en el informe ejecutivo ninguna traza de uso de IA sobre los aportes, sin evidencia). Sin uso de IA verificado.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
+          <t>https://vinadecide.cl/pages/presupuestoparticipativo</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-asamblea-itinerante</t>
+          <t>CL-vina-decide-presupuesto-participativo</t>
         </is>
       </c>
     </row>
@@ -5879,22 +5623,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
+          <t>Asamblea Ciudadana Itinerante del Concejo de Bogotá</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>No elegible. Dentro de un proceso participativo real (pod con mesas/talleres subregionales), la IA (plataforma lita / base de datos con IA) cumple funciones de almacenamiento, procesamiento y estructuración de información técnica territorial y cruce de datos técnicos/geoespaciales de punta para actualizar planes de ordenamiento y estructurar proyectos. no hay evidencia en ninguna fuente de que la IA procese el contenido/texto de los aportes ciudadanos (clasificar, agrupar, resumir o analizar sentimiento de lo aportado en las mesas). Los resultados de los talleres se compilan en un 'visor interactivo', pero no se atribuye a la IA el análisis del texto de los aportes. Esto encaja exactamente en la exclusión del criterio: 'no si la IA (plataforma lita) solo cruza datos geoespaciales/técnicos o almacena/estructura info sin analizar el texto de los aportes'. Por tanto: entra=no. Reevaluar si futuras fuentes documentan que lita sistematiza/clasifica/resume el texto de los aportes ciudadanos.</t>
+          <t>El proceso es elegible en su forma (mini-publico deliberativo recurrente convocado por gobierno local: Concejo de Bogota via DemoLab; 3 ediciones 2020/2021/2023). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes ciudadanos dentro del proceso participativo. La metodologia describe 'instrumentos que facilitan la sistematizacion' como innovacion metodologica/manual, sin mencion de IA, PLN ni analisis automatizado de propuestas. Las referencias a IA halladas pertenecen a iniciativas separadas: un estudio academico de 'Factibilidad de inteligencia artificial para la participacion ciudadana en la planificacion urbana de Bogota: caso del POT', que es investigacion de aceptacion/factibilidad de una herramienta propuesta, no desplegada en la Asamblea; politicas distritales de uso de IA en entidades publicas. Se mantiene la exclusion de 2025 ('No se encontro informacion sobre el uso de la IA en la implementacion de los Mini Publics'). Decision: (entra=no).</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
+          <t>https://concejodebogota.gov.co/llega-al-concejo-de-bogota-la-tercera-asamblea-ciudadana-que-busca/cbogota/2023-05-23/084537.php</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CO-atlantico-pod-lita</t>
+          <t>CO-EXC-asamblea-itinerante</t>
         </is>
       </c>
     </row>
@@ -5906,22 +5650,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Chatbot ALBA</t>
+          <t>Atlántico – Plan de Ordenamiento Departamental (POD) 2025-2050 / plataforma LITA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana.</t>
+          <t>No elegible. Dentro de un proceso participativo real (pod con mesas/talleres subregionales), la IA (plataforma lita / base de datos con IA) cumple funciones de almacenamiento, procesamiento y estructuración de información técnica territorial y cruce de datos técnicos/geoespaciales de punta para actualizar planes de ordenamiento y estructurar proyectos. no hay evidencia en ninguna fuente de que la IA procese el contenido/texto de los aportes ciudadanos (clasificar, agrupar, resumir o analizar sentimiento de lo aportado en las mesas). Los resultados de los talleres se compilan en un 'visor interactivo', pero no se atribuye a la IA el análisis del texto de los aportes. Esto encaja exactamente en la exclusión del criterio: 'no si la IA (plataforma lita) solo cruza datos geoespaciales/técnicos o almacena/estructura info sin analizar el texto de los aportes'. Por tanto: entra=no. Reevaluar si futuras fuentes documentan que lita sistematiza/clasifica/resume el texto de los aportes ciudadanos.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://barranquilla.gov.co/chatbot</t>
+          <t>https://www.atlantico.gov.co/index.php/noticias/prensa-planeacion/27250-plan-de-ordenamiento-departamental-toma-forma-en-el-atlantico</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-chatbot-alba</t>
+          <t>CO-atlantico-pod-lita</t>
         </is>
       </c>
     </row>
@@ -5933,7 +5677,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Rama Judicial</t>
+          <t>Chatbot ALBA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -5943,12 +5687,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
+          <t>https://barranquilla.gov.co/chatbot</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-chatbot-rama-judicial</t>
+          <t>CO-EXC-chatbot-alba</t>
         </is>
       </c>
     </row>
@@ -5960,22 +5704,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Rebecca</t>
+          <t>Chatbot Rama Judicial</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
+          <t>https://www.ramajudicial.gov.co/web/centro-de-documentacion-judicial/nuevo-chatbot</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-chatbot-rebecca</t>
+          <t>CO-EXC-chatbot-rama-judicial</t>
         </is>
       </c>
     </row>
@@ -5987,22 +5731,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
+          <t>Chatbot Rebecca</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://dialogosregionales.dnp.gov.co/</t>
+          <t>https://bogota.gov.co/mi-ciudad/habitat/bogota-tiene-chatbot-renobo-que-utiliza-inteligencia-artificial</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CO-dnp-dialogos-regionales-vinculantes-pnd</t>
+          <t>CO-EXC-chatbot-rebecca</t>
         </is>
       </c>
     </row>
@@ -6014,22 +5758,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
+          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
+          <t>Escucha social de redes abiertas (Twitter/Facebook) durante el paro de 2021: no hay proceso participativo convocado . Misma regla que U-Report (solo opinión).</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
+          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>CO-descongestion-de-solicitudes-diarias-del</t>
+          <t>CO-citibeats-pnud-colombia-deliberacion-pub</t>
         </is>
       </c>
     </row>
@@ -6041,22 +5785,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
+          <t>DNP - Diálogos Regionales Vinculantes (PND 2022-2026)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>El criterio de elegibilidad exige que dentro de un proceso participativo se despliegue IA real (institucional) sobre el contenido de los aportes ciudadanos. El caso documentado es un artículo académico (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revista Control Visible de la Auditoría General) de una 'investigación aplicada de enfoque mixto y alcance exploratorio dada la innovación de la propuesta', cuyo objetivo es 'identificar la factibilidad de aceptación de una herramienta de inteligencia artificial' para la participación en el POT. Es decir, propone/evalúa una herramienta de IA y mide su aceptación encuestando a 395 ciudadanos y entrevistando a expertos urbanistas; no despliega IA sobre aportes reales de un proceso participativo institucional en curso. La (búsqueda dirigida: 8 búsquedas web + 4 intentos de fetch) no halló ningún despliegue institucional de IA sobre aportes ciudadanos reales del POT por parte de la Secretaría Distrital de Planeación, el Concejo de Bogotá o la Auditoría. Los despliegues reales de IA de la SDP que sí aparecen (ISIDataInsights / 'Inteligencia 360°' / reto 'Datos con Historia', oct-nov 2024; Chatico vía WhatsApp) están explícitamente ligados al Plan Distrital de desarrollo 'Bogotá Camina Segura' 2024-2028 (la fuente indica que 'Datos con Historia' fue 'el primero de cinco' retos de la estrategia '5 en Innovación' del Plan de Desarrollo), no al POT, y constituyen casos distintos. Por ello el veredicto pasa de duda a no: se trata de un artículo/propuesta (estudio de aceptación), no de un caso desplegado., no IA aplicada a aportes; no hay IA en operación sobre el proceso);; nivel_consolidacion=0; tipo_convocante=universidad (autor del estudio).</t>
+          <t>Participación real, pero el análisis fue manual/cualitativo; solo text-analytics ligero (nubes de palabras + tabulación), sin NLP sobre el contenido.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
+          <t>https://dialogosregionales.dnp.gov.co/</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CO-ia-para-participacion-en-el-pot-de-bogot</t>
+          <t>CO-dnp-dialogos-regionales-vinculantes-pnd</t>
         </is>
       </c>
     </row>
@@ -6068,22 +5812,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
+          <t>Descongestión de solicitudes diarias del programa Ingreso Solidario</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Duda con inclinación no (reafirmada en con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el contenido de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, aplicar modelos de IA para identificar patrones clave, analizar datos cualitativos), lo que en principio encajaría con el criterio de IA sobre el contenido de los aportes dentro de un marco de planeación. Por otro lado —y de forma determinante tras 2ª (jun-2026) y 3ª (jul-2026) pasadas de investigación— el caso documentado es una herramienta ganadora de un concurso de innovación abierta (Reto de Ciudad 'Datos con Historia', SDP+Maloka, oct-nov 2024) que, en todas las fuentes disponibles, sigue descrita en fase prospectiva: 'entra en una tercera etapa, donde será integrada a los sistemas de información del Distrito' / 'la solución se implementará para que se incorpore a los sistemas donde la ciudad recoge información'. no existe evidencia de aplicación operativa real al contenido de los aportes de un proceso participativo concreto (consulta, cabildo, presupuesto participativo, construcción del pdd 2024-2028, POT, etc.). La amplió los canales más allá de la SDP: (i) la empresa desarrolladora igg no muestra la herramienta como producto con clientes/despliegues; su único rastro público con ISIDataInsights es el post 'Ganamos' de LinkedIn (~dic 2024) sobre ganar el reto, sin publicación posterior de despliegue; (ii) no hay contrato en SECOP/datos.gov.co que vincule a igg con la SDP para implementación; (iii) no hay despliegues en otras ciudades de latam; (iv) el texto de Maloka/SDP sobre 'metodologías ágiles', 'sesiones de prueba y validación' y 'capacidades instaladas' describe el desarrollo/configuración de la herramienta, no el análisis de aportes reales; (v) las demás iniciativas de IA+participación en Bogotá (POT con ~20 mil aportes, estudio académico de factibilidad de IA para el POT en revista Control Visible, Ecosistema de IA Urbana de la Agencia Atenea, agente Chatico) son separadas y ninguna reporta usar ISIDataInsights sobre aportes. Conforme a la regla de elegibilidad ('herramienta ganadora de concurso pero aún sin aplicación a un proceso participativo concreto duda/no'), el balance se inclina a R por ausencia de despliegue sobre aportes ciudadanos reales; se mantiene la etiqueta por la naturaleza negativa de la evidencia (ausencia de reportes, no prueba positiva de no-uso) y por el ajuste exacto de la función prevista al criterio. Nivel de consolidación bajo (1, anuncio). advertencia importante: existe una iniciativa distinta y separada de la SDP donde la ciudadanía participa en la construcción del Plan de Desarrollo mediante IA a través del agente virtual 'Chatico' (WhatsApp); esa no es ISIDataInsights y no debe conflarse con este caso.</t>
+          <t>Atención ciudadana (triage de 10.000 correos/día): servicio, no participación.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
+          <t>https://prosperidadsocial.gov.co/Noticias/inteligencia-artificial-la-herramienta-que-descongestiono-10-000-solicitudes-diarias-de-ingreso-solidario/</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CO-isidatainsights-reto-de-ciudad-datos-con</t>
+          <t>CO-descongestion-de-solicitudes-diarias-del</t>
         </is>
       </c>
     </row>
@@ -6095,22 +5839,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Mini-Public del diálogo social de la Procuraduría</t>
+          <t>IA para participación en el POT de Bogotá (Control Visible / Auditoría General)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Se mantiene excluido (entra=no), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es elegible por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la Nación y facilitado por ideemos), pero el criterio de inclusión exige evidencia de IA sobre el contenido de los aportes ciudadanos dentro del proceso participativo, y no se encontró ninguna. Todas las fuentes describen el diálogo social como una metodología de deliberación y construcción de acuerdos (mesas, escuelas de diálogo, espacios de investigación y diálogo), sin mención de procesamiento de lenguaje natural, machine learning, clasificación/clustering automatizado, relatoría asistida por IA ni sistematización automatizada de las contribuciones. Las referencias a IA de la Procuraduría que sí aparecen son ajenas al proceso participativo: (a) una herramienta de consulta con IA para la Guía Disciplinaria (asuntos disciplinarios, nov-2025) y (b) preparación frente a redes/algoritmos/IA y desinformación para 'proteger la democracia' (foro Semana). Ninguna procesa los aportes de los mini-públicos. No se trata de duda porque no hay indicios reales (aunque no concluyentes) de IA sobre el contenido de los aportes; simplemente hay ausencia de evidencia, igual que en 2025.</t>
+          <t>El criterio de elegibilidad exige que dentro de un proceso participativo se despliegue IA real (institucional) sobre el contenido de los aportes ciudadanos. El caso documentado es un artículo académico (Fundación Universitaria del Área Andina, Maestría en Innovación; publicado en la revista Control Visible de la Auditoría General) de una 'investigación aplicada de enfoque mixto y alcance exploratorio dada la innovación de la propuesta', cuyo objetivo es 'identificar la factibilidad de aceptación de una herramienta de inteligencia artificial' para la participación en el POT. Es decir, propone/evalúa una herramienta de IA y mide su aceptación encuestando a 395 ciudadanos y entrevistando a expertos urbanistas; no despliega IA sobre aportes reales de un proceso participativo institucional en curso. La (búsqueda dirigida: 8 búsquedas web + 4 intentos de fetch) no halló ningún despliegue institucional de IA sobre aportes ciudadanos reales del POT por parte de la Secretaría Distrital de Planeación, el Concejo de Bogotá o la Auditoría. Los despliegues reales de IA de la SDP que sí aparecen (ISIDataInsights / 'Inteligencia 360°' / reto 'Datos con Historia', oct-nov 2024; Chatico vía WhatsApp) están explícitamente ligados al Plan Distrital de desarrollo 'Bogotá Camina Segura' 2024-2028 (la fuente indica que 'Datos con Historia' fue 'el primero de cinco' retos de la estrategia '5 en Innovación' del Plan de Desarrollo), no al POT, y constituyen casos distintos. Por ello el veredicto pasa de duda a no: se trata de un artículo/propuesta (estudio de aceptación), no de un caso desplegado., no IA aplicada a aportes; no hay IA en operación sobre el proceso);; nivel_consolidacion=0; tipo_convocante=universidad (autor del estudio).</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
+          <t>https://controlvisible.auditoria.gov.co/index.php/rcf/article/view/63</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-procuraduria</t>
+          <t>CO-ia-para-participacion-en-el-pot-de-bogot</t>
         </is>
       </c>
     </row>
@@ -6122,22 +5866,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Pa' que veás (Cali)</t>
+          <t>ISIDataInsights / Reto de Ciudad 'Datos con Historia' (SDP Bogotá)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un monitor de inversion publica (dashboard de datos abiertos) construido sobre MapaInversiones del BID: visualiza, filtra y permite hacer seguimiento al gasto y los contratos publicos. Las menciones a IA en Cali (chatbots para consulta ciudadana, analisis predictivo para mitigacion de riesgos naturales como deslizamientos/dengue, seguridad) pertenecen a iniciativas separadas del ecosistema smart-city de la Alcaldia y se listan junto a 'Pa' que veas' solo como ejemplos de la estrategia de IA de la ciudad; el monitor aparece encuadrado unicamente en 'gestion eficiente de datos para... seguimiento a la inversion publica', no como IA aplicada a quejas. Las funcionalidades de reportes ciudadanos, alertas de irregularidades y envio de fotografias por la comunidad estan anunciadas como evolucion futura del sistema ('continuara evolucionando con nuevas funcionalidades'), no operan hoy y no hay evidencia de que vayan a ser procesadas por IA sobre su contenido. No se cumple el criterio de inclusión (IA sobre el contenido de los aportes ciudadanos dentro de un proceso participativo). Se mantiene la exclusion de 2025 ('No evidencia de uso de IA'). Decision: (entra=no).</t>
+          <t>Duda con inclinación no (reafirmada en con búsqueda amplia, jul-2026). Por un lado, la herramienta ISIDataInsights está diseñada para operar sobre el contenido de información cualitativa de planeación, incluyendo explícitamente 'los aportes ciudadanos' (procesar, validar consistencia, aplicar modelos de IA para identificar patrones clave, analizar datos cualitativos), lo que en principio encajaría con el criterio de IA sobre el contenido de los aportes dentro de un marco de planeación. Por otro lado —y de forma determinante tras 2ª (jun-2026) y 3ª (jul-2026) pasadas de investigación— el caso documentado es una herramienta ganadora de un concurso de innovación abierta (Reto de Ciudad 'Datos con Historia', SDP+Maloka, oct-nov 2024) que, en todas las fuentes disponibles, sigue descrita en fase prospectiva: 'entra en una tercera etapa, donde será integrada a los sistemas de información del Distrito' / 'la solución se implementará para que se incorpore a los sistemas donde la ciudad recoge información'. no existe evidencia de aplicación operativa real al contenido de los aportes de un proceso participativo concreto (consulta, cabildo, presupuesto participativo, construcción del pdd 2024-2028, POT, etc.). La amplió los canales más allá de la SDP: (i) la empresa desarrolladora igg no muestra la herramienta como producto con clientes/despliegues; su único rastro público con ISIDataInsights es el post 'Ganamos' de LinkedIn (~dic 2024) sobre ganar el reto, sin publicación posterior de despliegue; (ii) no hay contrato en SECOP/datos.gov.co que vincule a igg con la SDP para implementación; (iii) no hay despliegues en otras ciudades de latam; (iv) el texto de Maloka/SDP sobre 'metodologías ágiles', 'sesiones de prueba y validación' y 'capacidades instaladas' describe el desarrollo/configuración de la herramienta, no el análisis de aportes reales; (v) las demás iniciativas de IA+participación en Bogotá (POT con ~20 mil aportes, estudio académico de factibilidad de IA para el POT en revista Control Visible, Ecosistema de IA Urbana de la Agencia Atenea, agente Chatico) son separadas y ninguna reporta usar ISIDataInsights sobre aportes. Conforme a la regla de elegibilidad ('herramienta ganadora de concurso pero aún sin aplicación a un proceso participativo concreto duda/no'), el balance se inclina a R por ausencia de despliegue sobre aportes ciudadanos reales; se mantiene la etiqueta por la naturaleza negativa de la evidencia (ausencia de reportes, no prueba positiva de no-uso) y por el ajuste exacto de la función prevista al criterio. Nivel de consolidación bajo (1, anuncio). advertencia importante: existe una iniciativa distinta y separada de la SDP donde la ciudadanía participa en la construcción del Plan de Desarrollo mediante IA a través del agente virtual 'Chatico' (WhatsApp); esa no es ISIDataInsights y no debe conflarse con este caso.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
+          <t>https://www.sdp.gov.co/noticias/bogota-cuenta-herramienta-innovadora-abordar-los-problemas-urbanos-aporte-de-la-ciudadania</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-paqueveas</t>
+          <t>CO-isidatainsights-reto-de-ciudad-datos-con</t>
         </is>
       </c>
     </row>
@@ -6149,22 +5893,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Urna de Cristal</t>
+          <t>Mini-Public del diálogo social de la Procuraduría</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA.</t>
+          <t>Se mantiene excluido (entra=no), confirmando el motivo de exclusión de 2025 ('No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). El proceso es elegible por su naturaleza (mini-público / diálogo social deliberativo convocado por la Procuraduría General de la Nación y facilitado por ideemos), pero el criterio de inclusión exige evidencia de IA sobre el contenido de los aportes ciudadanos dentro del proceso participativo, y no se encontró ninguna. Todas las fuentes describen el diálogo social como una metodología de deliberación y construcción de acuerdos (mesas, escuelas de diálogo, espacios de investigación y diálogo), sin mención de procesamiento de lenguaje natural, machine learning, clasificación/clustering automatizado, relatoría asistida por IA ni sistematización automatizada de las contribuciones. Las referencias a IA de la Procuraduría que sí aparecen son ajenas al proceso participativo: (a) una herramienta de consulta con IA para la Guía Disciplinaria (asuntos disciplinarios, nov-2025) y (b) preparación frente a redes/algoritmos/IA y desinformación para 'proteger la democracia' (foro Semana). Ninguna procesa los aportes de los mini-públicos. No se trata de duda porque no hay indicios reales (aunque no concluyentes) de IA sobre el contenido de los aportes; simplemente hay ausencia de evidencia, igual que en 2025.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
+          <t>https://ideemos.org/mini-public-del-dialogo-social-de-la-procuraduria/</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-plataforma-urna-de-cristal</t>
+          <t>CO-EXC-procuraduria</t>
         </is>
       </c>
     </row>
@@ -6176,22 +5920,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SISBÉN IV</t>
+          <t>Pa' que veás (Cali)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Se revisa por su analogia con dIAra (bots que recopilan quejas ciudadanas y predicen riesgos en obras). Sin embargo, no se encontro evidencia de uso de inteligencia artificial sobre el contenido de los aportes/quejas ciudadanas dentro de un proceso participativo. 'Pa' que veas' es, en su nucleo, un monitor de inversion publica (dashboard de datos abiertos) construido sobre MapaInversiones del BID: visualiza, filtra y permite hacer seguimiento al gasto y los contratos publicos. Las menciones a IA en Cali (chatbots para consulta ciudadana, analisis predictivo para mitigacion de riesgos naturales como deslizamientos/dengue, seguridad) pertenecen a iniciativas separadas del ecosistema smart-city de la Alcaldia y se listan junto a 'Pa' que veas' solo como ejemplos de la estrategia de IA de la ciudad; el monitor aparece encuadrado unicamente en 'gestion eficiente de datos para... seguimiento a la inversion publica', no como IA aplicada a quejas. Las funcionalidades de reportes ciudadanos, alertas de irregularidades y envio de fotografias por la comunidad estan anunciadas como evolucion futura del sistema ('continuara evolucionando con nuevas funcionalidades'), no operan hoy y no hay evidencia de que vayan a ser procesadas por IA sobre su contenido. No se cumple el criterio de inclusión (IA sobre el contenido de los aportes ciudadanos dentro de un proceso participativo). Se mantiene la exclusion de 2025 ('No evidencia de uso de IA'). Decision: (entra=no).</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/sisben</t>
+          <t>https://www.iadb.org/en/news/city-cali-launches-platform-monitoring-public-investment-idb-support</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-sisben-iv</t>
+          <t>CO-EXC-paqueveas</t>
         </is>
       </c>
     </row>
@@ -6203,130 +5947,130 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
+          <t>Plataforma Urna de Cristal</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>El criterio de inclusión exige evidencia de IA aplicada al contenido de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su pdf) describe 'Inteligencia Artificial' y 'Machine Learning' solo como parte de un listado de técnicas cuantitativas/cualitativas para comprender el problema (al lado de encuestas, entrevistas, revisión documental, observación participante), separadas explícitamente de las técnicas de diálogo/deliberación (mini-públicos, asambleas, jurados, conferencias de consenso). El uso de IA aparece como diagnóstico/insumo de contexto que produce 'mediciones objetivas' presentadas a la gente, no como procesamiento del contenido de los aportes deliberativos. No se halló ninguna fuente que documente que la IA sistematice, codifique, agrupe o analice las intervenciones de los participantes en un mini-público concreto. En el caso aplicado real asociado a Ideemos (Asamblea Ciudadana Itinerante del Concejo de Bogotá, vía DemoLab, 3 capítulos 2020-2023) la deliberación se describe por 'método espiral' y comisiones temáticas, sin mención de IA sobre los aportes. Por tanto la 'IA' funciona como metodología/marketing de diagnóstico sin procesamiento real del contenido participativo: (coincide con el motivo de exclusión 2025: 'No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). No se eleva a duda porque la única mención de IA es genérica y de etapa de diagnóstico, sin indicio concreto de procesamiento de contenido deliberativo.</t>
+          <t>No evidencia de uso de IA.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
+          <t>https://projects.itforchange.net/mavc/wp-content/uploads/2017/09/Voice-or-Chatter_Case-Study_Colombia_August-2017.pdf</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CO-EXC-ilabs</t>
+          <t>CO-EXC-plataforma-urna-de-cristal</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-Report Costa Rica – chatbot juvenil</t>
+          <t>SISBÉN IV</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta . Solo opinión fuera.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://costarica.ureport.in/</t>
+          <t>https://fairlac.iadb.org/sisben</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CR-u-report-costa-rica-chatbot-juvenil</t>
+          <t>CO-EXC-sisben-iv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>dIAra</t>
+          <t>iLabs - Laboratorios de Inteligencia Colectiva (Ideemos)</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
+          <t>El criterio de inclusión exige evidencia de IA aplicada al contenido de los aportes ciudadanos dentro de un proceso participativo. La fuente primaria (página iLabs de Ideemos y su pdf) describe 'Inteligencia Artificial' y 'Machine Learning' solo como parte de un listado de técnicas cuantitativas/cualitativas para comprender el problema (al lado de encuestas, entrevistas, revisión documental, observación participante), separadas explícitamente de las técnicas de diálogo/deliberación (mini-públicos, asambleas, jurados, conferencias de consenso). El uso de IA aparece como diagnóstico/insumo de contexto que produce 'mediciones objetivas' presentadas a la gente, no como procesamiento del contenido de los aportes deliberativos. No se halló ninguna fuente que documente que la IA sistematice, codifique, agrupe o analice las intervenciones de los participantes en un mini-público concreto. En el caso aplicado real asociado a Ideemos (Asamblea Ciudadana Itinerante del Concejo de Bogotá, vía DemoLab, 3 capítulos 2020-2023) la deliberación se describe por 'método espiral' y comisiones temáticas, sin mención de IA sobre los aportes. Por tanto la 'IA' funciona como metodología/marketing de diagnóstico sin procesamiento real del contenido participativo: (coincide con el motivo de exclusión 2025: 'No se encontró información sobre el uso de la IA en la implementación de los Mini Publics'). No se eleva a duda porque la única mención de IA es genérica y de etapa de diagnóstico, sin indicio concreto de procesamiento de contenido deliberativo.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
+          <t>https://ideemos.org/ilabs-laboratorios-de-inteligencia-colectiva/</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CR-diara</t>
+          <t>CO-EXC-ilabs</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CiudadanIA</t>
+          <t>U-Report Costa Rica – chatbot juvenil</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación.</t>
+          <t>UNICEF lo define como 'encuestas de opinión' (panel de sondeo/percepción juvenil anónimo: clima, salud mental, educación); sin proceso participativo estructurado con incidencia concreta . Solo opinión fuera.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://www.genia.ai/paises-miembros</t>
+          <t>https://costarica.ureport.in/</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>DO-ciudadania</t>
+          <t>CR-u-report-costa-rica-chatbot-juvenil</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>dIAra</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>Civic tech de fiscalización de obras (control social vía app): no es un proceso participativo.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
+          <t>https://www.opengovpartnership.org/the-open-gov-challenge/costa-rica-artificial-intelligence-alerts-citizen-control-public-infrastructure/</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>DO-EXC-sara</t>
+          <t>CR-diara</t>
         </is>
       </c>
     </row>
@@ -6338,103 +6082,103 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>TAÍNA: Gobierno Inteligente</t>
+          <t>CiudadanIA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana.</t>
+          <t>Solo atención/servicio; la 'participación' es co-diseñar la IA aportando datos, no consulta pública. Sin módulo de participación.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
+          <t>https://www.genia.ai/paises-miembros</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>DO-EXC-taina-gobierno-inteligente</t>
+          <t>DO-ciudadania</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>El criterio elegible exige que la IA generativa se use para sistematizar/clasificar/resumir el contenido de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=14176 del 04-nov-2025; nota ?p=14622 comunidad de practica feb-2026; blog Red Ciudadana; blog PNUD/unsdg 'IA inclusiva para el desarrollo municipal') describe la plataforma como (a) herramienta interna de productividad con 'agentes' para 'tareas repetitivas', (b) analisis de datos/documentos institucionales para estadisticas y alertas sobre la 'papeleria', y (c) un proceso de fortalecimiento de capacidades / comunidad de practica del equipo tecnico. Coincide exactamente con la exclusion del criterio ('solo herramienta interna de productividad/capacitacion del equipo tecnico o comunidad de practica sin aplicarse a los aportes'). Aunque SEGEPLAN es el ente rector de los PDM (que si integran aportes de COCODES/COMUDES) y la linea del PNUD prototipa soluciones municipales (atencion ciudadana, catastro, ordenamiento territorial), no se halla ninguna cita que conecte la IA con el tratamiento del contenido de los aportes participativos. Se decide entra=NOapoyo',no'). Confirma la tendencia previa , resuelta a no con evidencia multiple.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
+          <t>https://www.undp.org/es/guatemala/comunicados-de-prensa/sara-la-nueva-herramienta-de-inteligencia-artificial-para-combatir-la-violencia-de-genero-en-centroamerica</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>GT-segeplan-plataforma-ia-generativa</t>
+          <t>DO-EXC-sara</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
+          <t>TAÍNA: Gobierno Inteligente</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
+          <t>https://www.diariolibre.com/actualidad/nacional/2023/10/11/gobierno-presenta-estrategia-de-inteligencia-artificial/2489157</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>LATAM-EXC-antai-smart-cid-autoridad-nacional-de-tr</t>
+          <t>DO-EXC-taina-gobierno-inteligente</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LATAM</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Botivist</t>
+          <t>Plataforma de modelos generativos de IA de SEGEPLAN + Red Ciudadana (Guatemala)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>No tiene foco en un país específico.</t>
+          <t>El criterio elegible exige que la IA generativa se use para sistematizar/clasificar/resumir el contenido de los aportes de los diagnosticos participativos (Consejos de Desarrollo COCODES/COMUDES) en los Planes de Desarrollo Municipal (PDM). Toda la evidencia primaria y secundaria (nota SEGEPLAN ?p=14176 del 04-nov-2025; nota ?p=14622 comunidad de practica feb-2026; blog Red Ciudadana; blog PNUD/unsdg 'IA inclusiva para el desarrollo municipal') describe la plataforma como (a) herramienta interna de productividad con 'agentes' para 'tareas repetitivas', (b) analisis de datos/documentos institucionales para estadisticas y alertas sobre la 'papeleria', y (c) un proceso de fortalecimiento de capacidades / comunidad de practica del equipo tecnico. Coincide exactamente con la exclusion del criterio ('solo herramienta interna de productividad/capacitacion del equipo tecnico o comunidad de practica sin aplicarse a los aportes'). Aunque SEGEPLAN es el ente rector de los PDM (que si integran aportes de COCODES/COMUDES) y la linea del PNUD prototipa soluciones municipales (atencion ciudadana, catastro, ordenamiento territorial), no se halla ninguna cita que conecte la IA con el tratamiento del contenido de los aportes participativos. Se decide entra=NOapoyo',no'). Confirma la tendencia previa , resuelta a no con evidencia multiple.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
+          <t>https://portal.segeplan.gob.gt/segeplan/?p=14176</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>LATAM-EXC-botivist</t>
+          <t>GT-segeplan-plataforma-ia-generativa</t>
         </is>
       </c>
     </row>
@@ -6446,22 +6190,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
+          <t>ANTAI Smart CID (Autoridad Nacional de Transparencia y Acceso a la Información + OS City)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
+          <t>https://www.caf.com/es/actualidad/noticias/2021/07/caf-realiza-su-primera-inversion-en-una-govtech-latinoamericana/</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>LATAM-EXC-chatbot-dci-denuncia-ciudadana-idonea</t>
+          <t>LATAM-EXC-antai-smart-cid-autoridad-nacional-de-tr</t>
         </is>
       </c>
     </row>
@@ -6473,22 +6217,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
+          <t>Botivist</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Análisis de redes sociales, no es participación.</t>
+          <t>No tiene foco en un país específico.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
+          <t>https://www.microsoft.com/en-us/research/publication/botivist-calling-volunteers-to-action-using-online-bots/</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>LATAM-EXC-citibeats-covid-19-percepciones-ciudadan</t>
+          <t>LATAM-EXC-botivist</t>
         </is>
       </c>
     </row>
@@ -6500,76 +6244,76 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Ushahidi "AI for Good"</t>
+          <t>Chatbot DCI (Denuncia Ciudadana Idónea)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam.</t>
+          <t>No evidencia de uso de IA.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://www.ushahidi.com/</t>
+          <t>https://www.policylab.tech/post/revolucionando-la-denuncia-ciudadana-en-am%C3%A9rica-latina-con-tecnolog%C3%ADa-el-caso-del-chatbot-dci-1</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>LATAM-EXC-ushahidi-ai-for-good</t>
+          <t>LATAM-EXC-chatbot-dci-denuncia-ciudadana-idonea</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>AMIMgo</t>
+          <t>Citibeats: Covid-19 (“Percepciones ciudadanas COVID-19”)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Análisis de redes sociales, no es participación.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
+          <t>https://forbescentroamerica.com/2021/04/28/civiclytics-el-big-data-apoya-la-recuperacion-economica</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-amimgo</t>
+          <t>LATAM-EXC-citibeats-covid-19-percepciones-ciudadan</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>LATAM</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ATIC</t>
+          <t>Ushahidi "AI for Good"</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>No se evidencia el uso de IA en los proyectos de participación listados para Latam.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
+          <t>https://www.ushahidi.com/</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-atic</t>
+          <t>LATAM-EXC-ushahidi-ai-for-good</t>
         </is>
       </c>
     </row>
@@ -6581,22 +6325,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>ChatBot “Claudia"</t>
+          <t>AMIMgo</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>No es participación.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
+          <t>https://amim.mx/noticias/detalle/estrena-amim-chatbot-para-la-atencion-ciudadana</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-chatbot-claudia</t>
+          <t>MX-EXC-amimgo</t>
         </is>
       </c>
     </row>
@@ -6608,22 +6352,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Chatbot "Inés"</t>
+          <t>ATIC</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>No es participación, es informativo.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
+          <t>https://oem.com.mx/la-prensa/metropoli/info-cdmx-implementa-atic-una-herramienta-con-ia-que-facilita-el-acceso-a-la-informacion-13081722</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-chatbot-ines</t>
+          <t>MX-EXC-atic</t>
         </is>
       </c>
     </row>
@@ -6635,22 +6379,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Sam Petrino</t>
+          <t>ChatBot “Claudia"</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>No es participación.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
+          <t>https://mexicocomovamos.mx/animal-politico/2024/08/chatbot-claudia-una-herramienta-de-participacion-ciudadana/</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-chatbot-sam-petrino</t>
+          <t>MX-EXC-chatbot-claudia</t>
         </is>
       </c>
     </row>
@@ -6662,22 +6406,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Chatbot Victoria</t>
+          <t>Chatbot "Inés"</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>No es participación, es informativo.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
+          <t>https://centralelectoral.ine.mx/2024/04/17/nueva-version-del-chatbot-del-ine-en-whatsapp-permitira-verificar-informacion-sobre-elecciones-2024/</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-chatbot-victoria</t>
+          <t>MX-EXC-chatbot-ines</t>
         </is>
       </c>
     </row>
@@ -6689,22 +6433,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
+          <t>Chatbot Sam Petrino</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://www.civica.digital/historias/chatbot-sam-petrino</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-inaoe-conacyt-laboratorio-de-tecnologias</t>
+          <t>MX-EXC-chatbot-sam-petrino</t>
         </is>
       </c>
     </row>
@@ -6716,22 +6460,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
+          <t>Chatbot Victoria</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero no hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas. Sin uso de IA.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
+          <t>https://adip.cdmx.gob.mx/comunicacion/nota/la-adip-y-el-gobierno-de-la-ciudad-presentan-victoria-el-robot-que-colaborara-en-la-atencion-de-la-ciudadania</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>MX-jalisco-armemos-un-plan</t>
+          <t>MX-EXC-chatbot-victoria</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6487,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Movimex</t>
+          <t>INAOE (Conacyt) – Laboratorio de Tecnologías del Lenguaje</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -6753,12 +6497,12 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-movimex</t>
+          <t>MX-EXC-inaoe-conacyt-laboratorio-de-tecnologias</t>
         </is>
       </c>
     </row>
@@ -6770,22 +6514,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Sistema *0311 Locatel</t>
+          <t>Jalisco - Consulta ¡Armemos un Plan! (Plan Estatal de Desarrollo y Gobernanza 2024-2030)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Atención ciudadana.</t>
+          <t>Proceso participativo real y masivo (675.484 participaciones; 15.899 propuestas), pero no hay evidencia de uso de IA para analizar/agrupar/clasificar el contenido de las propuestas. Sin uso de IA.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
+          <t>https://armemosunplan.mx/propuestas-ciudadanas/</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-sistema-0311-locatel</t>
+          <t>MX-jalisco-armemos-un-plan</t>
         </is>
       </c>
     </row>
@@ -6797,22 +6541,22 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Sufragio seguro</t>
+          <t>Movimex</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Integridad/proceso electoral, no contenido.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
+          <t>https://animalpolitico.com/estados/chatbot-movimex-tramites-denuncias-edomex</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>MX-sufragio-seguro</t>
+          <t>MX-EXC-movimex</t>
         </is>
       </c>
     </row>
@@ -6824,211 +6568,211 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Violetta</t>
+          <t>Sistema *0311 Locatel</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>Atención ciudadana.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://holasoyvioletta.com/acerca-de/</t>
+          <t>https://research.latinxinai.org/papers/naacl/2022/pdf/paper_01.pdf</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MX-EXC-violetta</t>
+          <t>MX-EXC-sistema-0311-locatel</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Dr. ROSA y Dr. NICO</t>
+          <t>Sufragio seguro</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Integridad/proceso electoral, no contenido.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://algoritmoscide.org/proyectos/sufragio-seguro/</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>PA-EXC-dr-rosa-y-dr-nico</t>
+          <t>MX-sufragio-seguro</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>JNE WhatsApp Chatbot</t>
+          <t>Violetta</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
+          <t>https://holasoyvioletta.com/acerca-de/</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>PE-EXC-jne-whatsapp-chatbot</t>
+          <t>MX-EXC-violetta</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
+          <t>Dr. ROSA y Dr. NICO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>PE-sistema-de-computo-con-ia-para-las-elecc</t>
+          <t>PA-EXC-dr-rosa-y-dr-nico</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
+          <t>JNE WhatsApp Chatbot</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>El criterio elegible exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) sobre el contenido de los aportes. Aquí ocurre lo contrario: la IA es el tema de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y el análisis de los aportes es de encuestas/mixed-methods tradicional: recoleccion via formularios (Microsoft Forms en la metodologia aila estandar), base de datos estructurada publicada en xls en Zenodo, puntajes ponderados y visualizacion (Power bi), con hallazgos presentados como cruces y correlaciones estadisticas (brecha urbano-rural; a mayor ingreso, mayor optimismo) y sintesis cualitativa de grupos focales/entrevistas. Se verifico especificamente la pista del equipo (¿se uso NLP/sentimiento/clustering o herramienta tipo Citibeats?) y no se hallo ninguna evidencia de ello en el blog del PNUD, en los reportes aila/nota metodologica ni en la prensa secundaria (La Tribuna, Foco/La Nacion, Forbes). Por tanto el analisis es cualitativo/estadistico tradicional y la IA solo es el tema =&gt; Confianza no maxima porque el blog PNUD y el pdf aila devolvieron http 403 a WebFetch/curl (proxy) y las citas verbatim se reconstruyeron via WebSearch; no obstante, multiples busquedas convergentes coinciden y ninguna menciona NLP sobre los aportes.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
+          <t>https://portal.jne.gob.pe/Portal/Pagina/Nota/12783</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>PY-consultas-ia-pnud-acclab</t>
+          <t>PE-EXC-jne-whatsapp-chatbot</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>PY</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ParaEmpleo</t>
+          <t>Sistema de cómputo con IA para las Elecciones Generales 2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>No es participación ciudadana.</t>
+          <t>Conteo electoral (OCR de actas): votación política, no participación.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://fairlac.iadb.org/en/paraempleo</t>
+          <t>https://andina.pe/agencia/noticia-onpe-utilizara-un-nuevo-sistema-computo-resultados-incorporara-ia-1021072.aspx</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>PY-EXC-paraempleo</t>
+          <t>PE-sistema-de-computo-con-ia-para-las-elecc</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Chatbot (Asistente virtual entrenado con IA)</t>
+          <t>Consultas ciudadanas sobre IA en Paraguay - PNUD Accelerator Lab (AccLab) + Columbia SIPA + MITIC / insumo del diagnóstico AILA (Atlas de IA)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Atencion ciudadana.</t>
+          <t>El criterio elegible exige que dentro de un proceso participativo convocado se use IA (NLP/ML/clustering/sentimiento) sobre el contenido de los aportes. Aquí ocurre lo contrario: la IA es el tema de la consulta (se pregunta a la ciudadania por su percepcion de la IA), y el análisis de los aportes es de encuestas/mixed-methods tradicional: recoleccion via formularios (Microsoft Forms en la metodologia aila estandar), base de datos estructurada publicada en xls en Zenodo, puntajes ponderados y visualizacion (Power bi), con hallazgos presentados como cruces y correlaciones estadisticas (brecha urbano-rural; a mayor ingreso, mayor optimismo) y sintesis cualitativa de grupos focales/entrevistas. Se verifico especificamente la pista del equipo (¿se uso NLP/sentimiento/clustering o herramienta tipo Citibeats?) y no se hallo ninguna evidencia de ello en el blog del PNUD, en los reportes aila/nota metodologica ni en la prensa secundaria (La Tribuna, Foco/La Nacion, Forbes). Por tanto el analisis es cualitativo/estadistico tradicional y la IA solo es el tema =&gt; Confianza no maxima porque el blog PNUD y el pdf aila devolvieron http 403 a WebFetch/curl (proxy) y las citas verbatim se reconstruyeron via WebSearch; no obstante, multiples busquedas convergentes coinciden y ninguna menciona NLP sobre los aportes.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
+          <t>https://www.undp.org/es/paraguay/blog/consultas-ciudadanas-sobre-ia-en-paraguay-visiones-diversas-entre-el-campo-y-la-ciudad</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>UY-EXC-chatbot-asistente-virtual-entrenado-con</t>
+          <t>PY-consultas-ia-pnud-acclab</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>UY</t>
+          <t>PY</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+          <t>ParaEmpleo</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>No evidencia de uso de IA.</t>
+          <t>No es participación ciudadana.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
+          <t>https://fairlac.iadb.org/en/paraempleo</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>UY-EXC-consulta-publica-de-la-estrategia-nacion</t>
+          <t>PY-EXC-paraempleo</t>
         </is>
       </c>
     </row>
@@ -7040,54 +6784,108 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+          <t>Chatbot (Asistente virtual entrenado con IA)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Temporal: la consulta está abierta hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis no se ha ejecutado, por lo que un eventual uso de IA sobre el contenido de los aportes no está demostrado ni desplegado. sustantivo: no se halló ninguna evidencia textual de que se use IA/NLP/ML/clustering para clasificar, agrupar, resumir o analizar el contenido de los aportes ciudadanos. Las descripciones oficiales del proceso (Agesic, misma Plataforma de Participación Ciudadana Digital / Decidim) apuntan a análisis humano por equipos técnicos ('los aportes recibidos se sistematizan y, analizada su viabilidad por equipos técnicos, se utilizan como insumos'; 'según su pertinencia, viabilidad y prioridad'), y el producto es un 'documento de síntesis' agregado. El precedente directo (Consulta Pública Estrategia Nacional de IA, uy, ya listado y excluido por 'No evidencia de uso de IA') usó análisis humano en esta misma plataforma. La IA es el tema/objeto de la consulta (impacto de la IA en la infancia), no una herramienta de procesamiento de los aportes. Por criterio (consulta abierta sin fase de análisis ejecutada + sin evidencia de IA sobre los aportes) -&gt; no.</t>
+          <t>Atencion ciudadana.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+          <t>https://www.oecd.org/es/publications/uso-estrategico-y-responsable-de-la-inteligencia-artificial-en-el-sector-publico-de-america-latina-y-el-caribe_5b189cb4-es/full-report.html</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UY-consulta-infancia-ia-2026</t>
+          <t>UY-EXC-chatbot-asistente-virtual-entrenado-con</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública de la Estrategia Nacional de Inteligencia Artificial (IA) de Uruguay 2024–2030,</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>No evidencia de uso de IA.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/agencia-gobierno-electronico-sociedad-informacion-conocimiento/comunicacion/publicaciones/estrategia-nacional-inteligencia-artificial-2024-2030</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>UY-EXC-consulta-publica-de-la-estrategia-nacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>UY</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Consulta Pública y Participación Multiactores: "Niñas, niños, adolescentes, entornos digitales e inteligencia artificial" (Uruguay, 2026)</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Temporal: la consulta está abierta hasta el 10/09/2026 y la fase de sistematización/análisis/validación (Fase 3) recién ocurre entre el 10/09 y el 10/10/2026, con informe final el 30/11/2026. A la fecha de evaluación (2026-07-01) la fase de análisis no se ha ejecutado, por lo que un eventual uso de IA sobre el contenido de los aportes no está demostrado ni desplegado. sustantivo: no se halló ninguna evidencia textual de que se use IA/NLP/ML/clustering para clasificar, agrupar, resumir o analizar el contenido de los aportes ciudadanos. Las descripciones oficiales del proceso (Agesic, misma Plataforma de Participación Ciudadana Digital / Decidim) apuntan a análisis humano por equipos técnicos ('los aportes recibidos se sistematizan y, analizada su viabilidad por equipos técnicos, se utilizan como insumos'; 'según su pertinencia, viabilidad y prioridad'), y el producto es un 'documento de síntesis' agregado. El precedente directo (Consulta Pública Estrategia Nacional de IA, uy, ya listado y excluido por 'No evidencia de uso de IA') usó análisis humano en esta misma plataforma. La IA es el tema/objeto de la consulta (impacto de la IA en la infancia), no una herramienta de procesamiento de los aportes. Por criterio (consulta abierta sin fase de análisis ejecutada + sin evidencia de IA sobre los aportes) -&gt; no.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gub.uy/ministerio-educacion-cultura/comunicacion/noticias/lanzamiento-consulta-publica-sobre-inteligencia-artificial-entornos-digitales</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>UY-consulta-infancia-ia-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>VE</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Plan de la Patria 7 Transformaciones (7T) - IA y Big Data en la sistematización de propuestas de la Consulta Popular</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>No (resuelto en , antes duda). Hay un proceso participativo claro (consulta/debate nacional para construir el Plan de la Patria 7T, con +63.000 asambleas, 3,4 M de participantes y 34.491 propuestas) cuyo contenido sí fue recolectado, cargado, sistematizado y agrupado. Pero la confirma que el actor del análisis fue humano + herramientas informáticas de clasificación + sig, no IA: la metodología oficial (corroborada en múltiples resultados que indexan el documento del Plan 7T) describe que las propuestas fueron 'revisadas una por una por el equipo de sistematización, con el apoyo de herramientas informáticas especializadas' y clasificadas en cuatro categorías, y que 'el relator sistematiza las propuestas concretas de la mesa validando con los participantes', con tres niveles de agregación. La única afirmación de que 'IA y Big Data procesaron 500.000+ propuestas' sigue proviniendo solo de prensa estatal/oficialista (Correo del Orinoco y mirrors mincyt, Cendit, fevp, mppre, más un diario regional), sin proveedor, sin descripción técnica (ningún modelo, NLP, ML, clustering), contradiciendo la cifra oficial verificable (34.491) y con la coletilla 'para generar los algoritmos' que apunta a la IA como producto del Plan Nacional de IA, no como herramienta sobre los aportes. no se halló ninguna corroboración técnica independiente (proveedor de software, paper académico, documento técnico, organismo) tras 6-10 búsquedas dirigidas; fuentes críticas/académicas (Small Wars Journal/asu, Data Big and Small, GISWatch, Bentata) tratan la agenda de IA soberana y la infraestructura de datos, pero ninguna corrobora IA sobre las propuestas de la consulta. Adicionalmente, 'incluir la IA en el Plan de las 7T' describe a la IA como eje temático/prioridad del plan; por la regla del índice, eje temático ≠ elegibilidad. Conclusión binaria: no, por ausencia de corroboración técnica creíble de IA (NLP/ML) procesando el contenido de las propuestas. Dato verificable que queda en su lugar: 34.491 propuestas sistematizadas por relatores humanos + herramientas de clasificación + sig. url de prensa estatal marcada en gaps para revisión manual.</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>http://www.correodelorinoco.gob.ve/venezuela-impulsa-el-debate-sobre-inteligencia-artificial-bajo-principios-de-soberania-y-etica/</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>VE-plan-de-la-patria-7-transformaciones-ia</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E73"/>
+  <autoFilter ref="A1:E75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7098,7 +6896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7421,87 +7219,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cátedra Brasil / Co:Lab USP - IA generativa en presupuesto participativo (SP)</t>
+          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Co:Lab / Colaboratório de Desenvolvimento e Participação (COLAB-USP) opera na USP Leste (EACH-USP), São Paulo, Brasil. (Localización institucional confirmada por colab.each.usp.br; no cita textual exacta recuperable por bloqueo 403 de la página.)</t>
+          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí, em parceria com a Colab. (Colab, 'OPA, Colab e a participação digital no Piauí')</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>No projeto da Cátedra Brasil, há o orçamento participativo da cidade em que cidadãos podem dar sugestões sobre o orçamento público com auxílio da inteligência artificial. (snippet de búsqueda sobre jornal.usp.br / Cátedra Brasil)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>um cidadão pode propor uma rede de ciclovias na zona leste de São Paulo e a IA o ajuda a escrever essa proposta, fazendo perguntas sobre seus objetivos. (snippet de búsqueda; describe el apoyo de IA en la fase de generación/redacción de la propuesta)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>A IA Generativa e o Futuro da Participação Cidadã: Pesquisas em Andamento (título del post Co:Lab, 2025-03-28; 'pesquisas em andamento' = investigación en curso)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Co:Lab USP has a research project titled 'A IA Generativa e o Futuro da Participação Cidadã: Pesquisas em Andamento' ... updated as of March 28, 2025. (snippet; encuadra como proyecto de investigación, sin ediciones recurrentes ni despliegue)</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>José Carlos Vaz, from the USP Public Policy Management course / professor at the University of São Paulo's School of Arts, Sciences and Humanities (EACH) ... coordinates GETIP. (snippet; convocante = universidad USP)</t>
-        </is>
-      </c>
+          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>AI could help generate proposals based on knowledge databases and transform them into legally viable drafts / a IA o ajuda a escrever essa proposta. (snippet; rol sobre el contenido del aporte, pero en marco de investigación)</t>
+          <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>https://colab.each.usp.br/blog/2025/03/28/a-ia-generativa-e-o-futuro-da-participacao-cidada-pesquisas-em-andamento/
-https://jornal.usp.br/radio-usp/ia-tem-potencial-para-ampliar-participacao-politica-online-e-auxiliar-gestores-em-decisoes/
-https://scope.uni-muenster.de/wp-content/uploads/2025/01/PT-BR-Policy-Brief-AI_Jan2025.pdf
-https://colab.each.usp.br/projetos-em-andamento-2/
-https://participemais.prefeitura.sp.gov.br/budgets</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí, em parceria com a Colab. (Colab, 'OPA, Colab e a participação digital no Piauí')</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/
 https://sia.pi.gov.br/projetos/opa/
@@ -7515,6 +7256,63 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Plan Plurianual de la ciudad de Natal</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Plataforma</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -7523,7 +7321,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -7538,12 +7336,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Traducción Política</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
+          <t>reconfirmado web (institucional): Reconfirmado 2025: la IA analiza transcripciones de 1.800+ audiencias y marca 2.700+ preguntas ciudadanas como respondidas.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7553,22 +7351,23 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+          <t>Senado Federal de Brasil</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias
+https://ipen-network.org/spotlight-on-public-engagement-practice-brazil/</t>
         </is>
       </c>
     </row>
@@ -7580,108 +7379,50 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>Programa de Metas 2025-2028, PPA e PAS 2026-2029 - portal Participe Mais da Prefeitura de São Paulo (participemais.prefeitura.sp.gov.br/legislation/processes/323).</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Governanza Colaborativa</t>
+          <t>as sugestões enviadas pela população para o PPA (Plano Plurianual) 2026-2029, durante a consulta pública do Programa de Metas no portal Participe Mais, que é a plataforma de participação social da Prefeitura</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política</t>
+          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios, facilitando a divulgação das propostas. (...) exibição dos relatórios e painéis visuais gerados pela análise destacam: ranking dos temas mais recorrentes; participação em cada distrito e subprefeitura</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado 2025: la IA analiza transcripciones de 1.800+ audiencias y marca 2.700+ preguntas ciudadanas como respondidas.</t>
+          <t>Após o Ciclo Participativo, com 36 audiências públicas híbridas pela cidade (abril e maio), recebimento de 6.368 propostas e mais de 31 mil interações dos cidadãos (...) através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
+          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios (...) No desenvolvimento da ferramenta foram utilizados conhecimentos em dados abertos, inteligência artificial e gestão pública.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Senado Federal de Brasil</t>
+          <t>através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
+          <t>A metodologia demonstra a solução com exposição de trechos de código e explicação das tecnologias utilizadas: Python, Pandas, Google Gemini. (...) desafios reais encontrados, como o alto volume de dados, otimização do tempo de análise e ajustes necessários nos comandos para a Inteligência Artificial</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
+          <t>uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias
-https://ipen-network.org/spotlight-on-public-engagement-practice-brazil/</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Programa de Metas 2025-2028, PPA e PAS 2026-2029 - portal Participe Mais da Prefeitura de São Paulo (participemais.prefeitura.sp.gov.br/legislation/processes/323).</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>as sugestões enviadas pela população para o PPA (Plano Plurianual) 2026-2029, durante a consulta pública do Programa de Metas no portal Participe Mais, que é a plataforma de participação social da Prefeitura</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios, facilitando a divulgação das propostas. (...) exibição dos relatórios e painéis visuais gerados pela análise destacam: ranking dos temas mais recorrentes; participação em cada distrito e subprefeitura</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Após o Ciclo Participativo, com 36 audiências públicas híbridas pela cidade (abril e maio), recebimento de 6.368 propostas e mais de 31 mil interações dos cidadãos (...) através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios (...) No desenvolvimento da ferramenta foram utilizados conhecimentos em dados abertos, inteligência artificial e gestão pública.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>A metodologia demonstra a solução com exposição de trechos de código e explicação das tecnologias utilizadas: Python, Pandas, Google Gemini. (...) desafios reais encontrados, como o alto volume de dados, otimização do tempo de análise e ajustes necessários nos comandos para a Inteligência Artificial</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
 https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/cursos-anteriores/cursos-realizados-em-2025/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
@@ -7697,58 +7438,58 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Cidadãos ajudam a escrever projetos de lei com ferramenta de inteligência artificial — Senado Notícias (Senado Federal, Brasil), 16/01/2026.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado permite que ideias enviadas ao portal e-Cidadania influenciem projetos de lei — mesmo quando não atingem o número mínimo de apoios antes exigido</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão. As ideias selecionadas podem ser incorporadas ao projeto e citadas em sua justificação</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>IA vai aproximar ideias legislativas do e-Cidadania a projetos de senadores — Rádio Senado, 15/01/2026 (matéria de divulgação da ferramenta em uso no início de 2026)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>O primeiro resultado já veio: uma sugestão enviada por Cândida Magalhães, de São Paulo, que pedia atendimento psicológico gratuito para filhos de mulheres vítimas de violência doméstica, foi identificada pela ferramenta e incorporada a um projeto de lei: o PL 6.125/2025</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Quando um senador pede ajuda à Consultoria Legislativa para elaborar um projeto, a equipe de consultores solicita ao e-Cidadania uma lista de sugestões feitas pelos cidadãos. Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial
 https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/
@@ -7760,58 +7501,58 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Cabildos 2016</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (academico): Evidencia académica del NLP sobre los cabildos 2016: argument mining sobre 240.468 argumentos (ACL 2017, UChile/DCC) y Structural Topic Modeling (PLOS One 2022)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
 https://aclanthology.org/W17-5101/
@@ -7819,58 +7560,58 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos cierra etapa de diálogos con más de 130 mil participantes en las 345 comunas del país (titular de noticia del Ministerio de Desarrollo Social y Familia - Gobierno de Chile).</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó la iniciativa el viernes 22 de noviembre de 2019. La participación fue posible hasta el 31 de marzo a través de diálogos ciudadanos o consultas individuales en www.chilequequeremos.cl (gob.cl).</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Este repositorio contiene los procedimientos para realizar la clasificación de las contribuciones con redes neuronales (README del repositorio MinCiencia/ECQQ, carpeta contributions_rnn).</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020. La decisión de concluir anticipadamente los diálogos ciudadanos fue parte de las medidas del gobierno para frenar la propagación del COVID-19, aunque la plataforma permaneció abierta hasta el 31 de marzo de 2020.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020 (proceso único, una sola edición).</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó 'El Chile que Queremos', iniciativa de diálogos y escucha social para avanzar en nuevas propuestas para el país. La iniciativa fue un esfuerzo conjunto entre los Ministerios de Desarrollo Social y Familia, de Ciencia, Tecnología, Conocimiento e Innovación, de Agricultura, la Secretaría General de Gobierno y la División de Gobierno Digital (gob.cl / desarrollosocialyfamilia.gob.cl).</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>La información recibida de la ciudadanía es sistematizada por el Ministerio de Ciencias, siendo la ciencia de datos una herramienta clave para este amplio y participativo ejercicio de escucha. / clasificación de las contribuciones con árboles de decisión (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Grouping Emotions.ipynb que sirve para sistematizar las Emociones / Analisis de Topicos - Necesidades.ipynb que sirve para sistematizar tanto las necesidades personales como las del país (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://github.com/MinCiencia/ECQQ
 https://www.desarrollosocialyfamilia.gob.cl/noticias/el-chile-que-queremos-cierra-etapa-de-dialogos-con-mas-de-130-mil-participantes-en-las-345-comunas-d
@@ -7882,6 +7623,64 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Secretaría de Gobierno Digital</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
+https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -7890,7 +7689,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+          <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -7905,7 +7704,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación, Análisis</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7920,23 +7719,23 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Gobierno Digital</t>
+          <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+          <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
+          <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
-https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
+          <t>https://estudiodialogos.cl/
+https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7747,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Estudio dIAlogos - Percepciones de Futuro</t>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -7963,7 +7762,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -7978,23 +7777,23 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Fundación Encuentros del Futuro y Merlín Research</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Realización de entrevistas y codificación de respuestas</t>
+          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Realización de entrevistas y codificación de respuestas</t>
+          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>https://estudiodialogos.cl/
-https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
+          <t>https://ipp.unab.cl/
+https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
@@ -8006,104 +7805,46 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+          <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+          <t>In 2020, the Senate of Chile partnered with the Stanford Center for Deliberative Democracy to involve citizens in the online deliberative process 'LXS 400 - Chile Delibera' performed through the Stanford Online Deliberation Platform. (OCDE 2025, 'AI in civic participation and open government')</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Governanza Colaborativa</t>
+          <t>Over 500 citizens representative of the Chilean society discussed in small groups and deliberated in plenary sessions on health and pension reforms. (OCDE 2025) / Entre el 5 y el 7 de marzo, 400 personas seleccionadas a traves de una metodologia aleatoria y representativas de todo Chile se reunieron para deliberar sobre dos de los temas publicos mas importantes para el pais: pensiones y salud.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
+          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
+          <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>La iniciativa fue impulsada por la Fundacion Tribu; el Senado a traves de la Comision de Desafios del Futuro; la Asociacion Chilena de Municipalidades; la Universidad de Chile; y el Centro para la Democracia Deliberativa de la Universidad de Stanford.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
+          <t>The platform used an AI tool to keep time and distribute speaking rights equitably... (OCDE 2025) [confirma que SI se uso IA dentro del proceso, en rol de facilitacion/logistica].</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
+          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / An automated moderator controls perspective elicitation, with an automated cue system to determine which participant to elicit a perspective from next and an automated timer to determine how long each participant has to state their perspective. (descripcion de la Stanford Online Deliberation Platform)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>https://ipp.unab.cl/
-https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>LXS 400 - Chile Delibera</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>In 2020, the Senate of Chile partnered with the Stanford Center for Deliberative Democracy to involve citizens in the online deliberative process 'LXS 400 - Chile Delibera' performed through the Stanford Online Deliberation Platform. (OCDE 2025, 'AI in civic participation and open government')</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Over 500 citizens representative of the Chilean society discussed in small groups and deliberated in plenary sessions on health and pension reforms. (OCDE 2025) / Entre el 5 y el 7 de marzo, 400 personas seleccionadas a traves de una metodologia aleatoria y representativas de todo Chile se reunieron para deliberar sobre dos de los temas publicos mas importantes para el pais: pensiones y salud.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>La iniciativa fue impulsada por la Fundacion Tribu; el Senado a traves de la Comision de Desafios del Futuro; la Asociacion Chilena de Municipalidades; la Universidad de Chile; y el Centro para la Democracia Deliberativa de la Universidad de Stanford.</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>The platform used an AI tool to keep time and distribute speaking rights equitably... (OCDE 2025) [confirma que SI se uso IA dentro del proceso, en rol de facilitacion/logistica].</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / An automated moderator controls perspective elicitation, with an automated cue system to determine which participant to elicit a perspective from next and an automated timer to determine how long each participant has to state their perspective. (descripcion de la Stanford Online Deliberation Platform)</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html
 https://deliberation.stanford.edu/news/lxs-400-national-deliberative-poll-chile
@@ -8115,6 +7856,64 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>La voz de los nuevos votantes</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Universidad Andres Bello</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
+https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
@@ -8123,7 +7922,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>La voz de los nuevos votantes</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -8138,7 +7937,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -8153,23 +7952,22 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Secretaría de Participación Ciudadana</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
-https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
     </row>
@@ -8181,7 +7979,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -8211,22 +8009,23 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Participación Ciudadana</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://www.tenemosquehablardechile.cl/
+https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8037,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -8268,78 +8067,20 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
+          <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
+          <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tenemosquehablardechile.cl/
-https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Universidad Andres Bello</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>Análisis temático de las transcripciones de las mesas</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Análisis temático de las transcripciones de las mesas</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
@@ -8347,58 +8088,58 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares, Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2024-2028: NLP y tecnologías semánticas procesaron 147.422 participaciones (10% propuestas libres) para el Plan Distrital de Desarrollo. Citado por</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
@@ -8406,6 +8147,63 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -8414,53 +8212,49 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats + PNUD Colombia (analítica de datos para la deliberación pública juvenil)</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Data analytics to improve public deliberation in Colombia (UNDP Colombia / El PNUD en Colombia, blog, Bogotá, Colombia).</t>
+          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats facilita la comprensión social de la situación actual de Colombia mediante el monitoreo y seguimiento en tiempo real de las opiniones y propuestas expresadas en espacios digitales y presenciales, buscando identificar los principales tópicos de interés de la población.</t>
+          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Citibeats utiliza algoritmos que combinan NLP (Procesamiento de Lenguaje Natural) y ML (Machine Learning), filtrando contenido relevante de distintas fuentes de datos abiertas (Twitter, Facebook, Instagram, foros, blogs, noticias y comentarios de video), clasificando las opiniones e información de los usuarios en categorías y extrayendo conocimiento y patrones de forma automática, en tiempo real.</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>El PNUD Colombia está experimentando con Citibeats, una plataforma de inteligencia artificial (IA) ética y responsable. (proyecto descrito como experimentación/piloto del Laboratorio de Aceleración, diciembre 2021).</t>
-        </is>
-      </c>
+          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>El Programa de las Naciones Unidas para el Desarrollo (PNUD) en Colombia está experimentando con Citibeats... La tecnologia sirve como un habilitador que permite acelerar la comprensión social respecto a los espacios de deliberación pública y las propuestas, necesidades y preocupaciones de la juventud colombiana.</t>
+          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>El PNUD y aliados estratégicos, como El Avispero, han generado espacios presenciales para contrastar lo que se dice en las conversaciones en línea, donde los jóvenes destacan preocupaciones sobre la corrupción en el país, la necesidad de prevenir la violencia de género y la importancia de promover la educación.</t>
+          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>El proyecto de comprensión ciudadana analizó 2.129.502 documentos. Las principales categorías de conversación en Colombia giraron en torno a Paz y Justicia, Gobernanza e Inclusión Social.</t>
+          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/colombia/blog/analitica-de-datos-para-mejorar-la-deliberacion-publica-en-colombia
-https://www.undp.org/es/colombia/blog/data-analytics-improve-public-deliberation-colombia
-https://www.co.undp.org/content/colombia/es/home/Blog/2021/diciembre/data-analytics-to-improve-public-deliberation-in-colombia.html
-https://www.undp.org/es/colombia/press-releases/universidades-p%C3%BAblicas-y-privadas-la-iglesia-cat%C3%B3lica-en-bogot%C3%A1-y-el-pnud-habilitan-una-plataforma-presencial-y-virtual-para
-https://blogthinkbig.com/citibeats-datos-objetivos-en-tiempo-real-para-un-impacto-social-positivo
-https://www.linkedin.com/posts/matteo-mezzanotte-67412817_latam-colombian-undp-activity-6879002241148170241-oxKI</t>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
+https://www.kienyke.com/</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8266,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -8487,12 +8281,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Implementación, Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+          <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8502,189 +8296,78 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://tenemosquehablarcolombia.co/
+https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
+          <t>Para agilizar la recogida y el procesamiento de los criterios, la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN) [proceso de consulta popular del Código de las Familias en Cuba].</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
+          <t>consulta popular del proyecto del Código de las Familias (...) la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
+          <t>luego se sube a GEMA-CEN (también operado por especialistas) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares, facilitando el trabajo y evitando errores. GEMA-CEN permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr"/>
+          <t>Más de seis millones 481 mil personas participaron en las reuniones (...) la consulta popular del proyecto del Código de las Familias (...) convocada entre febrero y abril [de 2022]; del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título, conformadas a partir de la asociación de propuestas idénticas y de aquellas con redacción diferente pero referidas al mismo criterio u opinión</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
+          <t>La consulta popular (...) fue organizada y supervisada por el Consejo Electoral Nacional (CEN) [órgano del Estado cubano]; los resultados se entregaron al Parlamento (Asamblea Nacional) y a su Comisión redactora</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
+          <t>se sube a GEMA-CEN (...) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares (...) permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
+          <t>GEMA es una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información (...) complementando los resultados mediante técnicas modernas de recuperación de información para obtener archivos similares, eliminar resultados no relevantes y agrupar documentos comunes</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
-https://www.kienyke.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Tenemos que hablar de Colombia</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>https://tenemosquehablarcolombia.co/
-https://tenemosquehablarcolombia.co/resultados/</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CU</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Para agilizar la recogida y el procesamiento de los criterios, la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN) [proceso de consulta popular del Código de las Familias en Cuba].</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>consulta popular del proyecto del Código de las Familias (...) la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN)</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>luego se sube a GEMA-CEN (también operado por especialistas) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares, facilitando el trabajo y evitando errores. GEMA-CEN permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Más de seis millones 481 mil personas participaron en las reuniones (...) la consulta popular del proyecto del Código de las Familias (...) convocada entre febrero y abril [de 2022]; del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título, conformadas a partir de la asociación de propuestas idénticas y de aquellas con redacción diferente pero referidas al mismo criterio u opinión</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>La consulta popular (...) fue organizada y supervisada por el Consejo Electoral Nacional (CEN) [órgano del Estado cubano]; los resultados se entregaron al Parlamento (Asamblea Nacional) y a su Comisión redactora</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>se sube a GEMA-CEN (...) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares (...) permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>GEMA es una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información (...) complementando los resultados mediante técnicas modernas de recuperación de información para obtener archivos similares, eliminar resultados no relevantes y agrupar documentos comunes</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>http://www.datys.cu/spa/site/product/15
 https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
@@ -8696,60 +8379,60 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/
@@ -8757,58 +8440,58 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
@@ -8816,115 +8499,115 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>HN</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -8937,111 +8620,111 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Presupuesto CRECES</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Activo</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Ayundamiento de Hermosilla</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -9052,58 +8735,58 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
@@ -9112,54 +8795,54 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -9181,54 +8864,54 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -9236,7 +8919,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/gates/base_completa_ILIA2026.xlsx
+++ b/data/gates/base_completa_ILIA2026.xlsx
@@ -1407,12 +1407,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política</t>
+          <t>Traducción Política; Análisis</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; LLM; NLP</t>
+          <t>Voz a Texto; LLM; NLP; Búsqueda semántica</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">

--- a/data/gates/base_completa_ILIA2026.xlsx
+++ b/data/gates/base_completa_ILIA2026.xlsx
@@ -12,9 +12,9 @@
     <sheet name="3 · Evidencia y fuentes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos que entran'!$A$1:$Z$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'1 · Casos que entran'!$A$1:$Z$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2 · Excluidos'!$A$1:$E$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Evidencia y fuentes'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'3 · Evidencia y fuentes'!$A$1:$K$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z34"/>
+  <dimension ref="A1:Z35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
+          <t>Meta Community Forum on Generative AI — cohorte Brasil (Deliberative Polling, Stanford)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
+          <t>Foro comunitario deliberativo (Deliberative Polling®) sobre principios para los chatbots de IA generativa, realizado el 28-29 de octubre de 2023 en la Stanford Online Deliberation Platform con 1.545 participantes de muestras científicas de Brasil, Alemania, España y ee.uu. Formato: grupos pequeños de 8-12 personas (166 grupos, con grupo de control por país), panel de expertos en plenario, cuadernillo informativo (~50 págs.) y 44 preguntas de opinión pre/post. Los resultados (publicados abr-2024) incluyen hallazgos específicos de Brasil (p. ej., fuerte oposición a relaciones románticas humano-chatbot; énfasis en perspectivas locales en las fuentes de la IA). Meta declaró que los resultados 'ayudaron a dar forma a algunas de las decisiones más fundamentales' del diseño de sus productos de IA generativa.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Participación Digital</t>
+          <t>Mini públicos</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1164,21 +1164,21 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>empresa; universidad</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1188,20 +1188,24 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Según el material de Colab, en la edición 2025-2026 / 2026-2027 la IA agilizó la fase de análisis y 'reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón en costos directos y 99,98% de disponibilidad del sistema incluso en picos de votación. Una fuente describe además que 'a inteligência artificial foi utilizada para filtrar conexões inseguras' mediante AWS CloudFront (seguridad/infraestructura). El uso adicional de IA en torno al opa es un chatbot creado en el curso CapacitIA y el 'Observatório do opa' (transparencia/monitoreo). no hay evidencia textual de que la IA clasifique por temas, agrupe (clustering), priorice o sintetice el contenido de las propuestas del opa; la 'análise técnica' (documentación, viabilidad de ejecución, claridad, adecuación al área temática, no duplicación) se describe de forma reiterada y convergente como tarea de 'equipes técnicas' conducida a través de la plataforma. La única atribución hallada de IA que 'agrupa ideias semelhantes / estrutura propostas por eixo temático' corresponde a otro proceso (Diálogos pelo Piauí / revisión del PPA 2024-2027, talleres presenciales en 12 Territórios de Desenvolvimento), no al opa, y ni siquiera pudo confirmarse verbatim para Diálogos.</t>
+          <t>Moderación/facilitación automatizada de la deliberación en grupos pequeños: administración de turnos de palabra, colas de habla y tiempos por agenda (apoyo logístico a la implementación del mini-público).</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>No identificado por nombre. Capacidad de IA integrada en la plataforma Colab Gov (govtech Colab) sobre infraestructura AWS. En el OPA, la IA se asocia a la 'análise'/'processamento' de propuestas (agilización, -40% de tiempo), al filtrado de conexiones inseguras vía AWS CloudFront (seguridad/infraestructura), a un chatbot construido en un curso CapacitIA y a un 'Observatório do OPA' (panel de transparencia). La infraestructura AWS descrita es de cómputo/almacenamiento/seguridad (Amazon EC2, Amazon RDS, AWS CloudFront), no servicios de ML de contenido. No se especifica modelo, técnica (NLP, clustering, LLM) ni que la IA actúe sobre el contenido semántico de las propuestas del OPA. La plataforma Colab Gov.AI (lanzada en oct/2025 con AWS, basada en IA generativa/LangChain) ofrece funciones genéricas (generar flujos de servicio, etiquetar demandas en dashboards, asistir al ciudadano a redactar propuestas), pero ninguna de estas se atribuye específicamente al análisis de contenido de las propuestas del OPA Piauí.</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>Stanford Online Deliberation Platform (Crowdsourced Democracy Team + Deliberative Democracy Lab, Stanford): plataforma con moderador automatizado que gestiona turnos y colas de palabra y agendas temporizadas en los grupos pequeños — la misma plataforma del caso 'LXS 400 - Chile Delibera' (2021).</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>no-claro</t>
@@ -1209,12 +1213,12 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
@@ -1224,12 +1228,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>Governo do Estado do Piauí - Secretaria do Planejamento (SEPLAN), con apoyo de la Secretaria de Relações Sociais (Seres). Socio tecnológico: GovTech Colab (plataforma Colab Gov); infraestructura: AWS (Amazon Web Services).</t>
+          <t>Meta (convocante/financista) + Stanford Deliberative Democracy Lab (diseño y ejecución del Deliberative Polling®) + Behavioural Insights Team (entrega y recomendaciones)</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1239,25 +1243,25 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
+          <t>ALTA (plataforma, moderador automatizado, fechas, cohorte BR y hallazgos BR confirmados con citas verbatim de Stanford/BIT); pendiente solo N de Brasil e idioma, y el pipeline de análisis (posible upgrade a 'contenido')</t>
         </is>
       </c>
       <c r="W6" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>Confirmar rol de la IA / uso de IA en el proceso (incertidumbre residual NO decisiva) → https://sia.pi.gov.br/projetos/opa/ · Confirmar sistema_IA / tipos de IA / uso de LLM generativa → https://tiinside.com.br/21/10/2025/em-parceria-com-a-aws-colab-lanca-ia-que-constroi-fluxos-de-governo-em-segundos/ · Confirmar cita textual (página renderizada) → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar etapas de uso de IA → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar estado de actividad → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar nivel de consolidación → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar convocante → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Abrir el informe de Stanford (cddrl.fsi.stanford.edu/publication/meta-community-forum-results-analysis) y confirmar: (1) que el pipeline ChatGPT+ArgumentMiner también se usó en este foro (si sí, agregar etapa Análisis y rol contenido); (2) N de participantes de Brasil e idioma. URLs en la ficha. · Confirmar pipeline de análisis de transcripciones en ESTE foro (ChatGPT para traducción + ArgumentMiner/Fileread.ai, confirmado en el foro hermano del Metaverso; de confirmarse aquí, agregar etapa 'Análisis' y rol 'contenido') → https://cddrl.fsi.stanford.edu/publication/meta-community-forum-results-analysis · Confirmar nº de participantes de Brasil, firma de muestreo e idioma (portugués) → https://transparency.meta.com/governance/community-forums/2023-community-forum-on-generative-AI/</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
+          <t>https://deliberation.stanford.edu/meta-community-forum-generative-ai-results</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>BR-opa-piaui-presupuesto-participativo-digi</t>
+          <t>BR-meta-community-forum-genai</t>
         </is>
       </c>
     </row>
@@ -1269,26 +1273,26 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
+          <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
+          <t>Opa (Orçamento Participativo Digital) es el presupuesto participativo 100% digital del Gobierno del Estado de Piauí (Brasil), creado en 2023 y coordinado por la Secretaria do Planejamento (seplan) con apoyo de la Secretaria de Relações Sociais (Seres). Se ejecuta sobre la plataforma Colab Gov (de la govtech Colab) con infraestructura AWS. El ciclo incluye cadastramento de propuestas por entidades comunitarias/asociaciones, una fase de 'análise técnica' (verificación de documentación, viabilidad de ejecución, claridad de la descripción, adecuación al área temática y no duplicación) y una votación popular abierta a la ciudadanía. En la edición 2026-2027, según el material de Colab, 'a análise ganhou agilidade com o uso de inteligência artificial, que reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón y 99,98% de disponibilidad del sistema. La señal disponible vincula la IA al procesamiento/agilización del flujo, a la seguridad de la infraestructura (filtrado de conexiones inseguras vía AWS CloudFront), a un chatbot/capacitación (CapacitIA) y a un 'Observatório do opa' de transparencia; la 'análise técnica' de viabilidad se describe de forma reiterada como tarea conducida por equipos técnicos a través de la plataforma. no hay evidencia de que la IA clasifique, agrupe (clustering) o sintetice el contenido temático/semántico de las propuestas en el opa.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1307,85 +1311,81 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas.</t>
+          <t>Según el material de Colab, en la edición 2025-2026 / 2026-2027 la IA agilizó la fase de análisis y 'reduziu em 40% o tempo de processamento das propostas', con economía de R$ 1,75 millón en costos directos y 99,98% de disponibilidad del sistema incluso en picos de votación. Una fuente describe además que 'a inteligência artificial foi utilizada para filtrar conexões inseguras' mediante AWS CloudFront (seguridad/infraestructura). El uso adicional de IA en torno al opa es un chatbot creado en el curso CapacitIA y el 'Observatório do opa' (transparencia/monitoreo). no hay evidencia textual de que la IA clasifique por temas, agrupe (clustering), priorice o sintetice el contenido de las propuestas del opa; la 'análise técnica' (documentación, viabilidad de ejecución, claridad, adecuación al área temática, no duplicación) se describe de forma reiterada y convergente como tarea de 'equipes técnicas' conducida a través de la plataforma. La única atribución hallada de IA que 'agrupa ideias semelhantes / estrutura propostas por eixo temático' corresponde a otro proceso (Diálogos pelo Piauí / revisión del PPA 2024-2027, talleres presenciales en 12 Territórios de Desenvolvimento), no al opa, y ni siquiera pudo confirmarse verbatim para Diálogos.</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>No identificado por nombre. Capacidad de IA integrada en la plataforma Colab Gov (govtech Colab) sobre infraestructura AWS. En el OPA, la IA se asocia a la 'análise'/'processamento' de propuestas (agilización, -40% de tiempo), al filtrado de conexiones inseguras vía AWS CloudFront (seguridad/infraestructura), a un chatbot construido en un curso CapacitIA y a un 'Observatório do OPA' (panel de transparencia). La infraestructura AWS descrita es de cómputo/almacenamiento/seguridad (Amazon EC2, Amazon RDS, AWS CloudFront), no servicios de ML de contenido. No se especifica modelo, técnica (NLP, clustering, LLM) ni que la IA actúe sobre el contenido semántico de las propuestas del OPA. La plataforma Colab Gov.AI (lanzada en oct/2025 con AWS, basada en IA generativa/LangChain) ofrece funciones genéricas (generar flujos de servicio, etiquetar demandas en dashboards, asistir al ciudadano a redactar propuestas), pero ninguna de estas se atribuye específicamente al análisis de contenido de las propuestas del OPA Piauí.</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>Governo do Estado do Piauí - Secretaria do Planejamento (SEPLAN), con apoyo de la Secretaria de Relações Sociais (Seres). Socio tecnológico: GovTech Colab (plataforma Colab Gov); infraestructura: AWS (Amazon Web Services).</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Chatbot de IA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>LLM; NLP</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno; Privado</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>Nacional, Internacional</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar rol de la IA / uso de IA en el proceso (incertidumbre residual NO decisiva) → https://sia.pi.gov.br/projetos/opa/ · Confirmar sistema_IA / tipos de IA / uso de LLM generativa → https://tiinside.com.br/21/10/2025/em-parceria-com-a-aws-colab-lanca-ia-que-constroi-fluxos-de-governo-em-segundos/ · Confirmar cita textual (página renderizada) → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar etapas de uso de IA → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar estado de actividad → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar nivel de consolidación → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confirmar convocante → https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+          <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
+          <t>BR-opa-piaui-presupuesto-participativo-digi</t>
         </is>
       </c>
     </row>
@@ -1397,22 +1397,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
+          <t>Plan Plurianual de la ciudad de Natal</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
+          <t>Recolección de información a través de tres preguntas habilitadas por WhatsApp para diseñar el Plan Plurianual de la ciudad 2026-2029.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa; Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Traducción Política; Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Modelo de IA desarrollado internamente para análisis de transcripciones y videos.</t>
+          <t>Chatbot de IA</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; LLM; NLP; Búsqueda semántica</t>
+          <t>LLM; NLP</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Gobierno; Privado</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Nacional, Internacional</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>Senado Federal de Brasil</t>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1498,22 +1498,22 @@
           <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
-      <c r="W8" s="5" t="n">
-        <v>1</v>
+      <c r="W8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>Confirmar nivel de consolidación → https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
+          <t>BR-plan-plurianual-de-la-ciudad-de-natal</t>
         </is>
       </c>
     </row>
@@ -1525,22 +1525,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
+          <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
+          <t>Implementación de IA para identificar y marcar en los videos de eventos las respuestas dadas a preguntas ciudadanas, incluso cuando estas no fueron respondidas directamente durante las audiencias.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa; Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Traducción Política; Análisis</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1568,22 +1568,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Clasificar y organizar el contenido de las propuestas ciudadanas enviadas a la consulta pública: la IA (Google Gemini) categoriza por tema las 6.368 propostas, las rankea por asunto y cantidad de apoyos y alimenta painéis de participación por distrito/subprefeitura, con el objetivo declarado de 'facilitar a divulgação das propostas à população'. Es procesamiento del contenido de los aportes (clasificar/agrupar/sintetizar), no apoyo meramente logístico.</t>
+          <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Herramienta de análisis de datos construida en Python con la librería Pandas y la IA generativa Google Gemini. A partir de la base de propostas exportada del portal Participe Mais, clasifica las propuestas ciudadanas en categorías temáticas, las ordena por asunto y por cantidad de apoyos, y produce relatórios y painéis visuales: ranking de los temas más recurrentes y participación por distrito y subprefeitura. Se describe el uso de prompts/comandos a la IA (con 'ajustes necessários nos comandos para a Inteligência Artificial' como desafío reportado). No se publica el detalle técnico (modelo Gemini exacto, prompts), por lo que la implementación se conoce solo por descripción.</t>
+          <t>Modelo de IA desarrollado internamente para análisis de transcripciones y videos.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>LLM generativa; NLP; Clasificación de texto</t>
+          <t>Voz a Texto; LLM; NLP; Búsqueda semántica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil; Gobierno</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>concluido</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>Proceso participativo (Programa de Metas / PPA / PAS): Prefeitura de São Paulo (Secretaria Municipal de Planejamento / Casa Civil / Coordenadoria de Governo Aberto, portal Participe Mais). Herramienta de IA: desarrollada por Carolina Borges, Agente de Governo Aberto de São Paulo (formación en Ciência da Computação y posgrado en Gestão e Controle Social de Políticas Públicas por la Escola de Contas do TCM-SP; experiencia profesional, académica y voluntaria), presentada en la oficina de la Escola do Parlamento da Câmara Municipal de São Paulo en parceria con el Programa Agentes de Governo Aberto. No se confirmó que la Prefeitura adoptara esta herramienta como su pipeline oficial de análisis del proceso.</t>
+          <t>Senado Federal de Brasil</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1623,25 +1623,25 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>MEDIA-ALTA</t>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
         </is>
       </c>
       <c r="W9" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>Confirmar cita textual (verificación carácter a carácter en los PDFs oficiales) → https://gestaourbana.prefeitura.sp.gov.br/wp-content/uploads/2025/10/Relatorio_Oficinas_Participativas.pdf · Confirmar confirmación de no-adopción (hipótesis remota de uso interno no publicado) → https://gestaourbana.prefeitura.sp.gov.br/planos-de-acao-das-subprefeituras/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar nivel de consolidación → https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>BR-sao-paulo-programa-de-metas-participe-ma</t>
+          <t>BR-portal-e-cidadania-marcado-automatico-de</t>
         </is>
       </c>
     </row>
@@ -1653,22 +1653,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
+          <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
+          <t>Consulta pública del Programa de Metas 2025-2028 / Plano Plurianual (PPA) 2026-2029 / Planos de Ação das Subprefeituras (pas) 2026-2029 de la Prefeitura de São Paulo, realizada en el portal Participe Mais (Participe+), plataforma de participación social de la Prefeitura construida sobre el software libre Decidim (basado en consul/Decidim de Madrid-Barcelona). La consulta estuvo abierta del 7/04/2025 al 11/05/2025; el ciclo participativo incluyó 36 audiencias públicas híbridas en la ciudad (abril-mayo 2025) y recibió 6.368 propostas y más de 31.000 interacciones ciudadanas (sugerencias, apoyos, propuestas y críticas). Sobre ese material, en mayo de 2025 Carolina Borges -Agente de Governo Aberto de la Prefeitura- desarrolló una herramienta (Python + Pandas + Google Gemini) que clasifica las propostas en categorías, las ordena por asunto y cantidad de apoyos y genera relatórios y painéis visuales (ranking de temas más recurrentes y participación por distrito y subprefeitura), 'facilitando a divulgação das propostas à população'. La herramienta y su metodología se presentaron en la oficina 'Análise de Dados com Inteligência Artificial na Gestão Pública: Programa de Metas' de la Escola do Parlamento de la Câmara Municipal de São Paulo (15/12/2025), realizada en parceria con el Programa Agentes de Governo Aberto da Prefeitura.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1696,32 +1696,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Recolectar/recuperar y emparejar (matching) el contenido de las ideas legislativas ciudadanas con proyectos de ley: con IA se hace una búsqueda en el banco de ideias legislativas y se seleccionan las compatibles con la propuesta del senador, que luego pueden incorporarse al proyecto y citarse en su justificación. Transforma un archivo antes subutilizado en fuente para fundamentar justificaciones, inspirar redacciones y orientar ajustes de los proyectos parlamentarios.</t>
+          <t>Clasificar y organizar el contenido de las propuestas ciudadanas enviadas a la consulta pública: la IA (Google Gemini) categoriza por tema las 6.368 propostas, las rankea por asunto y cantidad de apoyos y alimenta painéis de participación por distrito/subprefeitura, con el objetivo declarado de 'facilitar a divulgação das propostas à população'. Es procesamiento del contenido de los aportes (clasificar/agrupar/sintetizar), no apoyo meramente logístico.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Herramienta de análisis de datos construida en Python con la librería Pandas y la IA generativa Google Gemini. A partir de la base de propostas exportada del portal Participe Mais, clasifica las propuestas ciudadanas en categorías temáticas, las ordena por asunto y por cantidad de apoyos, y produce relatórios y painéis visuales: ranking de los temas más recurrentes y participación por distrito y subprefeitura. Se describe el uso de prompts/comandos a la IA (con 'ajustes necessários nos comandos para a Inteligência Artificial' como desafío reportado). No se publica el detalle técnico (modelo Gemini exacto, prompts), por lo que la implementación se conoce solo por descripción.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>LLM generativa; NLP; Clasificación de texto</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>Herramienta de inteligencia artificial de búsqueda semántica desarrollada internamente por el servidor Alisson Bruno (Desafio de Inovação do Senado). Realiza una búsqueda sobre el banco de ideias legislativas del e-Cidadania para seleccionar las sugerencias ciudadanas temáticamente compatibles con un proyecto de ley en preparación por la Consultoria Legislativa. No se publica el detalle técnico del modelo (embeddings/semantic search), por lo que la familia exacta no está confirmada documentalmente.</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>NLP; Búsqueda semántica</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Sociedad Civil; Gobierno</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1736,67 +1736,67 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>concluido</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>Senado Federal do Brasil - Consultoria Legislativa en conjunto con el Programa e-Cidadania (Secretaria de Transparência / Coordenação do e-Cidadania). Herramienta desarrollada por el servidor Alisson Bruno (coordenador do e-Cidadania) en el marco del Desafio de Inovação do Senado.</t>
+          <t>Proceso participativo (Programa de Metas / PPA / PAS): Prefeitura de São Paulo (Secretaria Municipal de Planejamento / Casa Civil / Coordenadoria de Governo Aberto, portal Participe Mais). Herramienta de IA: desarrollada por Carolina Borges, Agente de Governo Aberto de São Paulo (formación en Ciência da Computação y posgrado en Gestão e Controle Social de Políticas Públicas por la Escola de Contas do TCM-SP; experiencia profesional, académica y voluntaria), presentada en la oficina de la Escola do Parlamento da Câmara Municipal de São Paulo en parceria con el Programa Agentes de Governo Aberto. No se confirmó que la Prefeitura adoptara esta herramienta como su pipeline oficial de análisis del proceso.</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>NO (duplicado)</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA-ALTA</t>
         </is>
       </c>
       <c r="W10" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>Confirmar tipos de IA / uso de LLM generativa → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial · Confirmar año de inicio (mes exacto / fecha de despliegue) → https://www12.senado.leg.br/radio/1/noticia/2026/01/15/ia-vai-aproximar-ideias-legislativas-do-e-cidadania-e-projetos-de-senadores · Confirmar nivel de consolidación (&gt;=2 ediciones) → https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/ · Confirmar cita textual (cita textual exacta verificada en HTML) → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
+          <t>Confirmar cita textual (verificación carácter a carácter en los PDFs oficiales) → https://gestaourbana.prefeitura.sp.gov.br/wp-content/uploads/2025/10/Relatorio_Oficinas_Participativas.pdf · Confirmar confirmación de no-adopción (hipótesis remota de uso interno no publicado) → https://gestaourbana.prefeitura.sp.gov.br/planos-de-acao-das-subprefeituras/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
+          <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>BR-e-cidadania-senado-ia-matching-de-ideas</t>
+          <t>BR-sao-paulo-programa-de-metas-participe-ma</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cabildos 2016</t>
+          <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Análisis de los cabildos del proceso constitucional en 2016.</t>
+          <t>Portal e-Cidadania del Senado Federal de Brasil, módulo 'Ideia Legislativa', donde la población envía sugerencias para crear o mejorar leyes. Tradicionalmente una idea debía reunir 20.000 apoyos en 4 meses para ser formalizada como Sugestão Legislativa y analizada por la Comissão de Direitos Humanos e Legislação Participativa (cdh). A fines de 2025 / enero 2026 el Senado desplegó una herramienta de inteligencia artificial (búsqueda semántica) sobre el banco de ideias legislativas (145.993 ideias a enero 2026) que, a pedido de la Consultoria Legislativa cuando un senador prepara un proyecto, busca y selecciona las ideas ciudadanas temáticamente compatibles para incorporarlas y citarlas en la justificación del proyecto de ley, sin exigir el mínimo de apoyos.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Clasificación y análisis de texto para identificar conceptos clave.</t>
+          <t>Recolectar/recuperar y emparejar (matching) el contenido de las ideas legislativas ciudadanas con proyectos de ley: con IA se hace una búsqueda en el banco de ideias legislativas y se seleccionan las compatibles con la propuesta del senador, que luego pueden incorporarse al proyecto y citarse en su justificación. Transforma un archivo antes subutilizado en fuente para fundamentar justificaciones, inspirar redacciones y orientar ajustes de los proyectos parlamentarios.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1834,22 +1834,22 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de Lenguaje Natural</t>
+          <t>Herramienta de inteligencia artificial de búsqueda semántica desarrollada internamente por el servidor Alisson Bruno (Desafio de Inovação do Senado). Realiza una búsqueda sobre el banco de ideias legislativas del e-Cidadania para seleccionar las sugerencias ciudadanas temáticamente compatibles con un proyecto de ley en preparación por la Consultoria Legislativa. No se publica el detalle técnico del modelo (embeddings/semantic search), por lo que la familia exacta no está confirmada documentalmente.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP; Búsqueda semántica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1859,45 +1859,45 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
+          <t>Senado Federal do Brasil - Consultoria Legislativa en conjunto con el Programa e-Cidadania (Secretaria de Transparência / Coordenação do e-Cidadania). Herramienta desarrollada por el servidor Alisson Bruno (coordenador do e-Cidadania) en el marco del Desafio de Inovação do Senado.</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>sí</t>
+          <t>NO (duplicado)</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>0</v>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar tipos de IA / uso de LLM generativa → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial · Confirmar año de inicio (mes exacto / fecha de despliegue) → https://www12.senado.leg.br/radio/1/noticia/2026/01/15/ia-vai-aproximar-ideias-legislativas-do-e-cidadania-e-projetos-de-senadores · Confirmar nivel de consolidación (&gt;=2 ediciones) → https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/ · Confirmar cita textual (cita textual exacta verificada en HTML) → https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/</t>
+          <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>CL-cabildos-2016</t>
+          <t>BR-e-cidadania-senado-ia-matching-de-ideas</t>
         </is>
       </c>
     </row>
@@ -1909,17 +1909,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
+          <t>Cabildos 2016</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la segegob y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de sistematizar los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (rnn) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/lda) sobre el contenido de diálogos y consultas individuales.</t>
+          <t>Análisis de los cabildos del proceso constitucional en 2016.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>La IA procesa el contenido de los aportes ciudadanos (texto libre de diálogos y consultas individuales): clasifica las contribuciones mediante redes neuronales recurrentes (carpeta contributions_rnn) y mediante árboles de decisión/Random Forest (carpeta randomforest), sistematiza las emociones expresadas (Grouping Emotions.ipynb) y analiza los tópicos de necesidades personales y país (Analisis de Topicos - Necesidades.ipynb). El objetivo es sistematizar ~130.000 aportes ciudadanos para informar políticas públicas.</t>
+          <t>Clasificación y análisis de texto para identificar conceptos clave.</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Conjunto de modelos de aprendizaje automático y NLP desarrollados por MinCiencia (código público en GitHub: MinCiencia/ECQQ) para sistematizar las contribuciones ciudadanas: clasificación de contribuciones con redes neuronales recurrentes (RNN) y con árboles de decisión (Random Forest), agrupamiento/sistematización de emociones y análisis de tópicos de necesidades (NLP/LDA). Visualización mediante dashboards (Apache Superset).</t>
+          <t>Procesamiento de Lenguaje Natural</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>NLP; Clasificación de texto; Modelado de tópicos (LDA); Redes neuronales recurrentes (RNN); Random Forest; Clasificación de emociones; Machine Learning</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Gobierno de Chile - proceso conjunto liderado por el Ministerio de Desarrollo Social y Familia; sistematización de los aportes con ciencia de datos/IA a cargo del Ministerio de Ciencia, Tecnología, Conocimiento e Innovación (MinCiencia). Participaron también Ministerio de Agricultura, SEGEGOB y División de Gobierno Digital.</t>
+          <t>Gobierno de Chile (Presidencia/SEGPRES) — convocante del Proceso Constituyente Abierto; la Biblioteca del Congreso Nacional sistematiza y archiva los resultados (convenio con Senado, Cámara y SEGPRES).</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -2007,25 +2007,25 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>3</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
-          <t>Confirmar evidencia de actividad 2026 → https://github.com/MinCiencia/ECQQ/activity · Confirmar ano_cierre / informe final → https://www.chilequequeremos.cl · Confirmar rol de la IA (integración formal del output) → https://minciencia.gob.cl/noticias/</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/MinCiencia/ECQQ</t>
+          <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>CL-el-chile-que-queremos-ecqq-minciencia</t>
+          <t>CL-cabildos-2016</t>
         </is>
       </c>
     </row>
@@ -2037,17 +2037,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
+          <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Uso de IA para analizar datos cualitativos en consulta ciudadana.</t>
+          <t>Iniciativa gubernamental de diálogos ciudadanos y escucha social presentada por el Gobierno de Chile el 22 de noviembre de 2019, en el marco del Acuerdo por la Justicia Social y el Acuerdo por una Nueva Constitución tras el estallido social. Entre noviembre de 2019 y marzo de 2020, la ciudadanía pudo participar mediante diálogos grupales (cabildos) o consultas individuales en el sitio www.chilequequeremos.cl, registrando sus necesidades y propuestas para complementar futuras políticas públicas. El proceso fue un esfuerzo conjunto de los Ministerios de Desarrollo Social y Familia, de Ciencia/Tecnología/Conocimiento e Innovación (MinCiencia), de Agricultura, la segegob y la División de Gobierno Digital. El Ministerio de Ciencia fue responsable de sistematizar los aportes ciudadanos usando ciencia de datos / IA: el repositorio público MinCiencia/ECQQ contiene el código que clasifica las contribuciones (texto libre de los aportes) mediante redes neuronales recurrentes (rnn) y árboles de decisión (Random Forest), y sistematiza emociones y necesidades mediante análisis de tópicos (NLP/lda) sobre el contenido de diálogos y consultas individuales.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana.</t>
+          <t>La IA procesa el contenido de los aportes ciudadanos (texto libre de diálogos y consultas individuales): clasifica las contribuciones mediante redes neuronales recurrentes (carpeta contributions_rnn) y mediante árboles de decisión/Random Forest (carpeta randomforest), sistematiza las emociones expresadas (Grouping Emotions.ipynb) y analiza los tópicos de necesidades personales y país (Analisis de Topicos - Necesidades.ipynb). El objetivo es sistematizar ~130.000 aportes ciudadanos para informar políticas públicas.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>No especificado, probablemente NLP.</t>
+          <t>Conjunto de modelos de aprendizaje automático y NLP desarrollados por MinCiencia (código público en GitHub: MinCiencia/ECQQ) para sistematizar las contribuciones ciudadanas: clasificación de contribuciones con redes neuronales recurrentes (RNN) y con árboles de decisión (Random Forest), agrupamiento/sistematización de emociones y análisis de tópicos de necesidades (NLP/LDA). Visualización mediante dashboards (Apache Superset).</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP; Clasificación de texto; Modelado de tópicos (LDA); Redes neuronales recurrentes (RNN); Random Forest; Clasificación de emociones; Machine Learning</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Gobierno Digital</t>
+          <t>Gobierno de Chile - proceso conjunto liderado por el Ministerio de Desarrollo Social y Familia; sistematización de los aportes con ciencia de datos/IA a cargo del Ministerio de Ciencia, Tecnología, Conocimiento e Innovación (MinCiencia). Participaron también Ministerio de Agricultura, SEGEGOB y División de Gobierno Digital.</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -2135,25 +2135,25 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>0</v>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
-          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar evidencia de actividad 2026 → https://github.com/MinCiencia/ECQQ/activity · Confirmar ano_cierre / informe final → https://www.chilequequeremos.cl · Confirmar rol de la IA (integración formal del output) → https://minciencia.gob.cl/noticias/</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
+          <t>https://github.com/MinCiencia/ECQQ</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>CL-estrategia-de-gobierno-digital-informe-p</t>
+          <t>CL-el-chile-que-queremos-ecqq-minciencia</t>
         </is>
       </c>
     </row>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Estudio dIAlogos - Percepciones de Futuro</t>
+          <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena.</t>
+          <t>Uso de IA para analizar datos cualitativos en consulta ciudadana.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil; empresa</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Realización de entrevistas y codificación de respuestas.</t>
+          <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Apoyo a la interacción (chatbots, asistentes virtuales y otros), Razonamiento con estructuras de conocimiento, Reconocimiento.</t>
+          <t>No especificado, probablemente NLP.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>Fundación Encuentros del Futuro y Merlín Research</t>
+          <t>Secretaría de Gobierno Digital</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>https://estudiodialogos.cl/</t>
+          <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>CL-estudio-dialogos-percepciones-de-futuro</t>
+          <t>CL-estrategia-de-gobierno-digital-informe-p</t>
         </is>
       </c>
     </row>
@@ -2293,12 +2293,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
+          <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Jornadas de diálogo de la comunidad académica y otos stakeholders.</t>
+          <t>Estudio que utilizó distintas herramientas de IA para conocer las percepciones de futuro de la población chilena.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -2321,49 +2321,49 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>sociedad civil; empresa</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>Mixto</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Realización de entrevistas y codificación de respuestas.</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Apoyo a la interacción (chatbots, asistentes virtuales y otros), Razonamiento con estructuras de conocimiento, Reconocimiento.</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>NLP</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones.</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>Procesamiento de Lenguaje Natural (NLP)</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>Privado</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>Nacional</t>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2399,17 +2399,17 @@
       </c>
       <c r="X15" s="4" t="inlineStr">
         <is>
-          <t>Adjuntar el enlace directo del informe/dashboard de la jornada; el de Tableau no es verificable públicamente. El equipo ejecutó el proceso, confirmar la técnica de análisis usada. · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/</t>
+          <t>https://estudiodialogos.cl/</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>CL-jornada-de-escucha-lanzamiento-instituto</t>
+          <t>CL-estudio-dialogos-percepciones-de-futuro</t>
         </is>
       </c>
     </row>
@@ -2421,22 +2421,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LXS 400 - Chile Delibera</t>
+          <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
+          <t>Jornadas de diálogo de la comunidad académica y otos stakeholders.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Mini públicos</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Planificación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; universidad; sociedad civil</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>apoyo</t>
+          <t>contenido</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>El moderador automatizado de la Stanford Online Deliberation Platform gestiona la logística de la deliberación: mantiene los tiempos y distribuye equitativamente los derechos/turnos de palabra, permite a los participantes formar colas de habla (speaking queues), aplica agendas con tiempos (timed agendas), controla mediante un sistema de señal automatizado a quién se le pide la siguiente intervención y un temporizador para cuánto tiempo tiene cada participante; además solicita argumentos a favor y en contra de las propuestas, incentiva a quienes no están hablando y consulta si todas las posturas fueron exploradas. Es decir, estructura la conversación (turnos, tiempos, equidad de participación), no analiza ni sintetiza automáticamente el contenido de los aportes en reportes. En paralelo, la IA del Centro de Microdatos de la U. de Chile se usó para seleccionar la muestra representativa (~400 de un universo de ~35.000 / 18 millones de habitantes). El análisis sustantivo de resultados se hizo mediante encuesta cuantitativa (clcert/Centro de Microdatos) y un informe cualitativo, no mediante síntesis automática por IA del contenido deliberado.</t>
+          <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Stanford Online Deliberation Platform (plataforma de deliberación online del Center for Deliberative Democracy / Deliberative Democracy Lab de la Universidad de Stanford) con moderador automatizado (automated moderator) para facilitar la Encuesta Deliberativa online. Adicionalmente, el Centro de Microdatos de la U. de Chile empleó tecnología basada en IA para la selección de la muestra representativa.</t>
+          <t>Procesamiento de Lenguaje Natural (NLP)</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización; Muestreo estadístico asistido por IA</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2489,27 +2489,27 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>inactivo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>Senado de Chile (Comisión Desafíos del Futuro, Ciencia, Tecnología e Innovación) y Fundación Tribu, con la Universidad de Stanford (Center for Deliberative Democracy / Deliberative Democracy Lab), la Universidad de Chile (Centro de Microdatos), la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil e Identificación.</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2519,25 +2519,25 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>4</v>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
-          <t>Confirmar rol de la IA (reporte de IA) → https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera · Confirmar estado de actividad / evidencia de actividad 2026 → https://www.lxs400.cl/noticias/ · Confirmar nivel de consolidación → https://www.senado.cl/comunicaciones/noticias/chile-delibera-lxs-400-un-fin-de-semana-de-democracia-deliberativa-online · Confirmar fuentes (verbatim directo) → https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
+          <t>Adjuntar el enlace directo del informe/dashboard de la jornada; el de Tableau no es verificable públicamente. El equipo ejecutó el proceso, confirmar la técnica de análisis usada. · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
+          <t>https://ipp.unab.cl/</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>CL-lxs-400-chile-delibera</t>
+          <t>CL-jornada-de-escucha-lanzamiento-instituto</t>
         </is>
       </c>
     </row>
@@ -2549,22 +2549,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>La voz de los nuevos votantes</t>
+          <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Análisis de Lenguaje Natural para los audios transcritos de encuesta realizada en persona.</t>
+          <t>Encuesta deliberativa nacional (Deliberative Poll, modelo de James S. Fishkin) convocada por el Senado de Chile (Comisión Desafíos del Futuro) junto a la Fundación Tribu, el Centro para la Democracia Deliberativa de la Universidad de Stanford, la Universidad de Chile, la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil. Un mini-público de ~400-514 ciudadanos seleccionados aleatoriamente y representativos del país deliberó de forma online (vía Zoom y la Stanford Online Deliberation Platform) los días 5, 6 y 7 de marzo de 2021 sobre reformas a pensiones y salud, en grupos pequeños y sesiones plenarias, de cara al debate constitucional. El proceso comenzó en diciembre de 2020 con la selección de la muestra y la entrega de material informativo equilibrado (argumentos a favor y en contra). La plataforma online de Stanford incorporó un moderador automatizado (IA) que controlaba los tiempos y distribuía equitativamente los turnos de palabra (colas de habla, temporizador, sistema de señal para determinar quién hablaba a continuación); en paralelo, el Centro de Microdatos de la U. de Chile usó tecnología basada en IA para seleccionar la muestra representativa.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Mini públicos</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Implementación; Planificación</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -2577,22 +2577,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno nacional; universidad; sociedad civil</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>contenido</t>
+          <t>apoyo</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
+          <t>El moderador automatizado de la Stanford Online Deliberation Platform gestiona la logística de la deliberación: mantiene los tiempos y distribuye equitativamente los derechos/turnos de palabra, permite a los participantes formar colas de habla (speaking queues), aplica agendas con tiempos (timed agendas), controla mediante un sistema de señal automatizado a quién se le pide la siguiente intervención y un temporizador para cuánto tiempo tiene cada participante; además solicita argumentos a favor y en contra de las propuestas, incentiva a quienes no están hablando y consulta si todas las posturas fueron exploradas. Es decir, estructura la conversación (turnos, tiempos, equidad de participación), no analiza ni sintetiza automáticamente el contenido de los aportes en reportes. En paralelo, la IA del Centro de Microdatos de la U. de Chile se usó para seleccionar la muestra representativa (~400 de un universo de ~35.000 / 18 millones de habitantes). El análisis sustantivo de resultados se hizo mediante encuesta cuantitativa (clcert/Centro de Microdatos) y un informe cualitativo, no mediante síntesis automática por IA del contenido deliberado.</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de Lenguaje Natural (NLP)</t>
+          <t>Stanford Online Deliberation Platform (plataforma de deliberación online del Center for Deliberative Democracy / Deliberative Democracy Lab de la Universidad de Stanford) con moderador automatizado (automated moderator) para facilitar la Encuesta Deliberativa online. Adicionalmente, el Centro de Microdatos de la U. de Chile empleó tecnología basada en IA para la selección de la muestra representativa.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>Moderación/facilitación automatizada; Sistema de reglas/temporización; Muestreo estadístico asistido por IA</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2617,27 +2617,27 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>inactivo</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Senado de Chile (Comisión Desafíos del Futuro, Ciencia, Tecnología e Innovación) y Fundación Tribu, con la Universidad de Stanford (Center for Deliberative Democracy / Deliberative Democracy Lab), la Universidad de Chile (Centro de Microdatos), la Asociación Chilena de Municipalidades (AChM) y el Servicio de Registro Civil e Identificación.</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2647,25 +2647,25 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>0</v>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar rol de la IA (reporte de IA) → https://es.wikipedia.org/wiki/Lxs_400:_Chile_Delibera · Confirmar estado de actividad / evidencia de actividad 2026 → https://www.lxs400.cl/noticias/ · Confirmar nivel de consolidación → https://www.senado.cl/comunicaciones/noticias/chile-delibera-lxs-400-un-fin-de-semana-de-democracia-deliberativa-online · Confirmar fuentes (verbatim directo) → https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
+          <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>CL-la-voz-de-los-nuevos-votantes</t>
+          <t>CL-lxs-400-chile-delibera</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
+          <t>La voz de los nuevos votantes</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional.</t>
+          <t>Análisis de Lenguaje Natural para los audios transcritos de encuesta realizada en persona.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases.</t>
+          <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>Secretaría de Participación Ciudadana</t>
+          <t>Universidad Andres Bello</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+          <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>CL-participacion-ciudadana-proceso-constitu</t>
+          <t>CL-la-voz-de-los-nuevos-votantes</t>
         </is>
       </c>
     </row>
@@ -2805,12 +2805,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Chile</t>
+          <t>Participación Ciudadana Proceso Constitucional</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogo y participación llevada a cabo por la uch y puc en el contexto de manifestaciones sociales.</t>
+          <t>Análisis de los resultados obtenidos de los Diálogos Ciudadanos Autoconvocados dentro del proceso constitucional.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas.</t>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
+          <t>Secretaría de Participación Ciudadana</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>https://www.tenemosquehablardechile.cl/</t>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>CL-tenemos-que-hablar-de-chile</t>
+          <t>CL-participacion-ciudadana-proceso-constitu</t>
         </is>
       </c>
     </row>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
+          <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
+          <t>Iniciativa de diálogo y participación llevada a cabo por la uch y puc en el contexto de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Análisis temático de las transcripciones de las mesas.</t>
+          <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas.</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>Universidad Andres Bello</t>
+          <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -3044,39 +3044,39 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/</t>
+          <t>https://www.tenemosquehablardechile.cl/</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>CL-un-encuentro-para-la-equidad-de-genero-e</t>
+          <t>CL-tenemos-que-hablar-de-chile</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Chatico</t>
+          <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Agente virtual de Bogotá (Secretaría General) con módulos de participación además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa ; atiende por WhatsApp/Telegram/webchat.</t>
+          <t>Espacio participativo para levantar opiniones y propuestas de autoridades, miembros de la sociedad civil y académicos sobre la movilidad con perspectiva de género en Chile.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Participación Digital</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -3084,17 +3084,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo.</t>
+          <t>Análisis temático de las transcripciones de las mesas.</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3114,52 +3114,52 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural (NLP)</t>
+          <t>Procesamiento de Lenguaje Natural (NLP)</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>NLP; LLM</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>cerrado</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>Universidad Andres Bello</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>Privado; Gobierno</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="W21" s="3" t="n">
@@ -3167,17 +3167,17 @@
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones</t>
+          <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>CO-chatico</t>
+          <t>CL-un-encuentro-para-la-equidad-de-genero-e</t>
         </is>
       </c>
     </row>
@@ -3189,22 +3189,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ECHO – HáblameD Medellín</t>
+          <t>Chatico</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial.</t>
+          <t>Agente virtual de Bogotá (Secretaría General) con módulos de participación además de atención: votación de Causas Ciudadanas y de los Presupuestos Participativos (240.000+ votos desde 2022) y recepción de más de 147.000 aportes ciudadanos para la construcción del Plan Distrital de Desarrollo 'Bogotá Camina Segura' 2024-2027. Renovado con IA generativa ; atiende por WhatsApp/Telegram/webchat.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Presupuestos Participativos; Participación Digital</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; gobierno local</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+          <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo.</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de Lenguaje Natural (NLP), Speech to Text</t>
+          <t>Procesamiento de lenguaje natural (NLP)</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Voz a Texto; NLP; LLM</t>
+          <t>NLP; LLM</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -3257,27 +3257,27 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Privado; Gobierno</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+          <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+          <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>CO-echo-hablamed-medellin</t>
+          <t>CO-chatico</t>
         </is>
       </c>
     </row>
@@ -3317,22 +3317,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
+          <t>ECHO – HáblameD Medellín</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
+          <t>IA que capta voz ciudadana en debates guiados y clasifica cada enunciado en metas ODS, generando visualizaciones para la planificación territorial.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -3340,15 +3340,19 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>organización internacional; gobierno local</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Mixto</t>
+        </is>
+      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3356,7 +3360,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Resume las propuestas, organiza opiniones, procesa tendencias y construye consensos sobre el contenido de los aportes de la comunidad; convierte las opiniones en datos procesables y produce un resultado verificable (blockchain).</t>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3366,12 +3370,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>Gaitana IA — plataforma/chatbot basada en el LLM DeepSeek adaptado a la cosmovisión Zenú; registro de decisiones en blockchain (Ethereum)</t>
+          <t>Procesamiento de Lenguaje Natural (NLP), Speech to Text</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>LLM; NLP</t>
+          <t>Voz a Texto; NLP; LLM</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -3381,27 +3385,27 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Sociedad Civil</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3411,25 +3415,25 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
-        </is>
-      </c>
-      <c r="W23" s="5" t="n">
-        <v>3</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>Confirmar el alcance del uso del LLM (DeepSeek) sobre los aportes y el estado de consolidación (¿puntual o recurrente?). · Confirmar rol de la IA → https://cerosetenta.uniandes.edu.co/ · Confirmar nivel de consolidación → https://gaitanaia.org/ · Confirmar tipo_organizacion → https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>CO-gaitana-ia-resguardo-zenu</t>
+          <t>CO-echo-hablamed-medellin</t>
         </is>
       </c>
     </row>
@@ -3441,22 +3445,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Tenemos que hablar de Colombia</t>
+          <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
+          <t>Plataforma participativa donde jóvenes del resguardo Zenú deciden por votación digital la asignación de presupuestos locales del cabildo y debaten proyectos de ley / proponen iniciativas ciudadanas colectivas.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Presupuestos Participativos; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -3464,19 +3468,15 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>universidad; empresa; sociedad civil</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>Mixto</t>
-        </is>
-      </c>
+          <t>sociedad civil</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos.</t>
+          <t>Resume las propuestas, organiza opiniones, procesa tendencias y construye consensos sobre el contenido de los aportes de la comunidad; convierte las opiniones en datos procesables y produce un resultado verificable (blockchain).</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3494,22 +3494,22 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural (NLP)</t>
+          <t>Gaitana IA — plataforma/chatbot basada en el LLM DeepSeek adaptado a la cosmovisión Zenú; registro de decisiones en blockchain (Ethereum)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
+          <t>LLM; NLP</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>Academia</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3519,17 +3519,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>activo</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
+          <t>Resguardo indígena Zenú (Reparo Torrente, Bajo Sinú); creador Carlos Redondo Rincón</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3539,47 +3539,47 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>0</v>
+          <t>MEDIA (múltiples fuentes de prensa independientes; sin verificación técnica del método; cobertura crítica)</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
-          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar el alcance del uso del LLM (DeepSeek) sobre los aportes y el estado de consolidación (¿puntual o recurrente?). · Confirmar rol de la IA → https://cerosetenta.uniandes.edu.co/ · Confirmar nivel de consolidación → https://gaitanaia.org/ · Confirmar tipo_organizacion → https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>https://tenemosquehablarcolombia.co/</t>
+          <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>CO-tenemos-que-hablar-de-colombia</t>
+          <t>CO-gaitana-ia-resguardo-zenu</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
+          <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (cen). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema xiscop y luego procesadas en el sistema GEMA-cen, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). xiscop (uci) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
+          <t>Plataforma colaborativa de diálogo e incidencia ciudadana para la conversación entre diversos actores de la sociedad colombiana, surgido a partir de eventos de manifestaciones sociales.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>universidad; empresa; sociedad civil</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Analizar el contenido de las propuestas ciudadanas recogidas en la consulta popular: GEMA-cen procesaba los expedientes con propuestas, recuperaba y comparaba su contenido, agrupaba las propuestas similares (idénticas o con redacción distinta que se referían al mismo criterio u opinión) y permitía determinar las 'propuestas típicas' por párrafo en cada categoría/Título establecida, sintetizando así el universo de aportes (de las propuestas procesadas se determinaron 5.237 propuestas típicas por Título). xiscop realizaba la entrada, clasificación por juristas y estadísticas oficiales. La función técnica de GEMA combina recuperación de información, agrupamiento/clasificación de documentos por temática, OCR y resumen automático extractivo.</t>
+          <t>Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>GEMA-CEN: adaptación para el Consejo Electoral Nacional del producto GEMA de Datys (empresa estatal cubana). Según la ficha oficial de Datys, GEMA es 'una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información'; es un 'sistema de procesamiento paralelo, distribuido y resistente a fallos' que clasifica archivos 'atendiendo a temáticas predefinidas por los usuarios', extrae texto de imágenes mediante OCR, recupera información por contenido y 'mediante técnicas modernas de recuperación de información' obtiene archivos similares, elimina resultados no relevantes y agrupa documentos comunes; además genera sumarios 'conformados por las oraciones con mayor importancia dentro del texto'. En la consulta, los especialistas usaban GEMA-CEN para el 'análisis inteligente de los expedientes', agrupar propuestas similares y determinar 'propuestas típicas'. El sistema XISCOP (UCI) realizaba la captura, revisión/clasificación por juristas y las estadísticas oficiales. No se publica el detalle técnico exacto (si el agrupamiento usa ML/embeddings semánticos o similitud clásica de recuperación de información).</t>
+          <t>Procesamiento de lenguaje natural (NLP)</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Privado; Academia; Gobierno</t>
+          <t>Academia</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
+          <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3667,52 +3667,52 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="W25" s="5" t="n">
-        <v>4</v>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>Confirmar la técnica exacta de agrupamiento de GEMA-CEN (similitud/clustering) para precisar tipos de IA. · Confirmar tipos de IA / técnica exacta de agrupamiento → http://www.datys.cu/spa/site/product/15 · Confirmar cita textual (verificación carácter a carácter en HTML) → https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18 · Confirmar rol específico de XISCOP vs GEMA-CEN en el uso de IA → https://www.uci.cu/ · Confirmar uso de LLM generativa → http://www.datys.cu/spa/site/product/15</t>
+          <t>Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>http://www.datys.cu/spa/site/product/15</t>
+          <t>https://tenemosquehablarcolombia.co/</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>CU-consulta-popular-codigo-de-las-familias</t>
+          <t>CO-tenemos-que-hablar-de-colombia</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAGA IA </t>
+          <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios.</t>
+          <t>Consulta popular legislativa nacional sobre el proyecto del Código de las Familias en Cuba, organizada y supervisada por el Consejo Electoral Nacional (cen). Se desarrolló entre febrero y abril de 2022 mediante más de 79.000 reuniones en barrios, centros laborales y estudiantiles, con la participación de unos 6.481.200 personas que emitieron opiniones y propuestas sobre el articulado del proyecto de ley. Las propuestas recogidas eran revisadas y clasificadas por juristas en el sistema xiscop y luego procesadas en el sistema GEMA-cen, que mediante 'análisis inteligente de los expedientes' agrupaba propuestas similares y determinaba 'propuestas típicas' por párrafo/categoría (se determinaron 5.237 propuestas típicas por Título). xiscop (uci) emitía además las estadísticas oficiales. El proceso de consulta cerró en abril de 2022; el Código fue aprobado posteriormente en referendo el 25 de septiembre de 2022.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Participación Digital; Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -3720,17 +3720,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional; sociedad civil</t>
+          <t>gobierno nacional</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Mixto</t>
+          <t>Público</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto.</t>
+          <t>Analizar el contenido de las propuestas ciudadanas recogidas en la consulta popular: GEMA-cen procesaba los expedientes con propuestas, recuperaba y comparaba su contenido, agrupaba las propuestas similares (idénticas o con redacción distinta que se referían al mismo criterio u opinión) y permitía determinar las 'propuestas típicas' por párrafo en cada categoría/Título establecida, sintetizando así el universo de aportes (de las propuestas procesadas se determinaron 5.237 propuestas típicas por Título). xiscop realizaba la entrada, clasificación por juristas y estadísticas oficiales. La función técnica de GEMA combina recuperación de información, agrupamiento/clasificación de documentos por temática, OCR y resumen automático extractivo.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3750,97 +3750,97 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Modelos de lenguaje de gran escala (LLMs)</t>
+          <t>GEMA-CEN: adaptación para el Consejo Electoral Nacional del producto GEMA de Datys (empresa estatal cubana). Según la ficha oficial de Datys, GEMA es 'una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información'; es un 'sistema de procesamiento paralelo, distribuido y resistente a fallos' que clasifica archivos 'atendiendo a temáticas predefinidas por los usuarios', extrae texto de imágenes mediante OCR, recupera información por contenido y 'mediante técnicas modernas de recuperación de información' obtiene archivos similares, elimina resultados no relevantes y agrupa documentos comunes; además genera sumarios 'conformados por las oraciones con mayor importancia dentro del texto'. En la consulta, los especialistas usaban GEMA-CEN para el 'análisis inteligente de los expedientes', agrupar propuestas similares y determinar 'propuestas típicas'. El sistema XISCOP (UCI) realizaba la captura, revisión/clasificación por juristas y las estadísticas oficiales. No se publica el detalle técnico exacto (si el agrupamiento usa ML/embeddings semánticos o similitud clásica de recuperación de información).</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>LLM</t>
+          <t>NLP; Minería de texto; Recuperación de información; Clasificación automática de documentos</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Privado; Academia; Gobierno</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>cerrado</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>Consejo Electoral Nacional (CEN) de Cuba como órgano organizador y supervisor de la consulta popular. El procesamiento informático se apoyó en dos sistemas: XISCOP, desarrollado por la Universidad de las Ciencias Informáticas (UCI), para la entrada, revisión, clasificación y estadísticas oficiales; y GEMA-CEN, basado en el producto GEMA de la empresa estatal Datys, para el 'análisis inteligente' y agrupamiento de las propuestas. La Asamblea Nacional del Poder Popular y la Comisión redactora del Ministerio de Justicia recibieron los resultados.</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>activo</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>0</v>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar la técnica exacta de agrupamiento de GEMA-CEN (similitud/clustering) para precisar tipos de IA. · Confirmar tipos de IA / técnica exacta de agrupamiento → http://www.datys.cu/spa/site/product/15 · Confirmar cita textual (verificación carácter a carácter en HTML) → https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18 · Confirmar rol específico de XISCOP vs GEMA-CEN en el uso de IA → https://www.uci.cu/ · Confirmar uso de LLM generativa → http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>https://ia.gobiernoabierto.ec/</t>
+          <t>http://www.datys.cu/spa/site/product/15</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>EC-paga-ia</t>
+          <t>CU-consulta-popular-codigo-de-las-familias</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GT</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guatemala Joven Conversa </t>
+          <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
+          <t>Plataforma que utiliza inteligencia artificial para asistir en la creación de compromisos de Estado Abierto. Analiza datos de planes de acción de gobierno abierto de Ecuador y otros países de Hispanoamérica para sugerir actividades e hitos relacionados con temas propuestos por los usuarios.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Implementación; Análisis</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; sociedad civil</t>
+          <t>gobierno nacional; sociedad civil</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Facilitar diálogos anónimos en tiempo real, agrupar opiniones y permitir votaciones sobre las opiniones de otros participantes.</t>
+          <t>Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto.</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3878,32 +3878,32 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Remesh (plataforma de diálogo masivo con IA, Remesh Inc.), con apoyo de la DPPA Innovation Cell.</t>
+          <t>Modelos de lenguaje de gran escala (LLMs)</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>NLP - Sentiment; NLP - Tópicos</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sí</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
+          <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3936,39 +3936,39 @@
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47</t>
+          <t>https://ia.gobiernoabierto.ec/</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>GT-guatemala-joven-conversa</t>
+          <t>EC-paga-ia</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HN</t>
+          <t>GT</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
+          <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
+          <t>Iniciativa de diálogos digitales asistidos por inteligencia artificial que reunió a más de 300 jóvenes de los 22 departamentos de Guatemala para discutir temas como la reforma electoral, la participación juvenil en el desarrollo y la lucha contra la corrupción.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Referendos e Iniciativas Populares</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Implementación; Análisis</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>organización internacional; universidad</t>
+          <t>organización internacional; sociedad civil</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+          <t>Facilitar diálogos anónimos en tiempo real, agrupar opiniones y permitir votaciones sobre las opiniones de otros participantes.</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento de lenguaje natural para clasificar propuestas.</t>
+          <t>Remesh (plataforma de diálogo masivo con IA, Remesh Inc.), con apoyo de la DPPA Innovation Cell.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>NLP - Tópicos</t>
+          <t>NLP - Sentiment; NLP - Tópicos</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>Gobierno; Academia</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>Internacional, Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -4041,7 +4041,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+          <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -4064,34 +4064,34 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+          <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>HN-redpublica-iverify</t>
+          <t>GT-guatemala-joven-conversa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
+          <t xml:space="preserve">RedPública + iVerify </t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (copladeg), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e iplaneg. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
+          <t>Plataforma digital que recibe propuestas de ley y proyectos sociales, con un módulo de análisis que agrupa temas y genera tableros de tendencias. Integra iVerify, una herramienta que utiliza aprendizaje automático para detectar y clasificar desinformación electoral antes de su publicación.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa; Participación Digital</t>
+          <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>gobierno local</t>
+          <t>organización internacional; universidad</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Procesar y organizar las miles de ideas y propuestas ciudadanas recibidas en talleres/consultas; identificar las prioridades más mencionadas por la ciudadanía; entender las necesidades de cada región; transformar el diálogo social en datos claros para la toma de decisiones que estructuran los ejes del programa. (La asistente 'Esperanza' cumple una función adicional de consulta/atención sobre el programa ya elaborado.).</t>
+          <t>Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -4134,32 +4134,32 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Herramientas de inteligencia artificial (no especificadas públicamente por nombre/proveedor) empleadas para procesar y organizar los aportes ciudadanos e identificar prioridades. Por separado, asistente virtual conversacional 'Esperanza' para consultar el Programa de Gobierno ya publicado. Ninguna fuente nombra el modelo/empresa concreto usado para el análisis de los 26k aportes.</t>
+          <t>Procesamiento de lenguaje natural para clasificar propuestas.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>NLP; Otros(no especificado)</t>
+          <t>NLP - Tópicos</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Gobierno</t>
+          <t>Gobierno; Academia</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional, Nacional</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -4179,25 +4179,25 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="W29" s="5" t="n">
-        <v>4</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X29" s="4" t="inlineStr">
         <is>
-          <t>Confirmar sistema_IA → https://guanajuatointeligente.com/como-hicimos-el-programa/ · Confirmar uso de LLM generativa → https://iplaneg.guanajuato.gob.mx/programagobierno24-30/ · Confirmar tipos de IA → https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf · Confirmar ano_cierre → https://boletines.guanajuato.gob.mx/2025/02/13/guanajuato-hara-historia-con-el-primer-programa-de-gobierno-realizado-con-ia/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/</t>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>MX-guanajuato-inteligente-2024-2030</t>
+          <t>HN-redpublica-iverify</t>
         </is>
       </c>
     </row>
@@ -4209,22 +4209,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto CRECES</t>
+          <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos.</t>
+          <t>Elaboración del Programa de Gobierno del Estado de Guanajuato 2024-2030 ('Gobierno de la Gente'), un plan de gobierno construido con participación ciudadana: se recorrió el territorio y se realizaron cuatro talleres regionales (noreste, norte, centro y sur) con representación de los 46 municipios, integrando la voz de más de 26,000 personas mediante talleres y consultas. El contenido fue validado por el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (copladeg), conformado por ciudadanía, la Gobernadora, secretarios de cada eje e iplaneg. Se utilizaron herramientas de inteligencia artificial para procesar y organizar las miles de ideas y propuestas recibidas, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región, transformando el diálogo social en datos para la toma de decisiones que alimentaron los ejes del programa. Adicionalmente existe la asistente virtual 'Esperanza' para consultar el programa ya publicado.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Presupuestos Participativos</t>
+          <t>Gobernanza Colaborativa; Participación Digital</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional.</t>
+          <t>Procesar y organizar las miles de ideas y propuestas ciudadanas recibidas en talleres/consultas; identificar las prioridades más mencionadas por la ciudadanía; entender las necesidades de cada región; transformar el diálogo social en datos claros para la toma de decisiones que estructuran los ejes del programa. (La asistente 'Esperanza' cumple una función adicional de consulta/atención sobre el programa ya elaborado.).</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Chatbot a través de WhatsApp</t>
+          <t>Herramientas de inteligencia artificial (no especificadas públicamente por nombre/proveedor) empleadas para procesar y organizar los aportes ciudadanos e identificar prioridades. Por separado, asistente virtual conversacional 'Esperanza' para consultar el Programa de Gobierno ya publicado. Ninguna fuente nombra el modelo/empresa concreto usado para el análisis de los 26k aportes.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Chatbot - Inespecífico</t>
+          <t>NLP; Otros(no especificado)</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Gobierno</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>Ayundamiento de Hermosilla</t>
+          <t>Gobierno del Estado de Guanajuato — Instituto de Planeación, Estadística y Geografía del Estado de Guanajuato (IPLANEG), con validación del COPLADEG. Titular: Gobernadora Libia Dennise García Muñoz Ledo.</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4307,52 +4307,52 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
+          <t>MEDIA</t>
         </is>
       </c>
       <c r="W30" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X30" s="4" t="inlineStr">
         <is>
-          <t>Confirmar evidencia de actividad 2026 → https://presupuestocreces.hermosillo.gob.mx/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Confirmar sistema_IA → https://guanajuatointeligente.com/como-hicimos-el-programa/ · Confirmar uso de LLM generativa → https://iplaneg.guanajuato.gob.mx/programagobierno24-30/ · Confirmar tipos de IA → https://iplaneg.guanajuato.gob.mx/wp-content/uploads/03-2.05-Diagnostico-Programa-de-Gobierno-2024-2030-_Diagnostico-Estatal-2025_.pdf · Confirmar ano_cierre → https://boletines.guanajuato.gob.mx/2025/02/13/guanajuato-hara-historia-con-el-primer-programa-de-gobierno-realizado-con-ia/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+          <t>https://guanajuatointeligente.com/como-hicimos-el-programa/</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>MX-presupuesto-creces</t>
+          <t>MX-guanajuato-inteligente-2024-2030</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
+          <t>Presupuesto CRECES</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el contenido de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento punteral (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. importante: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
+          <t>Presupuesto participativo del Ayuntamiento de Hermosillo en México. Utiliza un chatbot que a través de IA simplifica y facilita la votación de los presupuestos participativos.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Presupuestos Participativos</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Análisis; Traducción Política</t>
+          <t>Implementación</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -4360,123 +4360,127 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>sociedad civil; gobierno nacional</t>
+          <t>gobierno local</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>contenido</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional.</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot a través de WhatsApp</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot - Inespecífico</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
           <t>Privado</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>contenido</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Según las fuentes, la IA permite acceder de forma fácil y expedita a más de 175.000 propuestas ciudadanas y 'recoge en un solo clic los consensos nacionales y regionales/provinciales', constituyendo una base de datos navegable de proyectos. Es decir, la IA agrega, organiza y sintetiza el contenido de los aportes ciudadanos del Pacto del Bicentenario para hacerlos consultables por tema y por territorio. No se especifica el método técnico (clasificación/clustering/búsqueda semántica/generación).</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>Mansa Idea (www.mansaidea.com): plataforma digital descrita por sus impulsores como 'basada en inteligencia artificial' que organiza, agrega y hace navegables las propuestas del Pacto del Bicentenario, presentando consensos nacionales y provinciales por tema. La tecnología de IA concreta (familia de modelos, si usa clustering/NLP/embeddings o LLM) NO está identificada explícitamente en las fuentes públicas halladas.</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>no-claro</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>Sociedad Civil</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>desconocido</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>MEDIA (baseline 2025; sin señal web 2026 nueva)</t>
         </is>
       </c>
       <c r="W31" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X31" s="4" t="inlineStr">
         <is>
-          <t>Confirmar sistema_IA / tipos de IA / uso de LLM generativa / funcion_IA (método técnico) → https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa. · Confirmar estado de actividad / evidencia de actividad 2026 → https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'. · Confirmar nivel de consolidación → https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias. · Confirmar convocante (atribución) → https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/ · Confirmar naturaleza jurídica Fundación Panamá Participa (empresa vs ONG) (abrir la fuente)</t>
+          <t>Confirmar evidencia de actividad 2026 → https://presupuestocreces.hermosillo.gob.mx/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/</t>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>PA-mansa-idea-pacto-del-bicentenario</t>
+          <t>MX-presupuesto-creces</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PE</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
+          <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
+          <t>Mansa Idea (www.mansaidea.com) es una plataforma digital basada en inteligencia artificial lanzada el 1 de abril de 2024 por la Fundación Panamá Participa (sociedad civil), liderada por Paulina Franceschi. La plataforma organiza y hace navegables más de 175.000 ideas y propuestas ciudadanas generadas durante el Pacto del Bicentenario 'Cerrando Brechas' (proceso participativo nacional convocado por el gobierno de Panamá / Concertación Nacional, presidente Cortizo, 2020-2021), agregando los consensos nacionales y regionales/provinciales por tema en un solo clic. La IA se aplica sobre el contenido de los aportes ciudadanos (organiza, agrega y sintetiza el corpus de propuestas) para convertirlo en una base de datos navegable. El uso de la IA es un tratamiento punteral (~2024) de un corpus histórico de un proceso participativo ya cerrado (el Pacto fue 2020-2021), orientado a elevar el nivel de la conversación electoral 2024 y a dotar a candidatos, medios y ciudadanía de una herramienta para alinear planes con las necesidades de la población y monitorear el mandato ciudadano. importante: el proceso participativo original (recolección de aportes) fue convocado por el gobierno; la capa de IA (Mansa Idea) la desarrolla la sociedad civil sobre ese corpus ya recolectado.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Gobernanza Colaborativa</t>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Análisis</t>
+          <t>Análisis; Traducción Política</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -4484,17 +4488,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Uso único</t>
+          <t>Plataforma</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>otra institución pública</t>
+          <t>sociedad civil; gobierno nacional</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Público</t>
+          <t>Privado</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -4504,7 +4508,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
+          <t>Según las fuentes, la IA permite acceder de forma fácil y expedita a más de 175.000 propuestas ciudadanas y 'recoge en un solo clic los consensos nacionales y regionales/provinciales', constituyendo una base de datos navegable de proyectos. Es decir, la IA agrega, organiza y sintetiza el contenido de los aportes ciudadanos del Pacto del Bicentenario para hacerlos consultables por tema y por territorio. No se especifica el método técnico (clasificación/clustering/búsqueda semántica/generación).</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -4514,42 +4518,38 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Procesamiento del Lenguaje Natural (PLN) / Comprensión del Lenguaje Natural (NLU)</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>NLP - Tópicos; NLP - Sentiment</t>
-        </is>
-      </c>
+          <t>Mansa Idea (www.mansaidea.com): plataforma digital descrita por sus impulsores como 'basada en inteligencia artificial' que organiza, agrega y hace navegables las propuestas del Pacto del Bicentenario, presentando consensos nacionales y provinciales por tema. La tecnología de IA concreta (familia de modelos, si usa clustering/NLP/embeddings o LLM) NO está identificada explícitamente en las fuentes públicas halladas.</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no-claro</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Privado</t>
+          <t>Sociedad Civil</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>cerrado</t>
+          <t>desconocido</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>Consejo Nacional de Educación del Perú</t>
+          <t>Fundación Panamá Participa (sociedad civil, Panamá), iniciativa liderada por Paulina Franceschi. El proceso participativo de origen (Pacto del Bicentenario 'Cerrando Brechas') fue convocado por el Gobierno de Panamá a través del mecanismo de Concertación Nacional para el Desarrollo (presidente Laurentino Cortizo), con apoyo del PNUD.</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4559,65 +4559,65 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>0</v>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="W32" s="5" t="n">
+        <v>5</v>
       </c>
       <c r="X32" s="4" t="inlineStr">
         <is>
-          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
+          <t>Confirmar sistema_IA / tipos de IA / uso de LLM generativa / funcion_IA (método técnico) → https://mansaidea.com/ (intentar archive.org / cache); buscar 'Mansa Idea metodología inteligencia artificial procesamiento propuestas' y entrevistas técnicas a Paulina Franceschi / Fundación Panamá Participa. · Confirmar estado de actividad / evidencia de actividad 2026 → https://mansaidea.com/ ; buscar 'Mansa Idea 2025' / 'Mansa Idea 2026' / 'Fundación Panamá Participa actividad reciente'. · Confirmar nivel de consolidación → https://mansaidea.com/ ; buscar evidencia de actualizaciones periódicas del corpus o nuevas convocatorias. · Confirmar convocante (atribución) → https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/ · Confirmar naturaleza jurídica Fundación Panamá Participa (empresa vs ONG) (abrir la fuente)</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional</t>
+          <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
+          <t>PA-mansa-idea-pacto-del-bicentenario</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+          <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (idb). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo no viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking depende del plan contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras de investigacion (&gt;=14 busquedas/fetches) no se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el contenido de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, excluido del criterio).</t>
+          <t>Una consulta pública para recoger opiniones sobre el Proyecto Educativo Nacional 2036, utilizando encuestas en línea, talleres y mesas deliberativas.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Participación Digital; Gobernanza Colaborativa</t>
+          <t>Gobernanza Colaborativa</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Implementación</t>
+          <t>Análisis</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>Uso único</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>gobierno nacional</t>
+          <t>otra institución pública</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>apoyo</t>
+          <t>contenido</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Capacidad de la plataforma Go Vocal: el modulo 'Sensemaking'/'AI Analysis' analiza y resume automaticamente grandes conjuntos de aportes, etiqueta automaticamente, detecta sentimiento e idioma, detecta patrones entre grupos y descubre vinculos estadisticamente significativos entre demografia, experiencia y prioridades, reduciendo el tiempo de analisis (&gt;=50% segun Go Vocal). Esa capacidad esta sujeta al plan contratado (Premium para auto-insights). no confirmado que la instancia de Trinidad la active ni use sobre el contenido de los aportes del NDTS. La unica IA confirmada en el ecosistema tt es AskNDTS, un chatbot conversacional que responde preguntas sobre el NDTS (FAQ informativo, no procesa aportes).</t>
+          <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4642,17 +4642,17 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Plataforma Go Vocal (antes CitizenLab), software de participacion ciudadana que ofrece de forma NATIVA pero NO por defecto un modulo de IA/NLP llamado 'Sensemaking'/'AI Analysis' (analisis y resumen automatico de aportes ciudadanos, deteccion de patrones, etiquetado automatico, deteccion de sentimiento, vinculos estadisticos). Segun el Go Vocal Support Base, el acceso a esa funcion DEPENDE DEL PLAN (Advanced Sensemaking con auto-insights = plan Premium), por lo que su disponibilidad en una instancia concreta no es automatica. En la instancia de Trinidad (engage.gov.tt) NO se confirma activacion ni uso de dicho modulo de IA sobre el contenido de los aportes del NDTS. Aparte, AskNDTS es un chatbot de IA conversacional (FAQ sobre el NDTS), pero no procesa aportes de un proceso participativo (excluido).</t>
+          <t>Procesamiento del Lenguaje Natural (PLN) / Comprensión del Lenguaje Natural (NLU)</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Chatbot - Inespecífico</t>
+          <t>NLP - Tópicos; NLP - Sentiment</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>no-claro</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4667,17 +4667,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>activo</t>
+          <t>cerrado</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
+          <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4687,158 +4687,286 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>MEDIA</t>
-        </is>
-      </c>
-      <c r="W33" s="5" t="n">
-        <v>5</v>
+          <t>ALTA (baseline 2025 + reverif. web 2026)</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="X33" s="4" t="inlineStr">
         <is>
-          <t>Confirmar si el módulo de IA de Go Vocal (Sensemaking) se activó sobre los aportes, o si el uso de IA es solo el chatbot informativo AskNDTS. Revisar el panel de engage.gov.tt o consultar al Ministerio (MPAAI). · Confirmar uso de IA en el proceso / rol de la IA (metodologia del Actionable Feedback) → https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan · Confirmar uso de IA en el proceso (plan contratado por TT) → https://www.govocal.com/plans · Confirmar uso de LLM generativa → https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool · Confirmar nivel de consolidación → https://engage.gov.tt/projects · Confirmar ano_cierre / estado de actividad → https://engage.gov.tt/pages/information · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+          <t>Datos completos y con fuente. Verificación estándar: abrir la fuente y confirmar tipo de proceso, etapas, nivel (0-3) y convocante.</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>https://support.govocal.com/en/articles/8316692-ai-analysis</t>
+          <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>TT-engagett-plataforma-go-vocal</t>
+          <t>PE-consulta-ciudadana-sobre-el-proyecto-nac</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EngageTT (engage.gov.tt) es la plataforma de participacion ciudadana del Ministry of Digital Transformation de Trinidad y Tobago (desde mayo 2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), lanzada en el simposio del NDTS el 12 de febrero de 2025 junto al BID (idb). Se usa como canal de participacion en el proceso de planificacion nacional del National Digital Transformation Strategy (NDTS) 2024-2027, donde ciudadanos, empresas y partes interesadas reciben actualizaciones y aportan retroalimentacion via encuestas, sondeos (polls), un 'Open Forum' de ideas y el envio de propuestas. La instancia corre sobre el software Go Vocal (antes CitizenLab) -confirmado por la ruta interna 'projects/e-democracy-govocal-internal'-. Go Vocal incorpora un modulo de IA/NLP de 'Sensemaking' (analisis y resumen automatico de aportes), pero ese modulo no viene activo por defecto: segun la documentacion de soporte de Go Vocal, el acceso a la funcion de AI Analysis/Sensemaking depende del plan contratado (Advanced Sensemaking con auto-insights esta en el plan Premium). Tras de investigacion (&gt;=14 busquedas/fetches) no se halla evidencia alguna de que la instancia de Trinidad active ni use esas funciones de IA sobre el contenido de los aportes; toda la documentacion describe a EngageTT como recolector (surveys, polls, Open Forum, ideas), es decir plataforma usada como formulario sin analisis automatico confirmado. Existe ademas AskNDTS, un chatbot/PWA de IA conversacional para responder preguntas sobre el NDTS (rol de FAQ informativo, excluido del criterio).</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Participación Digital; Gobernanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>gobierno nacional</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>apoyo</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Capacidad de la plataforma Go Vocal: el modulo 'Sensemaking'/'AI Analysis' analiza y resume automaticamente grandes conjuntos de aportes, etiqueta automaticamente, detecta sentimiento e idioma, detecta patrones entre grupos y descubre vinculos estadisticamente significativos entre demografia, experiencia y prioridades, reduciendo el tiempo de analisis (&gt;=50% segun Go Vocal). Esa capacidad esta sujeta al plan contratado (Premium para auto-insights). no confirmado que la instancia de Trinidad la active ni use sobre el contenido de los aportes del NDTS. La unica IA confirmada en el ecosistema tt es AskNDTS, un chatbot conversacional que responde preguntas sobre el NDTS (FAQ informativo, no procesa aportes).</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Plataforma Go Vocal (antes CitizenLab), software de participacion ciudadana que ofrece de forma NATIVA pero NO por defecto un modulo de IA/NLP llamado 'Sensemaking'/'AI Analysis' (analisis y resumen automatico de aportes ciudadanos, deteccion de patrones, etiquetado automatico, deteccion de sentimiento, vinculos estadisticos). Segun el Go Vocal Support Base, el acceso a esa funcion DEPENDE DEL PLAN (Advanced Sensemaking con auto-insights = plan Premium), por lo que su disponibilidad en una instancia concreta no es automatica. En la instancia de Trinidad (engage.gov.tt) NO se confirma activacion ni uso de dicho modulo de IA sobre el contenido de los aportes del NDTS. Aparte, AskNDTS es un chatbot de IA conversacional (FAQ sobre el NDTS), pero no procesa aportes de un proceso participativo (excluido).</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Chatbot - Inespecífico</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>no-claro</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>activo</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>Ministry of Digital Transformation de Trinidad y Tobago (desde el 23-may-2025 fusionado en el Ministry of Public Administration and Artificial Intelligence, MPAAI), en colaboracion con el Banco Interamericano de Desarrollo (BID/IDB). Plataforma de software: Go Vocal (antes CitizenLab), empresa belga.</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="W34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="X34" s="4" t="inlineStr">
+        <is>
+          <t>Confirmar si el módulo de IA de Go Vocal (Sensemaking) se activó sobre los aportes, o si el uso de IA es solo el chatbot informativo AskNDTS. Revisar el panel de engage.gov.tt o consultar al Ministerio (MPAAI). · Confirmar uso de IA en el proceso / rol de la IA (metodologia del Actionable Feedback) → https://engage.gov.tt/ideas/ndts-2025-actionable-feedback-implementation-plan · Confirmar uso de IA en el proceso (plan contratado por TT) → https://www.govocal.com/plans · Confirmar uso de LLM generativa → https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool · Confirmar nivel de consolidación → https://engage.gov.tt/projects · Confirmar ano_cierre / estado de actividad → https://engage.gov.tt/pages/information · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>https://support.govocal.com/en/articles/8316692-ai-analysis</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>TT-engagett-plataforma-go-vocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Referéndum nacional para derogar 135 artículos de la Ley de Urgente Consideración (LUC). Un equipo de la Universidad de la República corrió una conversación Pol.is en paralelo al referéndum del 27/03/2022 (documentado como caso 2021).</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="F35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Uso único</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>universidad</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Público</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>contenido</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>Mapea las respuestas de los participantes, agrupa opiniones en clusters e identifica automáticamente statements de consenso y de división ('bridges') sobre una consulta multi-tema.</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Pol.is — clustering de opiniones (reducción de dimensionalidad / agrupamiento no supervisado sobre votos de acuerdo/desacuerdo a statements ciudadanos)</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>Clustering; ML - Inespecífico</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>Sociedad Civil</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>cerrado</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>Equipo de 13 personas de la Universidad de la República (UdelaR) — ingenieros, comunicadores y científicos de datos; plataforma Pol.is (The Computational Democracy Project)</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>MEDIA (fuente primaria + OCDE 2025; fetch primario bloqueado por proxy, citas vía repo/WebSearch)</t>
         </is>
       </c>
-      <c r="W34" s="5" t="n">
+      <c r="W35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="X34" s="4" t="inlineStr">
+      <c r="X35" s="4" t="inlineStr">
         <is>
           <t>Confirmar criterio_temporal → https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/ · Confirmar nivel de consolidación → https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/ · Confianza media: cotejar tipo de proceso, etapa, nivel (0-3) y convocante con la fuente antes de calcular.</t>
         </is>
       </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>UY-polis-referendum-luc</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z34"/>
+  <autoFilter ref="A1:Z35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6896,7 +7024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7219,30 +7347,90 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>Meta Community Forum on Generative AI — cohorte Brasil (Deliberative Polling, Stanford)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>scientific samples from Brazil, Germany, Spain, and the United States (deliberation.stanford.edu/meta-community-forum-generative-ai-results)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>On October 28-29, 2023, participants from these countries gathered on the Stanford Online Deliberation Platform... to consider future directions for the development of AI chatbots (deliberation.stanford.edu)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Moderación automatizada de la deliberación en grupos pequeños = apoyo a la IMPLEMENTACIÓN (verbatim del moderador, informe Stanford DDL/FSI)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Deliberación 28-29 oct 2023; '2023 Results Announced' (abr-2024) — proceso concluido (deliberation.stanford.edu)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Uso único: foro de oct-2023; el foro 2024 de 'AI Agents' NO incluyó a Brasil (deliberation.stanford.edu / FSI)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Foro de Meta diseñado y ejecutado por el Stanford Deliberative Democracy Lab; BIT 'designed and delivered' foros 'on Meta's behalf' (transparency.meta.com; bi.team)</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>the small group discussion sessions were conducted using the Stanford Online Deliberation Platform, developed by the Deliberative Democracy Lab and the Stanford Crowdsourcing Democracy Team, with participants each assigned to rooms of 8-12 people (bi.team/blogs/metas-community-forum-on-ai — socio ejecutor)</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>[La plataforma] moderated the video based discussions, controlled the queue for talking, nudged those who had not volunteered to talk, intervened if there was incivility, and moved the group through the agenda... 'the AI-assisted featured moderator' (informe Stanford DDL/FSI, PDF oficial leído íntegro)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>https://deliberation.stanford.edu/meta-community-forum-generative-ai-results
+https://transparency.meta.com/governance/community-forums/2023-community-forum-on-generative-AI/
+https://about.fb.com/news/2024/04/leading-the-way-in-governance-innovation-with-community-forums-on-ai/
+https://cddrl.fsi.stanford.edu/publication/meta-community-forum-results-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>OPA Piauí - Orçamento Participativo Digital (Colab + AWS)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí, em parceria com a Colab. (Colab, 'OPA, Colab e a participação digital no Piauí')</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>OPA é o Orçamento Participativo 100% digital do Governo do Estado do Piauí... Após analisar a viabilidade das propostas, o Governo do Estado disponibilizará uma votação por meio da Colab para que qualquer cidadão acima de 16 anos com CPF possa votar no que considera mais importante para o seu município. (Colab)</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Todo esse processo é realizado por meio da plataforma Colab Gov... O sistema utiliza tecnologia da AWS, referência mundial em segurança digital. (la IA/tecnología se presenta como soporte operativo, de eficiencia y de seguridad del flujo, no como análisis del contenido de las propuestas → rol de apoyo)</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>https://www.colab.com.br/noticias/opa-e-a-participacao-popular-como-as-plataformas-colab-fortalecem-o-processo-participativo-no-piaui/
 https://sia.pi.gov.br/projetos/opa/
@@ -7256,63 +7444,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Plan Plurianual de la ciudad de Natal</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Implementación, Análisis</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Plataforma</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -7321,108 +7452,165 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Plan Plurianual de la ciudad de Natal</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: modelos de lenguaje identifican el tema de cada mensaje ciudadano por WhatsApp; nueva edición PPA 2026-2029 'Plano Natal Pra Frente'.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Plataforma</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Prefeitura Municipal de Natal, a través de la Secretaría Municipal de Planeamiento (SEMPLA)</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Interactuar con los ciudadanos y sistematizar respuestas para generar propuestas</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.natal.rn.gov.br/news/post2/42103</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>Portal e-Cidadania: Marcado automático de respuestas ciudadanas en videos de audiencias públicas</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Traducción Política</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2025: la IA analiza transcripciones de 1.800+ audiencias y marca 2.700+ preguntas ciudadanas como respondidas.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Senado Federal de Brasil</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Identificar y marcar momentos en los videos donde las preguntas ciudadanas fueron respondidas, ya sea directa o indirectamente.</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2025/03/28/e-cidadania-utiliza-ia-para-marcar-respostas-aos-cidadaos-em-audiencias
 https://ipen-network.org/spotlight-on-public-engagement-practice-brazil/</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>São Paulo - Programa de Metas / Participe Mais (Gemini)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Programa de Metas 2025-2028, PPA e PAS 2026-2029 - portal Participe Mais da Prefeitura de São Paulo (participemais.prefeitura.sp.gov.br/legislation/processes/323).</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>as sugestões enviadas pela população para o PPA (Plano Plurianual) 2026-2029, durante a consulta pública do Programa de Metas no portal Participe Mais, que é a plataforma de participação social da Prefeitura</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios, facilitando a divulgação das propostas. (...) exibição dos relatórios e painéis visuais gerados pela análise destacam: ranking dos temas mais recorrentes; participação em cada distrito e subprefeitura</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Após o Ciclo Participativo, com 36 audiências públicas híbridas pela cidade (abril e maio), recebimento de 6.368 propostas e mais de 31 mil interações dos cidadãos (...) através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Em maio de 2025, foi elaborada uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios (...) No desenvolvimento da ferramenta foram utilizados conhecimentos em dados abertos, inteligência artificial e gestão pública.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>através do site de consultas públicas da Prefeitura - ParticipeMais, a gestão incorporou seis metas a mais à versão inicial de 126</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>A metodologia demonstra a solução com exposição de trechos de código e explicação das tecnologias utilizadas: Python, Pandas, Google Gemini. (...) desafios reais encontrados, como o alto volume de dados, otimização do tempo de análise e ajustes necessários nos comandos para a Inteligência Artificial</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>uma ferramenta que classifica as propostas para o Programa de Metas em categorias e as ordena por assunto e quantidade de apoios</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/em-andamento/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
 https://www.saopaulo.sp.leg.br/escoladoparlamento/cursos/cursos-anteriores/cursos-realizados-em-2025/oficina-analise-de-dados-com-inteligencia-artificial-na-gestao-publica-programa-de-metas/
@@ -7438,58 +7626,58 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>e-Cidadania Senado - IA matching de ideas legislativas</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Cidadãos ajudam a escrever projetos de lei com ferramenta de inteligência artificial — Senado Notícias (Senado Federal, Brasil), 16/01/2026.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado permite que ideias enviadas ao portal e-Cidadania influenciem projetos de lei — mesmo quando não atingem o número mínimo de apoios antes exigido</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão. As ideias selecionadas podem ser incorporadas ao projeto e citadas em sua justificação</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>IA vai aproximar ideias legislativas do e-Cidadania a projetos de senadores — Rádio Senado, 15/01/2026 (matéria de divulgação da ferramenta em uso no início de 2026)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>O primeiro resultado já veio: uma sugestão enviada por Cândida Magalhães, de São Paulo, que pedia atendimento psicológico gratuito para filhos de mulheres vítimas de violência doméstica, foi identificada pela ferramenta e incorporada a um projeto de lei: o PL 6.125/2025</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>uma nova ferramenta de inteligência artificial criada pelo Senado</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Quando um senador pede ajuda à Consultoria Legislativa para elaborar um projeto, a equipe de consultores solicita ao e-Cidadania uma lista de sugestões feitas pelos cidadãos. Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Com o uso da inteligência artificial, é feita uma busca no banco de ideias legislativas e, então, são selecionadas aquelas que são compatíveis com a proposta em questão</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>https://www12.senado.leg.br/noticias/materias/2026/01/16/cidadaos-ajudam-a-escrever-projetos-de-lei-com-ferramenta-de-inteligencia-artificial
 https://www.poder360.com.br/poder-congresso/ia-do-senado-usa-sugestoes-enviadas-por-cidadaos-em-projetos-de-lei/
@@ -7501,58 +7689,58 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Cabildos 2016</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (academico): Evidencia académica del NLP sobre los cabildos 2016: argument mining sobre 240.468 argumentos (ACL 2017, UChile/DCC) y Structural Topic Modeling (PLOS One 2022)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Biblioteca del Congreso Nacional</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Clasificación y análisis de texto para identificar conceptos clave</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>https://www.bcn.cl/procesoconstituyente/cabildos2016/
 https://aclanthology.org/W17-5101/
@@ -7560,58 +7748,58 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos (ECQQ) - MinCiencia</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>El Chile que Queremos cierra etapa de diálogos con más de 130 mil participantes en las 345 comunas del país (titular de noticia del Ministerio de Desarrollo Social y Familia - Gobierno de Chile).</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó la iniciativa el viernes 22 de noviembre de 2019. La participación fue posible hasta el 31 de marzo a través de diálogos ciudadanos o consultas individuales en www.chilequequeremos.cl (gob.cl).</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Este repositorio contiene los procedimientos para realizar la clasificación de las contribuciones con redes neuronales (README del repositorio MinCiencia/ECQQ, carpeta contributions_rnn).</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020. La decisión de concluir anticipadamente los diálogos ciudadanos fue parte de las medidas del gobierno para frenar la propagación del COVID-19, aunque la plataforma permaneció abierta hasta el 31 de marzo de 2020.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>130.810 personas participaron en los Diálogos Ciudadanos impulsados por El Chile Que Queremos, desde noviembre de 2019 hasta marzo de 2020 (proceso único, una sola edición).</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>El Gobierno presentó 'El Chile que Queremos', iniciativa de diálogos y escucha social para avanzar en nuevas propuestas para el país. La iniciativa fue un esfuerzo conjunto entre los Ministerios de Desarrollo Social y Familia, de Ciencia, Tecnología, Conocimiento e Innovación, de Agricultura, la Secretaría General de Gobierno y la División de Gobierno Digital (gob.cl / desarrollosocialyfamilia.gob.cl).</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>La información recibida de la ciudadanía es sistematizada por el Ministerio de Ciencias, siendo la ciencia de datos una herramienta clave para este amplio y participativo ejercicio de escucha. / clasificación de las contribuciones con árboles de decisión (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Grouping Emotions.ipynb que sirve para sistematizar las Emociones / Analisis de Topicos - Necesidades.ipynb que sirve para sistematizar tanto las necesidades personales como las del país (README MinCiencia/ECQQ).</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>https://github.com/MinCiencia/ECQQ
 https://www.desarrollosocialyfamilia.gob.cl/noticias/el-chile-que-queremos-cierra-etapa-de-dialogos-con-mas-de-130-mil-participantes-en-las-345-comunas-d
@@ -7623,228 +7811,228 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Estrategia de Gobierno Digital. Informe proceso participativo segunda consulta ciudadana</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Secretaría de Gobierno Digital</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Identificar patrones, sintetizar las principales críticas y estructurar las conclusiones de manera clara y coherente de datos cualitativos en encuesta de consulta ciudadana</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>https://participacion.digital.gob.cl/projects/segunda-consulta-estrategia-de-gobierno-digital-2030
 https://participacion.digital.gob.cl/folders/consultas-ciudadanas</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Estudio dIAlogos - Percepciones de Futuro</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Implementación, Análisis</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Fundación Encuentros del Futuro y Merlín Research</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Realización de entrevistas y codificación de respuestas</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>https://estudiodialogos.cl/
 https://fairlac.iadb.org/en/dialogos-study-perceptions-future</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Jornada de Escucha Lanzamiento Instituto de Políticas Públicas UNAB</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Identificar tópicos y organizarlos demográficamente para generar visualizaciones</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/
 https://public.tableau.com/app/profile/ivania.yovanovic/viz/JornadasInstitutoPolticasPblicasUNAB/Dashboard3</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>LXS 400 - Chile Delibera</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>In 2020, the Senate of Chile partnered with the Stanford Center for Deliberative Democracy to involve citizens in the online deliberative process 'LXS 400 - Chile Delibera' performed through the Stanford Online Deliberation Platform. (OCDE 2025, 'AI in civic participation and open government')</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Over 500 citizens representative of the Chilean society discussed in small groups and deliberated in plenary sessions on health and pension reforms. (OCDE 2025) / Entre el 5 y el 7 de marzo, 400 personas seleccionadas a traves de una metodologia aleatoria y representativas de todo Chile se reunieron para deliberar sobre dos de los temas publicos mas importantes para el pais: pensiones y salud.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / El Centro de Microdatos de la Universidad de Chile, usando tecnologia basada en Inteligencia Artificial (IA), selecciono esta muestra representativa.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Lxs 400: Chile Delibera... es un evento de participacion ciudadana de escala nacional realizado en Chile desde el 9 de diciembre de 2020, con su evento principal a fines de marzo de 2021. (Wikipedia ES) [Evento puntual de una edicion 2020-2021; no se hallaron ediciones posteriores recurrentes].</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>La iniciativa fue impulsada por la Fundacion Tribu; el Senado a traves de la Comision de Desafios del Futuro; la Asociacion Chilena de Municipalidades; la Universidad de Chile; y el Centro para la Democracia Deliberativa de la Universidad de Stanford.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably... (OCDE 2025) [confirma que SI se uso IA dentro del proceso, en rol de facilitacion/logistica].</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>The platform used an AI tool to keep time and distribute speaking rights equitably, allowing participants to form speaking queues and discuss in small groups with timed agendas. (OCDE 2025) / An automated moderator controls perspective elicitation, with an automated cue system to determine which participant to elicit a perspective from next and an automated timer to determine how long each participant has to state their perspective. (descripcion de la Stanford Online Deliberation Platform)</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>https://www.oecd.org/en/publications/2025/06/governing-with-artificial-intelligence_398fa287/full-report/ai-in-civic-participation-and-open-government_51227ce7.html
 https://deliberation.stanford.edu/news/lxs-400-national-deliberative-poll-chile
@@ -7856,121 +8044,64 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>La voz de los nuevos votantes</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Implementación, Análisis</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Análisis de transcripciones para identificación de temas y palabras clave.</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/wp-content/uploads/2023/10/2-IPP-UNAB_Informe-Voz-de-los-votantes.pdf
 https://ipp.unab.cl/publicacion/la-voz-de-los-nuevos-votantes-san-bernardo/</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Participación Ciudadana Proceso Constitucional</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Cerrado</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Secretaría de Participación Ciudadana</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -7979,108 +8110,165 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>Participación Ciudadana Proceso Constitucional</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Cerrado</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Secretaría de Participación Ciudadana</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Identificación de tópicos (nodos centrales) y visualización de frases</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.secretariadeparticipacion.cl/wp-content/uploads/2023/10/Informe-SPC-Final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>Tenemos que hablar de Chile</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Universidad de Chile y Pontificia Universidad Católica de Chile</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Sistematización de datos y análisis de contenido de las intervenciones ciudadanas</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>https://www.tenemosquehablardechile.cl/
 https://static1.squarespace.com/static/630d0dbf05b8104ed4d55d7f/t/67f694b2f91e4f228bb941cb/1744213189210/01.+Primer-InformeTQHDCH.pdf</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Un encuentro para la equidad de género en la movilidad en Chile</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Universidad Andres Bello</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Análisis temático de las transcripciones de las mesas</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>https://ipp.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
 https://noticiasrepositorio.unab.cl/el-centro-ciudhad-y-observatorio-territorial-del-ipp-unab-realizaron-la-jornada-participativa-un-encuentro-para-la-equidad-de-genero-en-la-movilidad-en-chile/
@@ -8088,58 +8276,58 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Chatico</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares, Presupuestos Participativos</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado 2024-2028: NLP y tecnologías semánticas procesaron 147.422 participaciones (10% propuestas libres) para el Plan Distrital de Desarrollo. Citado por</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Secretaría General de la Alcaldía Mayor de Bogotá</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Interactuar con ciudadanos, responder consultas y plataforma para votar en causas ciudadanas y presupuesto participativo</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>https://secretariageneral.gov.co/noticias/chatico-el-agente-virtual-de-servicio-la-ciudadania-supero-los-36-millones-de-conversaciones
 https://bogota.gov.co/mi-ciudad/gestion-publica/distrito-presenta-su-agente-virtual-chatico-que-guia-la-ciudadania
@@ -8147,63 +8335,6 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ECHO – HáblameD Medellín</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Governanza Colaborativa</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Implementación, Análisis</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -8212,162 +8343,219 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>ECHO – HáblameD Medellín</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Governanza Colaborativa</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Implementación, Análisis</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reconfirmado: la IA del UNFPA clasifica por ODS las conversaciones ciudadanas captadas en campo (5.000+ personas, 16 comunas).</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA Colombia (Laboratorio de Innovación) y Personería de Medellín</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Analizar las percepciones ciudadanas y vincularlas con los ODS, facilitando la toma de decisiones en la planificación del desarrollo local.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>https://colombia.unfpa.org/es/news/primeros-resultados-de-echo-en-colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>Gaitana IA (resguardo Zenú, Bajo Sinú, Córdoba)</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>la herramienta de un resguardo indígena (Zenú, Bajo Sinú, Colombia) para llegar al Congreso (La Silla Vacía)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>a platform for young people in the Zenú community to decide, through digital voting, how they wanted to allocate local budgets</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>The AI summarizes proposals, organizes consensus, and facilitates collective decision-making</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>More than 10,000 users participate in the chatbot at gaitanaia.org, whose discussions feed the community's positions and proposals</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Gaitana IA is a tool created by Carlos Redondo Rincón ... a platform for young people in the Zenú community</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Gaitana is built on the DeepSeek large language model, adapted to the Zenú worldview ... summarizes proposals, organizes consensus</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>artificial intelligence organizes opinions, processes trends and builds consensuses that, if approved, would become legislative initiatives (KienyKe)</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>https://www.lasillavacia.com/en-vivo/gaitana-ia-la-herramienta-de-un-resguardo-indigena-para-llegar-al-congreso/
 https://www.kienyke.com/</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Tenemos que hablar de Colombia</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>BBDD 2025: Cerrado</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Alianza entre seis universidades colombianas (EAFIT, Universidad Nacional de Colombia, Universidad de los Andes, Universidad del Valle, Universidad del Norte y Universidad Industrial de Santander), con el apoyo del Grupo SURA y la Fundación Ideas para la Paz.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Etiquetado de tópicos y sentimientos a partir de la información recolectada en diálogos ciudadanos. </t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>https://tenemosquehablarcolombia.co/
 https://tenemosquehablarcolombia.co/resultados/</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>CU</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Consulta Popular Código de las Familias (GEMA-CEN / XISCOP)</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Para agilizar la recogida y el procesamiento de los criterios, la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN) [proceso de consulta popular del Código de las Familias en Cuba].</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>consulta popular del proyecto del Código de las Familias (...) la Universidad de las Ciencias Informáticas (UCI) y Datys diseñaron dos sistemas informáticos de gestión (XISCOP y GEMA-CEN)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>luego se sube a GEMA-CEN (también operado por especialistas) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares, facilitando el trabajo y evitando errores. GEMA-CEN permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Más de seis millones 481 mil personas participaron en las reuniones (...) la consulta popular del proyecto del Código de las Familias (...) convocada entre febrero y abril [de 2022]; del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>del total de propuestas procesadas se determinaron 5 237 propuestas típicas por Título, conformadas a partir de la asociación de propuestas idénticas y de aquellas con redacción diferente pero referidas al mismo criterio u opinión</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>La consulta popular (...) fue organizada y supervisada por el Consejo Electoral Nacional (CEN) [órgano del Estado cubano]; los resultados se entregaron al Parlamento (Asamblea Nacional) y a su Comisión redactora</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>se sube a GEMA-CEN (...) que, a través del análisis inteligente de los expedientes, organiza las propuestas y agrupa las similares (...) permite determinar las propuestas típicas para un párrafo en cada una de las categorías establecidas</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>GEMA es una herramienta para el análisis de información contenida en grandes volúmenes de archivos de diferentes formatos e idiomas, con funcionalidades orientadas a la recuperación y clasificación de información (...) complementando los resultados mediante técnicas modernas de recuperación de información para obtener archivos similares, eliminar resultados no relevantes y agrupar documentos comunes</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>http://www.datys.cu/spa/site/product/15
 https://www.granma.cu/cuba/2022-01-24/herramientas-digitales-seran-claves-durante-la-consulta-popular-del-codigo-de-las-familias-24-01-2022-13-01-18
@@ -8379,60 +8567,60 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PAGA IA </t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Referendos e Iniciativas Populares</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: integrada al Tercer Plan de Acción de Estado Abierto 2025-2027; analiza las propuestas ciudadanas y sugiere actividades.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Plataforma</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Gobierno Abierto Ecuador, en colaboración con la Fundación de Ayuda por Internet (Fundapi)</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Analizar temas propuestos y generar sugerencias de compromisos basados en experiencias previas de planes de acción de gobierno abierto
 </t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>https://ia.gobiernoabierto.ec/
 https://ia.gobiernoabierto.ec/
@@ -8440,58 +8628,58 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>GT</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Guatemala Joven Conversa </t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Implementación</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (institucional): Reconfirmado: diálogos digitales con IA (DPPA ONU + Fundación Esquipulas); 300+ jóvenes; la IA permite intercambios anónimos y votación de aportes para identifi</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Oficina del Coordinador Residente de las Naciones Unidas en Guatemala y Fundación Esquipulas para la Paz, la Democracia, el Desarrollo y la Integración</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Facilitar diálogos anónimos en tiempo real, permitir votaciones sobre opiniones y generar alertas sobre desviaciones en la ejecución de obras</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>https://dppa.medium.com/usando-el-poder-de-la-ia-para-impulsar-la-participaci%C3%B3n-pol%C3%ADtica-de-los-j%C3%B3venes-en-guatemala-6f6d7bf45a47
 https://www.fundaesq.org/guatemala-joven-la-voz-de-una-generacion-de-cambios/
@@ -8499,115 +8687,115 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>HN</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RedPública + iVerify </t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Referendos e Iniciativas Populares</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Análisis</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>HN</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RedPública + iVerify </t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Referendos e Iniciativas Populares</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Análisis</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>reconfirmado web (institucional): Reverificación: plataforma de propuestas ciudadanas con módulo de análisis de tendencias; evidencia de IA central débil, revisar en Fase 2.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Programa de las Naciones Unidas para el Desarrollo (PNUD) en colaboración con CEUTEC y la Unión Europea.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Detectar y clasificar desinformación electoral antes de su publicación; analizar y agrupar temas de propuestas ciudadanas.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.undp.org/es/honduras/historias/participacion-ciudadana-con-innovacion-digital-traves-de-redpublica-honduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>MX</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Guanajuato InteliGENTE 2024-2030 (Programa de Gobierno del Estado de Guanajuato)</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Guanajuato hará historia con el primer Programa de Gobierno realizado con IA</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Para integrar la participación ciudadana en este Programa de Gobierno, se realizaron cuatro talleres cubriendo las regiones noreste, norte, centro y sur, con representación de los 46 municipios de Guanajuato.</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno de Guanajuato 2024-2030 es la guía que orienta las acciones del Gobierno de la Gente para lograr un Guanajuato sostenible, equitativo y transparente.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Su diseño incorporó el uso de inteligencia artificial para integrar más de 26 mil voces de distintas regiones y sectores</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>El Programa de Gobierno 2024-2030 hizo historia al ser el primero en realizarse con ayuda de la Inteligencia Artificial (IA), según anunció la Gobernadora Libia Dennise García Muñoz Ledo en el Consejo de Planeación para el Desarrollo del Estado de Guanajuato (COPLADEG).</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Recibieron miles de ideas y propuestas, y para asegurar que cada una fuera tomada en cuenta, utilizaron herramientas de inteligencia artificial. Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía.</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Esta tecnología les ayudó a procesar y organizar la información, identificar las prioridades más mencionadas por la ciudadanía y entender las necesidades de cada región. Fue la herramienta que les permitió transformar el gran diálogo social en datos claros para la toma de decisiones.</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>https://guanajuatointeligente.com/como-hicimos-el-programa/
 https://guanajuatointeligente.com/
@@ -8620,111 +8808,111 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>MX</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Presupuesto CRECES</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Presupuestos Participativos</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Implementación</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>BBDD 2025: Activo</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Continuidad (BBDD 2025): Uso único</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Ayundamiento de Hermosilla</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
-        </is>
-      </c>
-    </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Presupuesto CRECES</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Presupuestos Participativos</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Implementación</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>BBDD 2025: Activo</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Continuidad (BBDD 2025): Uso único</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Ayundamiento de Hermosilla</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Facilitar las votaciones haciéndolo en forma conversacional</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>https://presupuestocreces.hermosillo.gob.mx/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea (Pacto del Bicentenario "Cerremos la Brecha", Panamá)</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea (www.mansaidea.com), una plataforma basada en inteligencia artificial que recoge miles de propuestas ciudadanas... iniciativa de alcance nacional que se nutre de ideas y propuestas que miles de panameños hicieron durante el desarrollo del Pacto del Bicentenario. (Panamá; fuentes panama24horas.com.pa y laestrella.com.pa)</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea, resultado del Pacto del Bicentenario, ofrece acceso fácil y transparente a más de 175 mil ideas y propuestas generadas por ciudadanos de todo el país. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía.</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales. (la IA agrega/organiza/sintetiza el contenido de las propuestas por tema y territorio = Análisis + Traducción Política; el método técnico exacto no se detalla en las fuentes).</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>La plataforma fue lanzada el 1 de abril de 2024... constituye una herramienta valiosa de participación ciudadana muy relevante para ciudadanos, candidatos a cargos de elección popular y medios durante la campaña electoral y luego como recurso para el monitoreo del mandato ciudadano. (un despliegue concreto de la plataforma, 2024; sin evidencia de ediciones recurrentes).</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>La Fundación Panamá Participa lanzó Mansa Idea... iniciativa liderada por Paulina Franceschi a través de la Fundación Panamá Participa (sociedad civil). El proceso participativo de origen: 'El 26 de noviembre de 2020, el presidente Laurentino Cortizo Cohen lanzó la iniciativa denominada Pacto del Bicentenario Cerrando Brechas' (gobierno nacional / Concertación Nacional).</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Mansa Idea es una plataforma innovadora basada en inteligencia artificial cuyo contenido refleja una inteligencia colectiva que busca construir, a través de miles de propuestas, un mejor futuro para todos. (la IA procesa el contenido de las propuestas del proceso participativo).</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>La herramienta digital recoge en un solo clic los consensos nacionales y regionales/provinciales, constituyendo una poderosa base de datos de proyectos con información transparente, 100% confiable y de calidad generada por la ciudadanía. (agregación/síntesis de los aportes ciudadanos = rol sobre el contenido).</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>https://www.panama24horas.com.pa/panama/fundacion-panama-participa-lanza-plataforma-de-propuestas-ciudadanas-mansa-idea/
 https://www.laestrella.com.pa/panama/politica/mansa-idea-una-herramienta-digital-con-propuestas-para-candidatos-YD6746221
@@ -8735,58 +8923,58 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>PE</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>Consulta Ciudadana sobre el Proyecto Nacional de Educación</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Caso del índice ILIA 2025 (BBDD oficial del equipo)</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Governanza Colaborativa</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Análisis</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>reconfirmado web (prensa): VERIFICADO (fuente primaria): el CNE usó IBM Watson Discovery + Studio (ML/NLP) sobre 87.991 documentos de aportes ciudadanos de 847 eventos y 49 espacios de di</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Continuidad (BBDD 2025): Uso único</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Consejo Nacional de Educación del Perú</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Analizar las opiniones de los participantes y sistematizar la información de forma objetiva.</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>https://www.gob.pe/institucion/cne/noticias/502734-lanzan-consulta-ciudadana-por-el-proyecto-educativo-nacional
 https://cdn.www.gob.pe/uploads/document/file/1915017/CNE-%20proyecto-educativo-nacional-al-2036.pdf.pdf?v=1679434080
@@ -8795,54 +8983,54 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>EngageTT (engage.gov.tt) sobre plataforma Go Vocal (antes CitizenLab) - consulta del National Digital Transformation Strategy (NDTS) 2024-2027</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Project: National Digital Transformation Strategy | Ministry of Digital Transformation, Trinidad and Tobago (engage.gov.tt/projects/national-digital-transformation-strategy). Ruta interna confirmatoria: engage.gov.tt/projects/e-democracy-govocal-internal (la instancia corre sobre Go Vocal). En 2026: 'Projects | Ministry of Public Administration and Artificial Intelligence' (engage.gov.tt/projects).</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>EngageTT es una plataforma en linea (engage.gov.tt) donde ciudadanos, empresas y partes interesadas pueden recibir actualizaciones en tiempo real sobre iniciativas de transformacion digital y ofrecer retroalimentacion via encuestas y sondeos (polls); el Ministro anima a todos a participar y enviar ideas y comentarios sobre el NDTS, que se disena para evolucionar mediante el compromiso y la colaboracion continuos. Incluye un 'Open Forum' (engage.gov.tt/ideas/open-forum) y 'Input: Submitting Proposals' (engage.gov.tt/ideas/submitting-proposals).</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>The National Strategy for a Digital TT is finalized, and while the Ministry of Digital Transformation is no longer seeking input, they welcome feedback or comments through the citizen engagement digital platform Engage TT. (engage.gov.tt sigue operativo en 2026 bajo MPAAI).</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... launched during a NDTS Symposium in collaboration with the Inter-American Development Bank (IDB) on Wednesday, February 12th 2025. A major highlight... was the introduction of two new digital tools (EngageTT y AskNDTS). (Lanzamiento/anuncio unico en feb-2025; plataforma de uso continuo pero sin &gt;=2 ediciones de proceso participativo documentadas).</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>The Ministry of Digital Transformation (MDT) officially presented the National Digital Transformation Strategy (NDTS) 2024-2027... and introduced the EngageTT website - an online platform where citizens, businesses, and stakeholders can get real-time updates on digital transformation initiatives, and offer feedback via surveys and polls. (Convocante: gobierno nacional / Ministry of Digital Transformation, hoy MPAAI).</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Go Vocal Support Base (AI Analysis): 'Access to this feature depends on your plan. Advanced Sensemaking with auto-insights is available in the Premium plan.' -&gt; la IA/NLP de Go Vocal NO es automatica, depende del plan; y para EngageTT solo se documenta 'feedback via surveys and polls'/Open Forum/ideas, SIN mencion de analisis automatico por IA de los aportes. No se halla evidencia de activacion del NLP sobre el contenido en la instancia TT. 3a PASADA (refuerzo): Oxford Insights, 'The country's AI utilisation for citizens is concentrated in a robust Chatbot programme' (mas 'deployment of large language models for internal development purposes') -&gt; la IA ciudadana de TT es el chatbot, NO el analisis de aportes.</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Sin evidencia de IA aplicada al contenido de los aportes en engage.gov.tt. La unica IA confirmada de cara al ciudadano (AskNDTS/ANANSI) es chatbot de FAQ, excluido del criterio. En 3a pasada, el material de MPAAI 2026 enmarca la IA en el asistente ANANSI y en encuestas de AI-readiness (resultados 'consolidated and reviewed' en talleres), sin mencion de analisis por IA de los aportes del NDTS ni de Go Vocal Sensemaking.</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>https://support.govocal.com/en/articles/8316692-ai-analysis
 https://support.govocal.com/en/articles/9015305-faq-on-our-ai-sensemaking-tool
@@ -8864,54 +9052,54 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>UY</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Pol.is en el Referéndum Nacional de la LUC (Uruguay) — equipo UdelaR</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Polis has been used to facilitate discussion and build consensus ... in Uruguay on a national referendum (OCDE 2025, 'Governing with AI')</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists — ran Polis alongside the referendum</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>The algorithm maps participants' responses and clusters opinions, facilitating the identification of positions that are supported by the majority of participants (OCDE 2025)</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>16,499 people cast more than 295,000 votes ... The referendum was lost by less than 1%</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>A 13-person team from Uruguay's National University — engineers, communicators, and data scientists</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>ran Polis alongside the referendum to look for something deeper than "yes or no"</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Polis revealed that even where public safety divided people, surprising points of consensus broke through on other issues — bridges between groups</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>https://compdemocracy.org/case-studies/2021-uruguay-national-referendum/
 https://www.oecd.org/en/publications/governing-with-artificial-intelligence_795de142-en.html</t>
@@ -8919,7 +9107,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>